--- a/www/flightdata/xlsx/eoss-343.xlsx
+++ b/www/flightdata/xlsx/eoss-343.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="447">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="452">
   <si>
     <t>flight</t>
   </si>
@@ -36,6 +36,18 @@
     <t>h2fill</t>
   </si>
   <si>
+    <t>maxaltitude</t>
+  </si>
+  <si>
+    <t>numpoints</t>
+  </si>
+  <si>
+    <t>flighttime</t>
+  </si>
+  <si>
+    <t>flighttime_secs</t>
+  </si>
+  <si>
     <t>weights.client</t>
   </si>
   <si>
@@ -73,6 +85,9 @@
   </si>
   <si>
     <t>243</t>
+  </si>
+  <si>
+    <t>1hrs 45mins 19secs</t>
   </si>
   <si>
     <t>3.13</t>
@@ -1718,10 +1733,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1761,46 +1776,70 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="G2">
+        <v>78749</v>
+      </c>
+      <c r="H2">
+        <v>192</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J2">
+        <v>6319</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1815,102 +1854,102 @@
   <sheetData>
     <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:30">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C2" s="2">
         <v>45094.33592848379</v>
@@ -1928,13 +1967,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J2" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="K2">
         <v>349</v>
@@ -1958,7 +1997,7 @@
         <v>1.38461538</v>
       </c>
       <c r="V2" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="X2">
         <v>1.384615</v>
@@ -1969,10 +2008,10 @@
     </row>
     <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C3" s="2">
         <v>45094.33596957176</v>
@@ -1990,13 +2029,13 @@
         <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="K3">
         <v>311</v>
@@ -2020,7 +2059,7 @@
         <v>19.75</v>
       </c>
       <c r="V3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W3">
         <v>4.591346</v>
@@ -2043,10 +2082,10 @@
     </row>
     <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C4" s="2">
         <v>45094.33613355324</v>
@@ -2064,13 +2103,13 @@
         <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J4" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="K4">
         <v>187</v>
@@ -2094,7 +2133,7 @@
         <v>17.46666667</v>
       </c>
       <c r="V4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W4">
         <v>-0.076111</v>
@@ -2123,10 +2162,10 @@
     </row>
     <row r="5" spans="1:30">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C5" s="2">
         <v>45094.33632274305</v>
@@ -2144,13 +2183,13 @@
         <v>34</v>
       </c>
       <c r="H5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J5" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="K5">
         <v>90</v>
@@ -2174,7 +2213,7 @@
         <v>22.3</v>
       </c>
       <c r="V5" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W5">
         <v>0.161111</v>
@@ -2203,10 +2242,10 @@
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C6" s="2">
         <v>45094.3364802662</v>
@@ -2224,13 +2263,13 @@
         <v>49</v>
       </c>
       <c r="H6" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J6" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="K6">
         <v>93</v>
@@ -2254,7 +2293,7 @@
         <v>22.6</v>
       </c>
       <c r="V6" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W6">
         <v>0.01</v>
@@ -2283,10 +2322,10 @@
     </row>
     <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C7" s="2">
         <v>45094.33666510417</v>
@@ -2304,13 +2343,13 @@
         <v>64</v>
       </c>
       <c r="H7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J7" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="K7">
         <v>98</v>
@@ -2334,7 +2373,7 @@
         <v>22.63333333</v>
       </c>
       <c r="V7" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W7">
         <v>0.001111</v>
@@ -2363,10 +2402,10 @@
     </row>
     <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C8" s="2">
         <v>45094.33682725694</v>
@@ -2384,13 +2423,13 @@
         <v>79</v>
       </c>
       <c r="H8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J8" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="K8">
         <v>148</v>
@@ -2414,7 +2453,7 @@
         <v>22.73333333</v>
       </c>
       <c r="V8" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W8">
         <v>0.003333</v>
@@ -2443,10 +2482,10 @@
     </row>
     <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C9" s="2">
         <v>45094.33701878472</v>
@@ -2464,13 +2503,13 @@
         <v>94</v>
       </c>
       <c r="H9" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I9" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J9" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="K9">
         <v>165</v>
@@ -2494,7 +2533,7 @@
         <v>22.2</v>
       </c>
       <c r="V9" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W9">
         <v>-0.017778</v>
@@ -2523,10 +2562,10 @@
     </row>
     <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C10" s="2">
         <v>45094.33717542824</v>
@@ -2544,13 +2583,13 @@
         <v>109</v>
       </c>
       <c r="H10" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J10" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="K10">
         <v>275</v>
@@ -2574,7 +2613,7 @@
         <v>21.6</v>
       </c>
       <c r="V10" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W10">
         <v>-0.02</v>
@@ -2603,10 +2642,10 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C11" s="2">
         <v>45094.33736206019</v>
@@ -2624,13 +2663,13 @@
         <v>124</v>
       </c>
       <c r="H11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J11" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K11">
         <v>271</v>
@@ -2654,7 +2693,7 @@
         <v>22.53333333</v>
       </c>
       <c r="V11" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W11">
         <v>0.031111</v>
@@ -2683,10 +2722,10 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C12" s="2">
         <v>45094.33752214121</v>
@@ -2704,13 +2743,13 @@
         <v>139</v>
       </c>
       <c r="H12" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I12" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J12" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="K12">
         <v>66</v>
@@ -2734,7 +2773,7 @@
         <v>22.2</v>
       </c>
       <c r="V12" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W12">
         <v>-0.011111</v>
@@ -2763,10 +2802,10 @@
     </row>
     <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C13" s="2">
         <v>45094.33770380787</v>
@@ -2784,13 +2823,13 @@
         <v>154</v>
       </c>
       <c r="H13" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I13" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J13" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="K13">
         <v>198</v>
@@ -2814,7 +2853,7 @@
         <v>21.86666667</v>
       </c>
       <c r="V13" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W13">
         <v>-0.011111</v>
@@ -2843,10 +2882,10 @@
     </row>
     <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C14" s="2">
         <v>45094.33786939815</v>
@@ -2864,13 +2903,13 @@
         <v>169</v>
       </c>
       <c r="H14" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I14" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J14" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="K14">
         <v>144</v>
@@ -2894,7 +2933,7 @@
         <v>22.63333333</v>
       </c>
       <c r="V14" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W14">
         <v>0.025556</v>
@@ -2923,10 +2962,10 @@
     </row>
     <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C15" s="2">
         <v>45094.33805721065</v>
@@ -2944,13 +2983,13 @@
         <v>184</v>
       </c>
       <c r="H15" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I15" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J15" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="K15">
         <v>120</v>
@@ -2974,7 +3013,7 @@
         <v>23.5</v>
       </c>
       <c r="V15" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W15">
         <v>0.028889</v>
@@ -3003,10 +3042,10 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C16" s="2">
         <v>45094.33821681713</v>
@@ -3024,13 +3063,13 @@
         <v>199</v>
       </c>
       <c r="H16" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I16" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J16" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="K16">
         <v>261</v>
@@ -3054,7 +3093,7 @@
         <v>23.26666667</v>
       </c>
       <c r="V16" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W16">
         <v>-0.007778</v>
@@ -3083,10 +3122,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C17" s="2">
         <v>45094.33856372685</v>
@@ -3104,13 +3143,13 @@
         <v>229</v>
       </c>
       <c r="H17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I17" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J17" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="K17">
         <v>100</v>
@@ -3134,7 +3173,7 @@
         <v>22.56666667</v>
       </c>
       <c r="V17" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W17">
         <v>-0.023333</v>
@@ -3163,10 +3202,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C18" s="2">
         <v>45094.33891157407</v>
@@ -3184,13 +3223,13 @@
         <v>259</v>
       </c>
       <c r="H18" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I18" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J18" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="K18">
         <v>178</v>
@@ -3214,7 +3253,7 @@
         <v>22.03333333</v>
       </c>
       <c r="V18" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W18">
         <v>-0.017778</v>
@@ -3243,10 +3282,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C19" s="2">
         <v>45094.33909788194</v>
@@ -3264,13 +3303,13 @@
         <v>274</v>
       </c>
       <c r="H19" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I19" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J19" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K19">
         <v>164</v>
@@ -3294,7 +3333,7 @@
         <v>22.27777778</v>
       </c>
       <c r="V19" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W19">
         <v>0.002716</v>
@@ -3323,10 +3362,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C20" s="2">
         <v>45094.33960560185</v>
@@ -3344,13 +3383,13 @@
         <v>319</v>
       </c>
       <c r="H20" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I20" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J20" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="K20">
         <v>146</v>
@@ -3374,7 +3413,7 @@
         <v>22.61666667</v>
       </c>
       <c r="V20" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W20">
         <v>0.005648</v>
@@ -3403,10 +3442,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C21" s="2">
         <v>45094.33979266204</v>
@@ -3424,13 +3463,13 @@
         <v>334</v>
       </c>
       <c r="H21" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I21" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J21" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="K21">
         <v>147</v>
@@ -3454,7 +3493,7 @@
         <v>23.45</v>
       </c>
       <c r="V21" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W21">
         <v>0.013889</v>
@@ -3483,10 +3522,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C22" s="2">
         <v>45094.33995288194</v>
@@ -3504,13 +3543,13 @@
         <v>349</v>
       </c>
       <c r="H22" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I22" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J22" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="K22">
         <v>105</v>
@@ -3534,7 +3573,7 @@
         <v>22.96666667</v>
       </c>
       <c r="V22" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W22">
         <v>-0.016111</v>
@@ -3563,10 +3602,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C23" s="2">
         <v>45094.34029994213</v>
@@ -3584,13 +3623,13 @@
         <v>379</v>
       </c>
       <c r="H23" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I23" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J23" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="K23">
         <v>160</v>
@@ -3614,7 +3653,7 @@
         <v>22.23333333</v>
       </c>
       <c r="V23" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W23">
         <v>-0.024444</v>
@@ -3643,10 +3682,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C24" s="2">
         <v>45094.34049260417</v>
@@ -3664,13 +3703,13 @@
         <v>395</v>
       </c>
       <c r="H24" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I24" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J24" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K24">
         <v>114</v>
@@ -3694,7 +3733,7 @@
         <v>22.37704918</v>
       </c>
       <c r="V24" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W24">
         <v>0.002356</v>
@@ -3723,10 +3762,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C25" s="2">
         <v>45094.34064704861</v>
@@ -3744,13 +3783,13 @@
         <v>409</v>
       </c>
       <c r="H25" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I25" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J25" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="K25">
         <v>103</v>
@@ -3774,7 +3813,7 @@
         <v>23.7</v>
       </c>
       <c r="V25" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W25">
         <v>0.044098</v>
@@ -3803,10 +3842,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C26" s="2">
         <v>45094.34099342593</v>
@@ -3824,13 +3863,13 @@
         <v>439</v>
       </c>
       <c r="H26" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I26" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J26" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="K26">
         <v>121</v>
@@ -3854,7 +3893,7 @@
         <v>23.23333333</v>
       </c>
       <c r="V26" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W26">
         <v>-0.015556</v>
@@ -3883,10 +3922,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C27" s="2">
         <v>45094.34117866898</v>
@@ -3904,13 +3943,13 @@
         <v>454</v>
       </c>
       <c r="H27" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I27" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J27" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="K27">
         <v>118</v>
@@ -3934,7 +3973,7 @@
         <v>23.23728814</v>
       </c>
       <c r="V27" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W27">
         <v>6.7E-05</v>
@@ -3963,10 +4002,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C28" s="2">
         <v>45094.34168921296</v>
@@ -3984,13 +4023,13 @@
         <v>499</v>
       </c>
       <c r="H28" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I28" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J28" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="K28">
         <v>137</v>
@@ -4014,7 +4053,7 @@
         <v>23.18333333</v>
       </c>
       <c r="V28" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W28">
         <v>-0.000899</v>
@@ -4043,10 +4082,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C29" s="2">
         <v>45094.34203625</v>
@@ -4064,13 +4103,13 @@
         <v>529</v>
       </c>
       <c r="H29" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I29" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="J29" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="K29">
         <v>162</v>
@@ -4094,7 +4133,7 @@
         <v>24.1</v>
       </c>
       <c r="V29" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W29">
         <v>0.030556</v>
@@ -4123,10 +4162,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2">
         <v>45094.34222148148</v>
@@ -4144,13 +4183,13 @@
         <v>544</v>
       </c>
       <c r="H30" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I30" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="J30" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="K30">
         <v>119</v>
@@ -4174,7 +4213,7 @@
         <v>24.05555556</v>
       </c>
       <c r="V30" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W30">
         <v>-0.000494</v>
@@ -4203,10 +4242,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C31" s="2">
         <v>45094.34273024306</v>
@@ -4224,13 +4263,13 @@
         <v>589</v>
       </c>
       <c r="H31" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I31" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J31" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="K31">
         <v>155</v>
@@ -4254,7 +4293,7 @@
         <v>23.96666667</v>
       </c>
       <c r="V31" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W31">
         <v>-0.001481</v>
@@ -4283,10 +4322,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C32" s="2">
         <v>45094.34291811343</v>
@@ -4304,13 +4343,13 @@
         <v>604</v>
       </c>
       <c r="H32" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I32" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J32" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K32">
         <v>119</v>
@@ -4334,7 +4373,7 @@
         <v>23.78333333</v>
       </c>
       <c r="V32" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W32">
         <v>-0.003056</v>
@@ -4363,10 +4402,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C33" s="2">
         <v>45094.34411873842</v>
@@ -4384,13 +4423,13 @@
         <v>709</v>
       </c>
       <c r="H33" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I33" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J33" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="K33">
         <v>257</v>
@@ -4414,7 +4453,7 @@
         <v>23.725</v>
       </c>
       <c r="V33" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W33">
         <v>-0.000486</v>
@@ -4443,10 +4482,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C34" s="2">
         <v>45094.34446693287</v>
@@ -4464,13 +4503,13 @@
         <v>739</v>
       </c>
       <c r="H34" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I34" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J34" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="K34">
         <v>51</v>
@@ -4494,7 +4533,7 @@
         <v>23.6</v>
       </c>
       <c r="V34" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W34">
         <v>-0.004167</v>
@@ -4523,10 +4562,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C35" s="2">
         <v>45094.34481342592</v>
@@ -4544,13 +4583,13 @@
         <v>769</v>
       </c>
       <c r="H35" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I35" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J35" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="K35">
         <v>221</v>
@@ -4574,7 +4613,7 @@
         <v>23.2</v>
       </c>
       <c r="V35" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W35">
         <v>-0.013333</v>
@@ -4603,10 +4642,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C36" s="2">
         <v>45094.34550837963</v>
@@ -4624,13 +4663,13 @@
         <v>829</v>
       </c>
       <c r="H36" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I36" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J36" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="K36">
         <v>69</v>
@@ -4654,7 +4693,7 @@
         <v>23.8</v>
       </c>
       <c r="V36" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W36">
         <v>0.01</v>
@@ -4683,10 +4722,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C37" s="2">
         <v>45094.34585572917</v>
@@ -4704,13 +4743,13 @@
         <v>859</v>
       </c>
       <c r="H37" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I37" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J37" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K37">
         <v>133</v>
@@ -4734,7 +4773,7 @@
         <v>23.56666667</v>
       </c>
       <c r="V37" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W37">
         <v>-0.007778</v>
@@ -4763,10 +4802,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C38" s="2">
         <v>45094.34620280092</v>
@@ -4784,13 +4823,13 @@
         <v>889</v>
       </c>
       <c r="H38" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I38" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J38" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="K38">
         <v>161</v>
@@ -4814,7 +4853,7 @@
         <v>24.16666667</v>
       </c>
       <c r="V38" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W38">
         <v>0.02</v>
@@ -4843,10 +4882,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C39" s="2">
         <v>45094.34654929398</v>
@@ -4864,13 +4903,13 @@
         <v>919</v>
       </c>
       <c r="H39" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I39" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J39" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="K39">
         <v>132</v>
@@ -4894,7 +4933,7 @@
         <v>24.16666667</v>
       </c>
       <c r="V39" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W39">
         <v>0</v>
@@ -4923,10 +4962,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C40" s="2">
         <v>45094.34689672454</v>
@@ -4944,13 +4983,13 @@
         <v>949</v>
       </c>
       <c r="H40" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I40" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="J40" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="K40">
         <v>149</v>
@@ -4974,7 +5013,7 @@
         <v>24.26666667</v>
       </c>
       <c r="V40" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W40">
         <v>0.003333</v>
@@ -5003,10 +5042,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C41" s="2">
         <v>45094.34724454861</v>
@@ -5024,13 +5063,13 @@
         <v>979</v>
       </c>
       <c r="H41" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I41" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J41" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="K41">
         <v>188</v>
@@ -5054,7 +5093,7 @@
         <v>23.23333333</v>
       </c>
       <c r="V41" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W41">
         <v>-0.034444</v>
@@ -5083,10 +5122,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C42" s="2">
         <v>45094.3475916088</v>
@@ -5104,13 +5143,13 @@
         <v>1009</v>
       </c>
       <c r="H42" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I42" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J42" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="K42">
         <v>173</v>
@@ -5134,7 +5173,7 @@
         <v>25.06666667</v>
       </c>
       <c r="V42" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W42">
         <v>0.061111</v>
@@ -5163,10 +5202,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C43" s="2">
         <v>45094.34793854166</v>
@@ -5184,13 +5223,13 @@
         <v>1039</v>
       </c>
       <c r="H43" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I43" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="J43" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="K43">
         <v>115</v>
@@ -5214,7 +5253,7 @@
         <v>25.1</v>
       </c>
       <c r="V43" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W43">
         <v>0.001111</v>
@@ -5243,10 +5282,10 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C44" s="2">
         <v>45094.34863305555</v>
@@ -5264,13 +5303,13 @@
         <v>1099</v>
       </c>
       <c r="H44" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I44" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="J44" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="K44">
         <v>206</v>
@@ -5294,7 +5333,7 @@
         <v>25.01666667</v>
       </c>
       <c r="V44" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W44">
         <v>-0.001389</v>
@@ -5323,10 +5362,10 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C45" s="2">
         <v>45094.34882231482</v>
@@ -5344,13 +5383,13 @@
         <v>1114</v>
       </c>
       <c r="H45" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I45" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J45" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K45">
         <v>143</v>
@@ -5374,7 +5413,7 @@
         <v>24.10392157</v>
       </c>
       <c r="V45" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W45">
         <v>-0.00179</v>
@@ -5403,10 +5442,10 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C46" s="2">
         <v>45094.34897998843</v>
@@ -5424,13 +5463,13 @@
         <v>1129</v>
       </c>
       <c r="H46" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I46" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J46" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="K46">
         <v>187</v>
@@ -5454,7 +5493,7 @@
         <v>27.83333333</v>
       </c>
       <c r="V46" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W46">
         <v>0.124314</v>
@@ -5483,10 +5522,10 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C47" s="2">
         <v>45094.34932815973</v>
@@ -5504,13 +5543,13 @@
         <v>1159</v>
       </c>
       <c r="H47" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I47" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="J47" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="K47">
         <v>193</v>
@@ -5534,7 +5573,7 @@
         <v>26.53333333</v>
       </c>
       <c r="V47" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W47">
         <v>-0.043333</v>
@@ -5563,10 +5602,10 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C48" s="2">
         <v>45094.34967472222</v>
@@ -5584,13 +5623,13 @@
         <v>1189</v>
       </c>
       <c r="H48" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I48" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="J48" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="K48">
         <v>81</v>
@@ -5614,7 +5653,7 @@
         <v>27.5</v>
       </c>
       <c r="V48" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W48">
         <v>0.032222</v>
@@ -5643,10 +5682,10 @@
     </row>
     <row r="49" spans="1:30">
       <c r="A49" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C49" s="2">
         <v>45094.35036913194</v>
@@ -5664,13 +5703,13 @@
         <v>1249</v>
       </c>
       <c r="H49" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I49" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J49" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="K49">
         <v>147</v>
@@ -5694,7 +5733,7 @@
         <v>27.01666667</v>
       </c>
       <c r="V49" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W49">
         <v>-0.008056000000000001</v>
@@ -5723,10 +5762,10 @@
     </row>
     <row r="50" spans="1:30">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C50" s="2">
         <v>45094.35055534722</v>
@@ -5744,13 +5783,13 @@
         <v>1264</v>
       </c>
       <c r="H50" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I50" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J50" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="K50">
         <v>122</v>
@@ -5774,7 +5813,7 @@
         <v>27.36</v>
       </c>
       <c r="V50" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W50">
         <v>0.002289</v>
@@ -5803,10 +5842,10 @@
     </row>
     <row r="51" spans="1:30">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C51" s="2">
         <v>45094.35071625</v>
@@ -5824,13 +5863,13 @@
         <v>1279</v>
       </c>
       <c r="H51" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I51" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="J51" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="K51">
         <v>118</v>
@@ -5854,7 +5893,7 @@
         <v>26.93333333</v>
       </c>
       <c r="V51" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W51">
         <v>-0.014222</v>
@@ -5883,10 +5922,10 @@
     </row>
     <row r="52" spans="1:30">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C52" s="2">
         <v>45094.35106363426</v>
@@ -5904,13 +5943,13 @@
         <v>1309</v>
       </c>
       <c r="H52" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I52" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="J52" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="K52">
         <v>104</v>
@@ -5934,7 +5973,7 @@
         <v>27.56666667</v>
       </c>
       <c r="V52" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W52">
         <v>0.021111</v>
@@ -5963,10 +6002,10 @@
     </row>
     <row r="53" spans="1:30">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C53" s="2">
         <v>45094.35141146991</v>
@@ -5984,13 +6023,13 @@
         <v>1339</v>
       </c>
       <c r="H53" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I53" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="J53" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="K53">
         <v>121</v>
@@ -6014,7 +6053,7 @@
         <v>25.36666667</v>
       </c>
       <c r="V53" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W53">
         <v>-0.073333</v>
@@ -6043,10 +6082,10 @@
     </row>
     <row r="54" spans="1:30">
       <c r="A54" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B54" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C54" s="2">
         <v>45094.35175868055</v>
@@ -6064,13 +6103,13 @@
         <v>1369</v>
       </c>
       <c r="H54" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I54" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="J54" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="K54">
         <v>139</v>
@@ -6094,7 +6133,7 @@
         <v>26.66666667</v>
       </c>
       <c r="V54" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W54">
         <v>0.043333</v>
@@ -6123,10 +6162,10 @@
     </row>
     <row r="55" spans="1:30">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B55" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C55" s="2">
         <v>45094.35210487268</v>
@@ -6144,13 +6183,13 @@
         <v>1399</v>
       </c>
       <c r="H55" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I55" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J55" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="K55">
         <v>136</v>
@@ -6174,7 +6213,7 @@
         <v>26.06666667</v>
       </c>
       <c r="V55" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W55">
         <v>-0.02</v>
@@ -6203,10 +6242,10 @@
     </row>
     <row r="56" spans="1:30">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C56" s="2">
         <v>45094.35228836806</v>
@@ -6224,13 +6263,13 @@
         <v>1414</v>
       </c>
       <c r="H56" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I56" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J56" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="K56">
         <v>122</v>
@@ -6254,7 +6293,7 @@
         <v>26.55333333</v>
       </c>
       <c r="V56" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W56">
         <v>0.003244</v>
@@ -6283,10 +6322,10 @@
     </row>
     <row r="57" spans="1:30">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C57" s="2">
         <v>45094.35245263889</v>
@@ -6304,13 +6343,13 @@
         <v>1429</v>
       </c>
       <c r="H57" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I57" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="J57" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="K57">
         <v>118</v>
@@ -6334,7 +6373,7 @@
         <v>27.16666667</v>
       </c>
       <c r="V57" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W57">
         <v>0.020444</v>
@@ -6363,10 +6402,10 @@
     </row>
     <row r="58" spans="1:30">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C58" s="2">
         <v>45094.3527999537</v>
@@ -6384,13 +6423,13 @@
         <v>1459</v>
       </c>
       <c r="H58" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I58" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="J58" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="K58">
         <v>114</v>
@@ -6414,7 +6453,7 @@
         <v>27.73333333</v>
       </c>
       <c r="V58" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W58">
         <v>0.018889</v>
@@ -6443,10 +6482,10 @@
     </row>
     <row r="59" spans="1:30">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C59" s="2">
         <v>45094.35349449074</v>
@@ -6464,13 +6503,13 @@
         <v>1519</v>
       </c>
       <c r="H59" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I59" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J59" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="K59">
         <v>119</v>
@@ -6494,7 +6533,7 @@
         <v>29.13333333</v>
       </c>
       <c r="V59" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W59">
         <v>0.023333</v>
@@ -6523,10 +6562,10 @@
     </row>
     <row r="60" spans="1:30">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C60" s="2">
         <v>45094.35384116898</v>
@@ -6544,13 +6583,13 @@
         <v>1549</v>
       </c>
       <c r="H60" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I60" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J60" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="K60">
         <v>114</v>
@@ -6574,7 +6613,7 @@
         <v>27.63333333</v>
       </c>
       <c r="V60" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W60">
         <v>-0.05</v>
@@ -6603,10 +6642,10 @@
     </row>
     <row r="61" spans="1:30">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C61" s="2">
         <v>45094.35418881944</v>
@@ -6624,13 +6663,13 @@
         <v>1579</v>
       </c>
       <c r="H61" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I61" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="J61" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="K61">
         <v>124</v>
@@ -6654,7 +6693,7 @@
         <v>28.23333333</v>
       </c>
       <c r="V61" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W61">
         <v>0.02</v>
@@ -6683,10 +6722,10 @@
     </row>
     <row r="62" spans="1:30">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C62" s="2">
         <v>45094.35453560185</v>
@@ -6704,13 +6743,13 @@
         <v>1609</v>
       </c>
       <c r="H62" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I62" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J62" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="K62">
         <v>117</v>
@@ -6734,7 +6773,7 @@
         <v>30.7</v>
       </c>
       <c r="V62" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W62">
         <v>0.082222</v>
@@ -6763,10 +6802,10 @@
     </row>
     <row r="63" spans="1:30">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C63" s="2">
         <v>45094.35472105324</v>
@@ -6784,13 +6823,13 @@
         <v>1624</v>
       </c>
       <c r="H63" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I63" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="J63" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="K63">
         <v>123</v>
@@ -6814,7 +6853,7 @@
         <v>28.52380952</v>
       </c>
       <c r="V63" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W63">
         <v>-0.010363</v>
@@ -6843,10 +6882,10 @@
     </row>
     <row r="64" spans="1:30">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B64" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C64" s="2">
         <v>45094.35488359954</v>
@@ -6864,13 +6903,13 @@
         <v>1639</v>
       </c>
       <c r="H64" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I64" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J64" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="K64">
         <v>119</v>
@@ -6894,7 +6933,7 @@
         <v>28.26666667</v>
       </c>
       <c r="V64" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W64">
         <v>-0.008571</v>
@@ -6923,10 +6962,10 @@
     </row>
     <row r="65" spans="1:30">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C65" s="2">
         <v>45094.35523041667</v>
@@ -6944,13 +6983,13 @@
         <v>1669</v>
       </c>
       <c r="H65" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I65" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="J65" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K65">
         <v>121</v>
@@ -6974,7 +7013,7 @@
         <v>28.43333333</v>
       </c>
       <c r="V65" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W65">
         <v>0.005556</v>
@@ -7003,10 +7042,10 @@
     </row>
     <row r="66" spans="1:30">
       <c r="A66" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C66" s="2">
         <v>45094.35557736111</v>
@@ -7024,13 +7063,13 @@
         <v>1699</v>
       </c>
       <c r="H66" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I66" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J66" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="K66">
         <v>119</v>
@@ -7054,7 +7093,7 @@
         <v>29.56666667</v>
       </c>
       <c r="V66" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W66">
         <v>0.037778</v>
@@ -7083,10 +7122,10 @@
     </row>
     <row r="67" spans="1:30">
       <c r="A67" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C67" s="2">
         <v>45094.35592439815</v>
@@ -7104,13 +7143,13 @@
         <v>1729</v>
       </c>
       <c r="H67" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I67" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="J67" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="K67">
         <v>115</v>
@@ -7134,7 +7173,7 @@
         <v>27.96666667</v>
       </c>
       <c r="V67" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W67">
         <v>-0.053333</v>
@@ -7163,10 +7202,10 @@
     </row>
     <row r="68" spans="1:30">
       <c r="A68" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C68" s="2">
         <v>45094.35627298611</v>
@@ -7184,13 +7223,13 @@
         <v>1759</v>
       </c>
       <c r="H68" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I68" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J68" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="K68">
         <v>120</v>
@@ -7214,7 +7253,7 @@
         <v>31.6</v>
       </c>
       <c r="V68" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W68">
         <v>0.121111</v>
@@ -7243,10 +7282,10 @@
     </row>
     <row r="69" spans="1:30">
       <c r="A69" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C69" s="2">
         <v>45094.35661945602</v>
@@ -7264,13 +7303,13 @@
         <v>1789</v>
       </c>
       <c r="H69" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I69" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="J69" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="K69">
         <v>116</v>
@@ -7294,7 +7333,7 @@
         <v>34.36666667</v>
       </c>
       <c r="V69" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W69">
         <v>0.092222</v>
@@ -7323,10 +7362,10 @@
     </row>
     <row r="70" spans="1:30">
       <c r="A70" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B70" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C70" s="2">
         <v>45094.3569668287</v>
@@ -7344,13 +7383,13 @@
         <v>1819</v>
       </c>
       <c r="H70" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I70" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="J70" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K70">
         <v>116</v>
@@ -7374,7 +7413,7 @@
         <v>30.46666667</v>
       </c>
       <c r="V70" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W70">
         <v>-0.13</v>
@@ -7403,10 +7442,10 @@
     </row>
     <row r="71" spans="1:30">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B71" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C71" s="2">
         <v>45094.35731451389</v>
@@ -7424,13 +7463,13 @@
         <v>1849</v>
       </c>
       <c r="H71" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I71" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="J71" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="K71">
         <v>125</v>
@@ -7454,7 +7493,7 @@
         <v>20.53333333</v>
       </c>
       <c r="V71" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W71">
         <v>-0.331111</v>
@@ -7483,10 +7522,10 @@
     </row>
     <row r="72" spans="1:30">
       <c r="A72" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C72" s="2">
         <v>45094.3580084375</v>
@@ -7504,13 +7543,13 @@
         <v>1909</v>
       </c>
       <c r="H72" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I72" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="J72" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="K72">
         <v>112</v>
@@ -7534,7 +7573,7 @@
         <v>31.93333333</v>
       </c>
       <c r="V72" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W72">
         <v>0.19</v>
@@ -7563,10 +7602,10 @@
     </row>
     <row r="73" spans="1:30">
       <c r="A73" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B73" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C73" s="2">
         <v>45094.35835541667</v>
@@ -7584,13 +7623,13 @@
         <v>1939</v>
       </c>
       <c r="H73" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I73" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="J73" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K73">
         <v>97</v>
@@ -7614,7 +7653,7 @@
         <v>32.63333333</v>
       </c>
       <c r="V73" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W73">
         <v>0.023333</v>
@@ -7643,10 +7682,10 @@
     </row>
     <row r="74" spans="1:30">
       <c r="A74" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B74" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C74" s="2">
         <v>45094.35870262732</v>
@@ -7664,13 +7703,13 @@
         <v>1969</v>
       </c>
       <c r="H74" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I74" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="J74" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K74">
         <v>102</v>
@@ -7694,7 +7733,7 @@
         <v>25.8</v>
       </c>
       <c r="V74" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W74">
         <v>-0.227778</v>
@@ -7723,10 +7762,10 @@
     </row>
     <row r="75" spans="1:30">
       <c r="A75" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B75" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C75" s="2">
         <v>45094.35904986111</v>
@@ -7744,13 +7783,13 @@
         <v>1999</v>
       </c>
       <c r="H75" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I75" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="J75" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="K75">
         <v>111</v>
@@ -7774,7 +7813,7 @@
         <v>23.46666667</v>
       </c>
       <c r="V75" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W75">
         <v>-0.077778</v>
@@ -7803,10 +7842,10 @@
     </row>
     <row r="76" spans="1:30">
       <c r="A76" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B76" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C76" s="2">
         <v>45094.35939660879</v>
@@ -7824,13 +7863,13 @@
         <v>2029</v>
       </c>
       <c r="H76" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I76" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J76" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="K76">
         <v>114</v>
@@ -7854,7 +7893,7 @@
         <v>26.86666667</v>
       </c>
       <c r="V76" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W76">
         <v>0.113333</v>
@@ -7883,10 +7922,10 @@
     </row>
     <row r="77" spans="1:30">
       <c r="A77" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C77" s="2">
         <v>45094.35974424768</v>
@@ -7904,13 +7943,13 @@
         <v>2059</v>
       </c>
       <c r="H77" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I77" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="J77" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K77">
         <v>156</v>
@@ -7934,7 +7973,7 @@
         <v>28.2</v>
       </c>
       <c r="V77" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W77">
         <v>0.044444</v>
@@ -7963,10 +8002,10 @@
     </row>
     <row r="78" spans="1:30">
       <c r="A78" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B78" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C78" s="2">
         <v>45094.36043918981</v>
@@ -7984,13 +8023,13 @@
         <v>2119</v>
       </c>
       <c r="H78" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I78" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="J78" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="K78">
         <v>154</v>
@@ -8014,7 +8053,7 @@
         <v>31.26666667</v>
       </c>
       <c r="V78" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W78">
         <v>0.051111</v>
@@ -8043,10 +8082,10 @@
     </row>
     <row r="79" spans="1:30">
       <c r="A79" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B79" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C79" s="2">
         <v>45094.36078555555</v>
@@ -8064,13 +8103,13 @@
         <v>2149</v>
       </c>
       <c r="H79" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I79" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="J79" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="K79">
         <v>49</v>
@@ -8094,7 +8133,7 @@
         <v>38.76666667</v>
       </c>
       <c r="V79" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W79">
         <v>0.25</v>
@@ -8123,10 +8162,10 @@
     </row>
     <row r="80" spans="1:30">
       <c r="A80" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B80" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C80" s="2">
         <v>45094.36113313658</v>
@@ -8144,13 +8183,13 @@
         <v>2179</v>
       </c>
       <c r="H80" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I80" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J80" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="K80">
         <v>82</v>
@@ -8174,7 +8213,7 @@
         <v>22.5</v>
       </c>
       <c r="V80" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W80">
         <v>-0.542222</v>
@@ -8203,10 +8242,10 @@
     </row>
     <row r="81" spans="1:30">
       <c r="A81" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B81" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C81" s="2">
         <v>45094.36148015047</v>
@@ -8224,13 +8263,13 @@
         <v>2209</v>
       </c>
       <c r="H81" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I81" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="J81" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="K81">
         <v>38</v>
@@ -8254,7 +8293,7 @@
         <v>29.73333333</v>
       </c>
       <c r="V81" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W81">
         <v>0.241111</v>
@@ -8283,10 +8322,10 @@
     </row>
     <row r="82" spans="1:30">
       <c r="A82" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B82" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C82" s="2">
         <v>45094.36182846065</v>
@@ -8304,13 +8343,13 @@
         <v>2239</v>
       </c>
       <c r="H82" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I82" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="J82" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="K82">
         <v>115</v>
@@ -8334,7 +8373,7 @@
         <v>24.7</v>
       </c>
       <c r="V82" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W82">
         <v>-0.167778</v>
@@ -8363,10 +8402,10 @@
     </row>
     <row r="83" spans="1:30">
       <c r="A83" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B83" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C83" s="2">
         <v>45094.36217550926</v>
@@ -8384,13 +8423,13 @@
         <v>2269</v>
       </c>
       <c r="H83" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I83" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="J83" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="K83">
         <v>153</v>
@@ -8414,7 +8453,7 @@
         <v>28.5</v>
       </c>
       <c r="V83" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="W83">
         <v>0.126667</v>
@@ -8443,10 +8482,10 @@
     </row>
     <row r="84" spans="1:30">
       <c r="A84" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B84" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C84" s="2">
         <v>45094.36252275463</v>
@@ -8464,13 +8503,13 @@
         <v>2299</v>
       </c>
       <c r="H84" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I84" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="J84" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="K84">
         <v>81</v>
@@ -8494,7 +8533,7 @@
         <v>28.83333333</v>
       </c>
       <c r="V84" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W84">
         <v>0.011111</v>
@@ -8523,10 +8562,10 @@
     </row>
     <row r="85" spans="1:30">
       <c r="A85" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B85" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C85" s="2">
         <v>45094.3628693287</v>
@@ -8544,13 +8583,13 @@
         <v>2329</v>
       </c>
       <c r="H85" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I85" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="J85" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="K85">
         <v>149</v>
@@ -8574,7 +8613,7 @@
         <v>23.53333333</v>
       </c>
       <c r="V85" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W85">
         <v>-0.176667</v>
@@ -8603,10 +8642,10 @@
     </row>
     <row r="86" spans="1:30">
       <c r="A86" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B86" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C86" s="2">
         <v>45094.36321664352</v>
@@ -8624,13 +8663,13 @@
         <v>2359</v>
       </c>
       <c r="H86" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I86" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J86" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="K86">
         <v>119</v>
@@ -8654,7 +8693,7 @@
         <v>24.53333333</v>
       </c>
       <c r="V86" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W86">
         <v>0.033333</v>
@@ -8683,10 +8722,10 @@
     </row>
     <row r="87" spans="1:30">
       <c r="A87" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B87" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C87" s="2">
         <v>45094.36356399306</v>
@@ -8704,13 +8743,13 @@
         <v>2389</v>
       </c>
       <c r="H87" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I87" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J87" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="K87">
         <v>175</v>
@@ -8734,7 +8773,7 @@
         <v>23.6</v>
       </c>
       <c r="V87" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W87">
         <v>-0.031111</v>
@@ -8763,10 +8802,10 @@
     </row>
     <row r="88" spans="1:30">
       <c r="A88" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B88" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C88" s="2">
         <v>45094.36391078704</v>
@@ -8784,13 +8823,13 @@
         <v>2419</v>
       </c>
       <c r="H88" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I88" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="J88" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="K88">
         <v>345</v>
@@ -8814,7 +8853,7 @@
         <v>22.86666667</v>
       </c>
       <c r="V88" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W88">
         <v>-0.024444</v>
@@ -8843,10 +8882,10 @@
     </row>
     <row r="89" spans="1:30">
       <c r="A89" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B89" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C89" s="2">
         <v>45094.36425849537</v>
@@ -8864,13 +8903,13 @@
         <v>2449</v>
       </c>
       <c r="H89" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I89" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="J89" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K89">
         <v>109</v>
@@ -8894,7 +8933,7 @@
         <v>21.7</v>
       </c>
       <c r="V89" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W89">
         <v>-0.038889</v>
@@ -8923,10 +8962,10 @@
     </row>
     <row r="90" spans="1:30">
       <c r="A90" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B90" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C90" s="2">
         <v>45094.36460600694</v>
@@ -8944,13 +8983,13 @@
         <v>2479</v>
       </c>
       <c r="H90" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I90" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="J90" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="K90">
         <v>70</v>
@@ -8974,7 +9013,7 @@
         <v>21.5</v>
       </c>
       <c r="V90" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W90">
         <v>-0.006667</v>
@@ -9003,10 +9042,10 @@
     </row>
     <row r="91" spans="1:30">
       <c r="A91" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B91" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C91" s="2">
         <v>45094.365646875</v>
@@ -9024,13 +9063,13 @@
         <v>2569</v>
       </c>
       <c r="H91" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I91" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="J91" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="K91">
         <v>190</v>
@@ -9054,7 +9093,7 @@
         <v>27.68888889</v>
       </c>
       <c r="V91" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W91">
         <v>0.06876500000000001</v>
@@ -9083,10 +9122,10 @@
     </row>
     <row r="92" spans="1:30">
       <c r="A92" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B92" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C92" s="2">
         <v>45094.36599543982</v>
@@ -9104,13 +9143,13 @@
         <v>2599</v>
       </c>
       <c r="H92" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I92" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="J92" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="K92">
         <v>280</v>
@@ -9134,7 +9173,7 @@
         <v>24.63333333</v>
       </c>
       <c r="V92" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W92">
         <v>-0.101852</v>
@@ -9163,10 +9202,10 @@
     </row>
     <row r="93" spans="1:30">
       <c r="A93" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B93" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C93" s="2">
         <v>45094.36634144676</v>
@@ -9184,13 +9223,13 @@
         <v>2629</v>
       </c>
       <c r="H93" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I93" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="J93" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="K93">
         <v>278</v>
@@ -9214,7 +9253,7 @@
         <v>25</v>
       </c>
       <c r="V93" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W93">
         <v>0.012222</v>
@@ -9243,10 +9282,10 @@
     </row>
     <row r="94" spans="1:30">
       <c r="A94" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B94" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C94" s="2">
         <v>45094.36668912037</v>
@@ -9264,13 +9303,13 @@
         <v>2659</v>
       </c>
       <c r="H94" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I94" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="J94" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="K94">
         <v>291</v>
@@ -9294,7 +9333,7 @@
         <v>24.86666667</v>
       </c>
       <c r="V94" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W94">
         <v>-0.004444</v>
@@ -9323,10 +9362,10 @@
     </row>
     <row r="95" spans="1:30">
       <c r="A95" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B95" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C95" s="2">
         <v>45094.36703568287</v>
@@ -9344,13 +9383,13 @@
         <v>2689</v>
       </c>
       <c r="H95" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I95" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="J95" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K95">
         <v>210</v>
@@ -9374,7 +9413,7 @@
         <v>24.23333333</v>
       </c>
       <c r="V95" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W95">
         <v>-0.021111</v>
@@ -9403,10 +9442,10 @@
     </row>
     <row r="96" spans="1:30">
       <c r="A96" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B96" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C96" s="2">
         <v>45094.36738269676</v>
@@ -9424,13 +9463,13 @@
         <v>2719</v>
       </c>
       <c r="H96" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I96" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J96" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="K96">
         <v>311</v>
@@ -9454,7 +9493,7 @@
         <v>24.6</v>
       </c>
       <c r="V96" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W96">
         <v>0.012222</v>
@@ -9483,10 +9522,10 @@
     </row>
     <row r="97" spans="1:30">
       <c r="A97" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B97" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C97" s="2">
         <v>45094.36773050926</v>
@@ -9504,13 +9543,13 @@
         <v>2749</v>
       </c>
       <c r="H97" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I97" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="J97" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="K97">
         <v>250</v>
@@ -9534,7 +9573,7 @@
         <v>22.43333333</v>
       </c>
       <c r="V97" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W97">
         <v>-0.07222199999999999</v>
@@ -9563,10 +9602,10 @@
     </row>
     <row r="98" spans="1:30">
       <c r="A98" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B98" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C98" s="2">
         <v>45094.36807675926</v>
@@ -9584,13 +9623,13 @@
         <v>2779</v>
       </c>
       <c r="H98" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I98" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="J98" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K98">
         <v>260</v>
@@ -9614,7 +9653,7 @@
         <v>22.63333333</v>
       </c>
       <c r="V98" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W98">
         <v>0.006667</v>
@@ -9643,10 +9682,10 @@
     </row>
     <row r="99" spans="1:30">
       <c r="A99" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B99" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C99" s="2">
         <v>45094.36877180556</v>
@@ -9664,13 +9703,13 @@
         <v>2839</v>
       </c>
       <c r="H99" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I99" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J99" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="K99">
         <v>248</v>
@@ -9694,7 +9733,7 @@
         <v>24.65</v>
       </c>
       <c r="V99" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W99">
         <v>0.033611</v>
@@ -9723,10 +9762,10 @@
     </row>
     <row r="100" spans="1:30">
       <c r="A100" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C100" s="2">
         <v>45094.36946652778</v>
@@ -9744,13 +9783,13 @@
         <v>2899</v>
       </c>
       <c r="H100" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I100" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="J100" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K100">
         <v>290</v>
@@ -9774,7 +9813,7 @@
         <v>22.41666667</v>
       </c>
       <c r="V100" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W100">
         <v>-0.037222</v>
@@ -9803,10 +9842,10 @@
     </row>
     <row r="101" spans="1:30">
       <c r="A101" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B101" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C101" s="2">
         <v>45094.36981353009</v>
@@ -9824,13 +9863,13 @@
         <v>2929</v>
       </c>
       <c r="H101" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I101" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J101" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="K101">
         <v>289</v>
@@ -9854,7 +9893,7 @@
         <v>24.73333333</v>
       </c>
       <c r="V101" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W101">
         <v>0.077222</v>
@@ -9883,10 +9922,10 @@
     </row>
     <row r="102" spans="1:30">
       <c r="A102" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B102" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C102" s="2">
         <v>45094.37016189815</v>
@@ -9904,13 +9943,13 @@
         <v>2959</v>
       </c>
       <c r="H102" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I102" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="J102" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="K102">
         <v>295</v>
@@ -9934,7 +9973,7 @@
         <v>23.76666667</v>
       </c>
       <c r="V102" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W102">
         <v>-0.032222</v>
@@ -9963,10 +10002,10 @@
     </row>
     <row r="103" spans="1:30">
       <c r="A103" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B103" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C103" s="2">
         <v>45094.37050813658</v>
@@ -9984,13 +10023,13 @@
         <v>2989</v>
       </c>
       <c r="H103" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I103" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="J103" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="K103">
         <v>276</v>
@@ -10014,7 +10053,7 @@
         <v>24.23333333</v>
       </c>
       <c r="V103" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W103">
         <v>0.015556</v>
@@ -10043,10 +10082,10 @@
     </row>
     <row r="104" spans="1:30">
       <c r="A104" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B104" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C104" s="2">
         <v>45094.37085590278</v>
@@ -10064,13 +10103,13 @@
         <v>3019</v>
       </c>
       <c r="H104" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I104" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="J104" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="K104">
         <v>328</v>
@@ -10094,7 +10133,7 @@
         <v>24.46666667</v>
       </c>
       <c r="V104" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W104">
         <v>0.007778</v>
@@ -10123,10 +10162,10 @@
     </row>
     <row r="105" spans="1:30">
       <c r="A105" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B105" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C105" s="2">
         <v>45094.37120224537</v>
@@ -10144,13 +10183,13 @@
         <v>3049</v>
       </c>
       <c r="H105" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I105" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="J105" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="K105">
         <v>311</v>
@@ -10174,7 +10213,7 @@
         <v>23.73333333</v>
       </c>
       <c r="V105" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="W105">
         <v>-0.024444</v>
@@ -10213,102 +10252,102 @@
   <sheetData>
     <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:30">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C2" s="2">
         <v>45094.37155011574</v>
@@ -10326,13 +10365,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="J2" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="K2">
         <v>318</v>
@@ -10356,7 +10395,7 @@
         <v>-33.13333333</v>
       </c>
       <c r="V2" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="X2">
         <v>-33.133333</v>
@@ -10367,10 +10406,10 @@
     </row>
     <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C3" s="2">
         <v>45094.37189753472</v>
@@ -10388,13 +10427,13 @@
         <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I3" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="J3" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="K3">
         <v>297</v>
@@ -10418,7 +10457,7 @@
         <v>-51.76666667</v>
       </c>
       <c r="V3" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W3">
         <v>-0.621111</v>
@@ -10441,10 +10480,10 @@
     </row>
     <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C4" s="2">
         <v>45094.37259148148</v>
@@ -10462,13 +10501,13 @@
         <v>90</v>
       </c>
       <c r="H4" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I4" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="J4" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="K4">
         <v>272</v>
@@ -10492,7 +10531,7 @@
         <v>-45.38333333</v>
       </c>
       <c r="V4" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W4">
         <v>0.106389</v>
@@ -10521,10 +10560,10 @@
     </row>
     <row r="5" spans="1:30">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C5" s="2">
         <v>45094.37328638889</v>
@@ -10542,13 +10581,13 @@
         <v>150</v>
       </c>
       <c r="H5" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I5" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="J5" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="K5">
         <v>280</v>
@@ -10572,7 +10611,7 @@
         <v>-41.38333333</v>
       </c>
       <c r="V5" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W5">
         <v>0.066667</v>
@@ -10601,10 +10640,10 @@
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C6" s="2">
         <v>45094.37363313657</v>
@@ -10622,13 +10661,13 @@
         <v>180</v>
       </c>
       <c r="H6" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I6" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="J6" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="K6">
         <v>235</v>
@@ -10652,7 +10691,7 @@
         <v>-43.8</v>
       </c>
       <c r="V6" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W6">
         <v>-0.080556</v>
@@ -10681,10 +10720,10 @@
     </row>
     <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C7" s="2">
         <v>45094.37398188657</v>
@@ -10702,13 +10741,13 @@
         <v>210</v>
       </c>
       <c r="H7" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I7" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="J7" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="K7">
         <v>238</v>
@@ -10732,7 +10771,7 @@
         <v>-36.96666667</v>
       </c>
       <c r="V7" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W7">
         <v>0.227778</v>
@@ -10761,10 +10800,10 @@
     </row>
     <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C8" s="2">
         <v>45094.37467542824</v>
@@ -10782,13 +10821,13 @@
         <v>270</v>
       </c>
       <c r="H8" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I8" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="J8" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="K8">
         <v>194</v>
@@ -10812,7 +10851,7 @@
         <v>-40.2</v>
       </c>
       <c r="V8" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W8">
         <v>-0.053889</v>
@@ -10841,10 +10880,10 @@
     </row>
     <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C9" s="2">
         <v>45094.37502232639</v>
@@ -10862,13 +10901,13 @@
         <v>300</v>
       </c>
       <c r="H9" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I9" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J9" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="K9">
         <v>140</v>
@@ -10892,7 +10931,7 @@
         <v>-38.36666667</v>
       </c>
       <c r="V9" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W9">
         <v>0.061111</v>
@@ -10921,10 +10960,10 @@
     </row>
     <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C10" s="2">
         <v>45094.37536953704</v>
@@ -10942,13 +10981,13 @@
         <v>330</v>
       </c>
       <c r="H10" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I10" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="J10" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="K10">
         <v>30</v>
@@ -10972,7 +11011,7 @@
         <v>-32.26666667</v>
       </c>
       <c r="V10" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W10">
         <v>0.203333</v>
@@ -11001,10 +11040,10 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C11" s="2">
         <v>45094.37571655092</v>
@@ -11022,13 +11061,13 @@
         <v>360</v>
       </c>
       <c r="H11" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I11" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="J11" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="K11">
         <v>174</v>
@@ -11052,7 +11091,7 @@
         <v>-35.63333333</v>
       </c>
       <c r="V11" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W11">
         <v>-0.112222</v>
@@ -11081,10 +11120,10 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C12" s="2">
         <v>45094.37606354167</v>
@@ -11102,13 +11141,13 @@
         <v>390</v>
       </c>
       <c r="H12" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I12" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="J12" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="K12">
         <v>25</v>
@@ -11132,7 +11171,7 @@
         <v>-33.16666667</v>
       </c>
       <c r="V12" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W12">
         <v>0.082222</v>
@@ -11161,10 +11200,10 @@
     </row>
     <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C13" s="2">
         <v>45094.37641184028</v>
@@ -11182,13 +11221,13 @@
         <v>420</v>
       </c>
       <c r="H13" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I13" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="J13" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="K13">
         <v>39</v>
@@ -11212,7 +11251,7 @@
         <v>-30.96666667</v>
       </c>
       <c r="V13" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W13">
         <v>0.073333</v>
@@ -11241,10 +11280,10 @@
     </row>
     <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C14" s="2">
         <v>45094.37675826389</v>
@@ -11262,13 +11301,13 @@
         <v>450</v>
       </c>
       <c r="H14" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I14" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="J14" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="K14">
         <v>66</v>
@@ -11292,7 +11331,7 @@
         <v>-28.46666667</v>
       </c>
       <c r="V14" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W14">
         <v>0.083333</v>
@@ -11321,10 +11360,10 @@
     </row>
     <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C15" s="2">
         <v>45094.3771059838</v>
@@ -11342,13 +11381,13 @@
         <v>480</v>
       </c>
       <c r="H15" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I15" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J15" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="K15">
         <v>94</v>
@@ -11372,7 +11411,7 @@
         <v>-31.83333333</v>
       </c>
       <c r="V15" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W15">
         <v>-0.112222</v>
@@ -11401,10 +11440,10 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C16" s="2">
         <v>45094.37745237268</v>
@@ -11422,13 +11461,13 @@
         <v>510</v>
       </c>
       <c r="H16" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I16" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="J16" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="K16">
         <v>82</v>
@@ -11452,7 +11491,7 @@
         <v>-34.53333333</v>
       </c>
       <c r="V16" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W16">
         <v>-0.09</v>
@@ -11481,10 +11520,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C17" s="2">
         <v>45094.37918865741</v>
@@ -11502,13 +11541,13 @@
         <v>660</v>
       </c>
       <c r="H17" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I17" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="J17" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="K17">
         <v>131</v>
@@ -11532,7 +11571,7 @@
         <v>-33.04</v>
       </c>
       <c r="V17" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W17">
         <v>0.009956</v>
@@ -11561,10 +11600,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C18" s="2">
         <v>45094.37953603009</v>
@@ -11582,13 +11621,13 @@
         <v>690</v>
       </c>
       <c r="H18" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I18" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="J18" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="K18">
         <v>121</v>
@@ -11612,7 +11651,7 @@
         <v>-29.96666667</v>
       </c>
       <c r="V18" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W18">
         <v>0.102444</v>
@@ -11641,10 +11680,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C19" s="2">
         <v>45094.3798837963</v>
@@ -11662,13 +11701,13 @@
         <v>720</v>
       </c>
       <c r="H19" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I19" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="J19" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="K19">
         <v>97</v>
@@ -11692,7 +11731,7 @@
         <v>-29.46666667</v>
       </c>
       <c r="V19" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W19">
         <v>0.016667</v>
@@ -11721,10 +11760,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C20" s="2">
         <v>45094.38057789352</v>
@@ -11742,13 +11781,13 @@
         <v>780</v>
       </c>
       <c r="H20" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I20" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="J20" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="K20">
         <v>114</v>
@@ -11772,7 +11811,7 @@
         <v>-28.15</v>
       </c>
       <c r="V20" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W20">
         <v>0.021944</v>
@@ -11801,10 +11840,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C21" s="2">
         <v>45094.38092582176</v>
@@ -11822,13 +11861,13 @@
         <v>810</v>
       </c>
       <c r="H21" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I21" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="J21" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="K21">
         <v>122</v>
@@ -11852,7 +11891,7 @@
         <v>-27.5</v>
       </c>
       <c r="V21" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W21">
         <v>0.021667</v>
@@ -11881,10 +11920,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C22" s="2">
         <v>45094.38148519676</v>
@@ -11902,13 +11941,13 @@
         <v>840</v>
       </c>
       <c r="H22" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I22" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="J22" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="K22">
         <v>124</v>
@@ -11932,7 +11971,7 @@
         <v>-26.06666667</v>
       </c>
       <c r="V22" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W22">
         <v>0.047778</v>
@@ -11961,10 +12000,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C23" s="2">
         <v>45094.3816187037</v>
@@ -11982,13 +12021,13 @@
         <v>870</v>
       </c>
       <c r="H23" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I23" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="J23" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="K23">
         <v>123</v>
@@ -12012,7 +12051,7 @@
         <v>-25.4</v>
       </c>
       <c r="V23" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W23">
         <v>0.022222</v>
@@ -12041,10 +12080,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C24" s="2">
         <v>45094.38196700231</v>
@@ -12062,13 +12101,13 @@
         <v>900</v>
       </c>
       <c r="H24" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I24" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="J24" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="K24">
         <v>114</v>
@@ -12092,7 +12131,7 @@
         <v>-21.96666667</v>
       </c>
       <c r="V24" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W24">
         <v>0.114444</v>
@@ -12121,10 +12160,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C25" s="2">
         <v>45094.38231439815</v>
@@ -12142,13 +12181,13 @@
         <v>930</v>
       </c>
       <c r="H25" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I25" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="J25" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="K25">
         <v>115</v>
@@ -12172,7 +12211,7 @@
         <v>-23.2</v>
       </c>
       <c r="V25" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W25">
         <v>-0.041111</v>
@@ -12201,10 +12240,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C26" s="2">
         <v>45094.38300857639</v>
@@ -12222,13 +12261,13 @@
         <v>990</v>
       </c>
       <c r="H26" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I26" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="J26" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="K26">
         <v>121</v>
@@ -12252,7 +12291,7 @@
         <v>-22.96666667</v>
       </c>
       <c r="V26" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W26">
         <v>0.003889</v>
@@ -12281,10 +12320,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C27" s="2">
         <v>45094.38335523148</v>
@@ -12302,13 +12341,13 @@
         <v>1020</v>
       </c>
       <c r="H27" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I27" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="J27" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="K27">
         <v>115</v>
@@ -12332,7 +12371,7 @@
         <v>-22.63333333</v>
       </c>
       <c r="V27" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W27">
         <v>0.011111</v>
@@ -12361,10 +12400,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C28" s="2">
         <v>45094.38370341435</v>
@@ -12382,13 +12421,13 @@
         <v>1050</v>
       </c>
       <c r="H28" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I28" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="J28" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="K28">
         <v>120</v>
@@ -12412,7 +12451,7 @@
         <v>-21.66666667</v>
       </c>
       <c r="V28" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W28">
         <v>0.032222</v>
@@ -12441,10 +12480,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C29" s="2">
         <v>45094.38405054398</v>
@@ -12462,13 +12501,13 @@
         <v>1080</v>
       </c>
       <c r="H29" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I29" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="J29" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="K29">
         <v>120</v>
@@ -12492,7 +12531,7 @@
         <v>-21.6</v>
       </c>
       <c r="V29" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W29">
         <v>0.002222</v>
@@ -12521,10 +12560,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C30" s="2">
         <v>45094.38439748843</v>
@@ -12542,13 +12581,13 @@
         <v>1110</v>
       </c>
       <c r="H30" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I30" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="J30" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="K30">
         <v>116</v>
@@ -12572,7 +12611,7 @@
         <v>-21.26666667</v>
       </c>
       <c r="V30" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W30">
         <v>0.011111</v>
@@ -12601,10 +12640,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C31" s="2">
         <v>45094.38474394676</v>
@@ -12622,13 +12661,13 @@
         <v>1140</v>
       </c>
       <c r="H31" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I31" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="J31" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="K31">
         <v>118</v>
@@ -12652,7 +12691,7 @@
         <v>-21</v>
       </c>
       <c r="V31" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W31">
         <v>0.008888999999999999</v>
@@ -12681,10 +12720,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C32" s="2">
         <v>45094.38543905093</v>
@@ -12702,13 +12741,13 @@
         <v>1200</v>
       </c>
       <c r="H32" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I32" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="J32" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="K32">
         <v>125</v>
@@ -12732,7 +12771,7 @@
         <v>-20.21666667</v>
       </c>
       <c r="V32" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W32">
         <v>0.013056</v>
@@ -12761,10 +12800,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C33" s="2">
         <v>45094.38578665509</v>
@@ -12782,13 +12821,13 @@
         <v>1230</v>
       </c>
       <c r="H33" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I33" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="J33" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="K33">
         <v>125</v>
@@ -12812,7 +12851,7 @@
         <v>-19.16666667</v>
       </c>
       <c r="V33" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W33">
         <v>0.035</v>
@@ -12841,10 +12880,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C34" s="2">
         <v>45094.3861330787</v>
@@ -12862,13 +12901,13 @@
         <v>1260</v>
       </c>
       <c r="H34" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I34" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="J34" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="K34">
         <v>122</v>
@@ -12892,7 +12931,7 @@
         <v>-19.26666667</v>
       </c>
       <c r="V34" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W34">
         <v>-0.003333</v>
@@ -12921,10 +12960,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C35" s="2">
         <v>45094.38648175926</v>
@@ -12942,13 +12981,13 @@
         <v>1290</v>
       </c>
       <c r="H35" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I35" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="J35" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="K35">
         <v>115</v>
@@ -12972,7 +13011,7 @@
         <v>-19</v>
       </c>
       <c r="V35" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W35">
         <v>0.008888999999999999</v>
@@ -13001,10 +13040,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C36" s="2">
         <v>45094.38682829861</v>
@@ -13022,13 +13061,13 @@
         <v>1320</v>
       </c>
       <c r="H36" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I36" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="J36" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="K36">
         <v>114</v>
@@ -13052,7 +13091,7 @@
         <v>-18.73333333</v>
       </c>
       <c r="V36" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W36">
         <v>0.008888999999999999</v>
@@ -13081,10 +13120,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C37" s="2">
         <v>45094.38717591435</v>
@@ -13102,13 +13141,13 @@
         <v>1350</v>
       </c>
       <c r="H37" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I37" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="J37" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="K37">
         <v>121</v>
@@ -13132,7 +13171,7 @@
         <v>-18.63333333</v>
       </c>
       <c r="V37" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W37">
         <v>0.003333</v>
@@ -13161,10 +13200,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C38" s="2">
         <v>45094.38752283565</v>
@@ -13182,13 +13221,13 @@
         <v>1380</v>
       </c>
       <c r="H38" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I38" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="J38" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="K38">
         <v>130</v>
@@ -13212,7 +13251,7 @@
         <v>-18.9</v>
       </c>
       <c r="V38" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W38">
         <v>-0.008888999999999999</v>
@@ -13241,10 +13280,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C39" s="2">
         <v>45094.38787030092</v>
@@ -13262,13 +13301,13 @@
         <v>1410</v>
       </c>
       <c r="H39" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I39" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="J39" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="K39">
         <v>130</v>
@@ -13292,7 +13331,7 @@
         <v>-18.2</v>
       </c>
       <c r="V39" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W39">
         <v>0.023333</v>
@@ -13321,10 +13360,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C40" s="2">
         <v>45094.38821748843</v>
@@ -13342,13 +13381,13 @@
         <v>1440</v>
       </c>
       <c r="H40" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I40" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="J40" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="K40">
         <v>129</v>
@@ -13372,7 +13411,7 @@
         <v>-18</v>
       </c>
       <c r="V40" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W40">
         <v>0.006667</v>
@@ -13401,10 +13440,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C41" s="2">
         <v>45094.38856420139</v>
@@ -13422,13 +13461,13 @@
         <v>1470</v>
       </c>
       <c r="H41" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I41" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="J41" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="K41">
         <v>129</v>
@@ -13452,7 +13491,7 @@
         <v>-18.5</v>
       </c>
       <c r="V41" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W41">
         <v>-0.016667</v>
@@ -13481,10 +13520,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C42" s="2">
         <v>45094.38891199074</v>
@@ -13502,13 +13541,13 @@
         <v>1500</v>
       </c>
       <c r="H42" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I42" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="J42" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="K42">
         <v>118</v>
@@ -13532,7 +13571,7 @@
         <v>-18.56666667</v>
       </c>
       <c r="V42" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W42">
         <v>-0.002222</v>
@@ -13561,10 +13600,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C43" s="2">
         <v>45094.38925871528</v>
@@ -13582,13 +13621,13 @@
         <v>1530</v>
       </c>
       <c r="H43" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I43" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="J43" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="K43">
         <v>106</v>
@@ -13612,7 +13651,7 @@
         <v>-17.96666667</v>
       </c>
       <c r="V43" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W43">
         <v>0.02</v>
@@ -13641,10 +13680,10 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C44" s="2">
         <v>45094.38960546297</v>
@@ -13662,13 +13701,13 @@
         <v>1560</v>
       </c>
       <c r="H44" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I44" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="J44" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="K44">
         <v>108</v>
@@ -13692,7 +13731,7 @@
         <v>-17.26666667</v>
       </c>
       <c r="V44" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W44">
         <v>0.023333</v>
@@ -13721,10 +13760,10 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C45" s="2">
         <v>45094.38995331019</v>
@@ -13742,13 +13781,13 @@
         <v>1590</v>
       </c>
       <c r="H45" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I45" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="J45" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="K45">
         <v>102</v>
@@ -13772,7 +13811,7 @@
         <v>-17.26666667</v>
       </c>
       <c r="V45" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W45">
         <v>0</v>
@@ -13801,10 +13840,10 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C46" s="2">
         <v>45094.39030013889</v>
@@ -13822,13 +13861,13 @@
         <v>1620</v>
       </c>
       <c r="H46" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I46" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="J46" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="K46">
         <v>107</v>
@@ -13852,7 +13891,7 @@
         <v>-16.73333333</v>
       </c>
       <c r="V46" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W46">
         <v>0.017778</v>
@@ -13881,10 +13920,10 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C47" s="2">
         <v>45094.39064818287</v>
@@ -13902,13 +13941,13 @@
         <v>1650</v>
       </c>
       <c r="H47" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I47" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="J47" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="K47">
         <v>110</v>
@@ -13932,7 +13971,7 @@
         <v>-16.83333333</v>
       </c>
       <c r="V47" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W47">
         <v>-0.003333</v>
@@ -13961,10 +14000,10 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C48" s="2">
         <v>45094.39099511574</v>
@@ -13982,13 +14021,13 @@
         <v>1680</v>
       </c>
       <c r="H48" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I48" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="J48" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="K48">
         <v>111</v>
@@ -14012,7 +14051,7 @@
         <v>-16.9</v>
       </c>
       <c r="V48" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W48">
         <v>-0.002222</v>
@@ -14041,10 +14080,10 @@
     </row>
     <row r="49" spans="1:30">
       <c r="A49" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C49" s="2">
         <v>45094.39203666666</v>
@@ -14062,13 +14101,13 @@
         <v>1770</v>
       </c>
       <c r="H49" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I49" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="J49" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="K49">
         <v>106</v>
@@ -14092,7 +14131,7 @@
         <v>-14.71111111</v>
       </c>
       <c r="V49" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W49">
         <v>0.024321</v>
@@ -14121,10 +14160,10 @@
     </row>
     <row r="50" spans="1:30">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C50" s="2">
         <v>45094.39239282408</v>
@@ -14142,13 +14181,13 @@
         <v>1800</v>
       </c>
       <c r="H50" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I50" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="J50" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="K50">
         <v>137</v>
@@ -14172,7 +14211,7 @@
         <v>-12.53333333</v>
       </c>
       <c r="V50" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W50">
         <v>0.072593</v>
@@ -14201,10 +14240,10 @@
     </row>
     <row r="51" spans="1:30">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C51" s="2">
         <v>45094.39273111111</v>
@@ -14222,13 +14261,13 @@
         <v>1830</v>
       </c>
       <c r="H51" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I51" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="J51" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="K51">
         <v>98</v>
@@ -14252,7 +14291,7 @@
         <v>-12.7</v>
       </c>
       <c r="V51" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W51">
         <v>-0.005556</v>
@@ -14281,10 +14320,10 @@
     </row>
     <row r="52" spans="1:30">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C52" s="2">
         <v>45094.39307847223</v>
@@ -14302,13 +14341,13 @@
         <v>1860</v>
       </c>
       <c r="H52" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I52" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="J52" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="K52">
         <v>129</v>
@@ -14332,7 +14371,7 @@
         <v>-13.1</v>
       </c>
       <c r="V52" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W52">
         <v>-0.013333</v>
@@ -14361,10 +14400,10 @@
     </row>
     <row r="53" spans="1:30">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C53" s="2">
         <v>45094.39342516204</v>
@@ -14382,13 +14421,13 @@
         <v>1890</v>
       </c>
       <c r="H53" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I53" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="J53" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="K53">
         <v>99</v>
@@ -14412,7 +14451,7 @@
         <v>-11.9</v>
       </c>
       <c r="V53" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W53">
         <v>0.04</v>
@@ -14441,10 +14480,10 @@
     </row>
     <row r="54" spans="1:30">
       <c r="A54" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B54" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C54" s="2">
         <v>45094.39377326389</v>
@@ -14462,13 +14501,13 @@
         <v>1920</v>
       </c>
       <c r="H54" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I54" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="J54" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="K54">
         <v>112</v>
@@ -14492,7 +14531,7 @@
         <v>-12.1</v>
       </c>
       <c r="V54" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W54">
         <v>-0.006667</v>
@@ -14521,10 +14560,10 @@
     </row>
     <row r="55" spans="1:30">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B55" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C55" s="2">
         <v>45094.39446917824</v>
@@ -14542,13 +14581,13 @@
         <v>1980</v>
       </c>
       <c r="H55" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I55" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="J55" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="K55">
         <v>99</v>
@@ -14572,7 +14611,7 @@
         <v>-12.01666667</v>
       </c>
       <c r="V55" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W55">
         <v>0.001389</v>
@@ -14601,10 +14640,10 @@
     </row>
     <row r="56" spans="1:30">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C56" s="2">
         <v>45094.39487491898</v>
@@ -14622,13 +14661,13 @@
         <v>2010</v>
       </c>
       <c r="H56" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I56" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="J56" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="K56">
         <v>162</v>
@@ -14652,7 +14691,7 @@
         <v>-11.76666667</v>
       </c>
       <c r="V56" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W56">
         <v>0.008333</v>
@@ -14681,10 +14720,10 @@
     </row>
     <row r="57" spans="1:30">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C57" s="2">
         <v>45094.39516130787</v>
@@ -14702,13 +14741,13 @@
         <v>2040</v>
       </c>
       <c r="H57" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I57" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="J57" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="K57">
         <v>100</v>
@@ -14732,7 +14771,7 @@
         <v>-11.9</v>
       </c>
       <c r="V57" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W57">
         <v>-0.004444</v>
@@ -14761,10 +14800,10 @@
     </row>
     <row r="58" spans="1:30">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C58" s="2">
         <v>45094.39551729167</v>
@@ -14782,13 +14821,13 @@
         <v>2070</v>
       </c>
       <c r="H58" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I58" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="J58" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="K58">
         <v>169</v>
@@ -14812,7 +14851,7 @@
         <v>-11.8</v>
       </c>
       <c r="V58" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W58">
         <v>0.003333</v>
@@ -14841,10 +14880,10 @@
     </row>
     <row r="59" spans="1:30">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C59" s="2">
         <v>45094.3958559838</v>
@@ -14862,13 +14901,13 @@
         <v>2100</v>
       </c>
       <c r="H59" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I59" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="J59" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="K59">
         <v>113</v>
@@ -14892,7 +14931,7 @@
         <v>-11.9</v>
       </c>
       <c r="V59" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W59">
         <v>-0.003333</v>
@@ -14921,10 +14960,10 @@
     </row>
     <row r="60" spans="1:30">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C60" s="2">
         <v>45094.39620366898</v>
@@ -14942,13 +14981,13 @@
         <v>2130</v>
       </c>
       <c r="H60" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I60" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="J60" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="K60">
         <v>162</v>
@@ -14972,7 +15011,7 @@
         <v>-12.56666667</v>
       </c>
       <c r="V60" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W60">
         <v>-0.022222</v>
@@ -15001,10 +15040,10 @@
     </row>
     <row r="61" spans="1:30">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C61" s="2">
         <v>45094.39654993056</v>
@@ -15022,13 +15061,13 @@
         <v>2160</v>
       </c>
       <c r="H61" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I61" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="J61" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="K61">
         <v>101</v>
@@ -15052,7 +15091,7 @@
         <v>-11.73333333</v>
       </c>
       <c r="V61" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W61">
         <v>0.027778</v>
@@ -15081,10 +15120,10 @@
     </row>
     <row r="62" spans="1:30">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C62" s="2">
         <v>45094.3975924537</v>
@@ -15102,13 +15141,13 @@
         <v>2250</v>
       </c>
       <c r="H62" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I62" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="J62" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="K62">
         <v>171</v>
@@ -15132,7 +15171,7 @@
         <v>-11.46666667</v>
       </c>
       <c r="V62" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W62">
         <v>0.002963</v>
@@ -15161,10 +15200,10 @@
     </row>
     <row r="63" spans="1:30">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C63" s="2">
         <v>45094.39793901621</v>
@@ -15182,13 +15221,13 @@
         <v>2280</v>
       </c>
       <c r="H63" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I63" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="J63" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="K63">
         <v>139</v>
@@ -15212,7 +15251,7 @@
         <v>-11.13333333</v>
       </c>
       <c r="V63" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W63">
         <v>0.011111</v>
@@ -15241,10 +15280,10 @@
     </row>
     <row r="64" spans="1:30">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B64" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C64" s="2">
         <v>45094.3982862037</v>
@@ -15262,13 +15301,13 @@
         <v>2310</v>
       </c>
       <c r="H64" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I64" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="J64" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="K64">
         <v>114</v>
@@ -15292,7 +15331,7 @@
         <v>-11.26666667</v>
       </c>
       <c r="V64" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W64">
         <v>-0.004444</v>
@@ -15321,10 +15360,10 @@
     </row>
     <row r="65" spans="1:30">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C65" s="2">
         <v>45094.39863377315</v>
@@ -15342,13 +15381,13 @@
         <v>2340</v>
       </c>
       <c r="H65" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I65" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="J65" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="K65">
         <v>171</v>
@@ -15372,7 +15411,7 @@
         <v>-11.06666667</v>
       </c>
       <c r="V65" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W65">
         <v>0.006667</v>
@@ -15401,10 +15440,10 @@
     </row>
     <row r="66" spans="1:30">
       <c r="A66" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C66" s="2">
         <v>45094.39898017361</v>
@@ -15422,13 +15461,13 @@
         <v>2370</v>
       </c>
       <c r="H66" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I66" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="J66" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="K66">
         <v>140</v>
@@ -15452,7 +15491,7 @@
         <v>-11</v>
       </c>
       <c r="V66" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W66">
         <v>0.002222</v>
@@ -15481,10 +15520,10 @@
     </row>
     <row r="67" spans="1:30">
       <c r="A67" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C67" s="2">
         <v>45094.39932827546</v>
@@ -15502,13 +15541,13 @@
         <v>2400</v>
       </c>
       <c r="H67" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I67" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="J67" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="K67">
         <v>93</v>
@@ -15532,7 +15571,7 @@
         <v>-10.46666667</v>
       </c>
       <c r="V67" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W67">
         <v>0.017778</v>
@@ -15561,10 +15600,10 @@
     </row>
     <row r="68" spans="1:30">
       <c r="A68" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C68" s="2">
         <v>45094.40002246528</v>
@@ -15582,13 +15621,13 @@
         <v>2460</v>
       </c>
       <c r="H68" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I68" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="J68" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="K68">
         <v>156</v>
@@ -15612,7 +15651,7 @@
         <v>-10.23333333</v>
       </c>
       <c r="V68" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W68">
         <v>0.003889</v>
@@ -15641,10 +15680,10 @@
     </row>
     <row r="69" spans="1:30">
       <c r="A69" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C69" s="2">
         <v>45094.40036984954</v>
@@ -15662,13 +15701,13 @@
         <v>2490</v>
       </c>
       <c r="H69" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I69" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="J69" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="K69">
         <v>149</v>
@@ -15692,7 +15731,7 @@
         <v>-9.866666670000001</v>
       </c>
       <c r="V69" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W69">
         <v>0.012222</v>
@@ -15721,10 +15760,10 @@
     </row>
     <row r="70" spans="1:30">
       <c r="A70" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B70" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C70" s="2">
         <v>45094.40071681713</v>
@@ -15742,13 +15781,13 @@
         <v>2520</v>
       </c>
       <c r="H70" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I70" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="J70" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="K70">
         <v>131</v>
@@ -15772,7 +15811,7 @@
         <v>-10.1</v>
       </c>
       <c r="V70" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W70">
         <v>-0.007778</v>
@@ -15801,10 +15840,10 @@
     </row>
     <row r="71" spans="1:30">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B71" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C71" s="2">
         <v>45094.4010644213</v>
@@ -15822,13 +15861,13 @@
         <v>2550</v>
       </c>
       <c r="H71" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I71" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="J71" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="K71">
         <v>134</v>
@@ -15852,7 +15891,7 @@
         <v>-9.83333333</v>
       </c>
       <c r="V71" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W71">
         <v>0.008888999999999999</v>
@@ -15881,10 +15920,10 @@
     </row>
     <row r="72" spans="1:30">
       <c r="A72" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C72" s="2">
         <v>45094.40141065972</v>
@@ -15902,13 +15941,13 @@
         <v>2580</v>
       </c>
       <c r="H72" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I72" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="J72" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="K72">
         <v>147</v>
@@ -15932,7 +15971,7 @@
         <v>-9.66666667</v>
       </c>
       <c r="V72" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W72">
         <v>0.005556</v>
@@ -15961,10 +16000,10 @@
     </row>
     <row r="73" spans="1:30">
       <c r="A73" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B73" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C73" s="2">
         <v>45094.40175862268</v>
@@ -15982,13 +16021,13 @@
         <v>2610</v>
       </c>
       <c r="H73" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I73" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="J73" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="K73">
         <v>129</v>
@@ -16012,7 +16051,7 @@
         <v>-9.66666667</v>
       </c>
       <c r="V73" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W73">
         <v>0</v>
@@ -16041,10 +16080,10 @@
     </row>
     <row r="74" spans="1:30">
       <c r="A74" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B74" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C74" s="2">
         <v>45094.40245278935</v>
@@ -16062,13 +16101,13 @@
         <v>2670</v>
       </c>
       <c r="H74" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I74" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="J74" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="K74">
         <v>131</v>
@@ -16092,7 +16131,7 @@
         <v>-9.68333333</v>
       </c>
       <c r="V74" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W74">
         <v>-0.000278</v>
@@ -16121,10 +16160,10 @@
     </row>
     <row r="75" spans="1:30">
       <c r="A75" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B75" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C75" s="2">
         <v>45094.40279944445</v>
@@ -16142,13 +16181,13 @@
         <v>2700</v>
       </c>
       <c r="H75" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I75" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="J75" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="K75">
         <v>121</v>
@@ -16172,7 +16211,7 @@
         <v>-9.733333330000001</v>
       </c>
       <c r="V75" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W75">
         <v>-0.001667</v>
@@ -16201,10 +16240,10 @@
     </row>
     <row r="76" spans="1:30">
       <c r="A76" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B76" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C76" s="2">
         <v>45094.40314679398</v>
@@ -16222,13 +16261,13 @@
         <v>2730</v>
       </c>
       <c r="H76" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I76" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="J76" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="K76">
         <v>99</v>
@@ -16252,7 +16291,7 @@
         <v>-9.633333329999999</v>
       </c>
       <c r="V76" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W76">
         <v>0.003333</v>
@@ -16281,10 +16320,10 @@
     </row>
     <row r="77" spans="1:30">
       <c r="A77" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C77" s="2">
         <v>45094.40349465278</v>
@@ -16302,13 +16341,13 @@
         <v>2760</v>
       </c>
       <c r="H77" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I77" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="J77" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="K77">
         <v>83</v>
@@ -16332,7 +16371,7 @@
         <v>-9.866666670000001</v>
       </c>
       <c r="V77" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W77">
         <v>-0.007778</v>
@@ -16361,10 +16400,10 @@
     </row>
     <row r="78" spans="1:30">
       <c r="A78" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B78" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C78" s="2">
         <v>45094.40384165509</v>
@@ -16382,13 +16421,13 @@
         <v>2790</v>
       </c>
       <c r="H78" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I78" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="J78" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="K78">
         <v>61</v>
@@ -16412,7 +16451,7 @@
         <v>-9.43333333</v>
       </c>
       <c r="V78" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W78">
         <v>0.014444</v>
@@ -16441,10 +16480,10 @@
     </row>
     <row r="79" spans="1:30">
       <c r="A79" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B79" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C79" s="2">
         <v>45094.40418819444</v>
@@ -16462,13 +16501,13 @@
         <v>2820</v>
       </c>
       <c r="H79" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I79" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="J79" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="K79">
         <v>52</v>
@@ -16492,7 +16531,7 @@
         <v>-9.53333333</v>
       </c>
       <c r="V79" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W79">
         <v>-0.003333</v>
@@ -16521,10 +16560,10 @@
     </row>
     <row r="80" spans="1:30">
       <c r="A80" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B80" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C80" s="2">
         <v>45094.40453605324</v>
@@ -16542,13 +16581,13 @@
         <v>2850</v>
       </c>
       <c r="H80" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I80" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="J80" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="K80">
         <v>24</v>
@@ -16572,7 +16611,7 @@
         <v>-9.46666667</v>
       </c>
       <c r="V80" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W80">
         <v>0.002222</v>
@@ -16601,10 +16640,10 @@
     </row>
     <row r="81" spans="1:30">
       <c r="A81" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B81" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C81" s="2">
         <v>45094.40488373843</v>
@@ -16622,13 +16661,13 @@
         <v>2880</v>
       </c>
       <c r="H81" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I81" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="J81" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="K81">
         <v>81</v>
@@ -16652,7 +16691,7 @@
         <v>-9.56666667</v>
       </c>
       <c r="V81" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W81">
         <v>-0.003333</v>
@@ -16681,10 +16720,10 @@
     </row>
     <row r="82" spans="1:30">
       <c r="A82" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B82" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C82" s="2">
         <v>45094.40523104167</v>
@@ -16702,13 +16741,13 @@
         <v>2910</v>
       </c>
       <c r="H82" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I82" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="J82" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="K82">
         <v>175</v>
@@ -16732,7 +16771,7 @@
         <v>-9.43333333</v>
       </c>
       <c r="V82" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W82">
         <v>0.004444</v>
@@ -16761,10 +16800,10 @@
     </row>
     <row r="83" spans="1:30">
       <c r="A83" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B83" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C83" s="2">
         <v>45094.40557918981</v>
@@ -16782,13 +16821,13 @@
         <v>2940</v>
       </c>
       <c r="H83" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I83" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="J83" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="K83">
         <v>173</v>
@@ -16812,7 +16851,7 @@
         <v>-9.733333330000001</v>
       </c>
       <c r="V83" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W83">
         <v>-0.01</v>
@@ -16841,10 +16880,10 @@
     </row>
     <row r="84" spans="1:30">
       <c r="A84" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B84" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C84" s="2">
         <v>45094.40662034722</v>
@@ -16862,13 +16901,13 @@
         <v>3030</v>
       </c>
       <c r="H84" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I84" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="J84" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="K84">
         <v>214</v>
@@ -16892,7 +16931,7 @@
         <v>-9.57777778</v>
       </c>
       <c r="V84" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W84">
         <v>0.001728</v>
@@ -16921,10 +16960,10 @@
     </row>
     <row r="85" spans="1:30">
       <c r="A85" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B85" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C85" s="2">
         <v>45094.40696665509</v>
@@ -16942,13 +16981,13 @@
         <v>3060</v>
       </c>
       <c r="H85" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I85" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="J85" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="K85">
         <v>250</v>
@@ -16972,7 +17011,7 @@
         <v>-9.16666667</v>
       </c>
       <c r="V85" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W85">
         <v>0.013704</v>
@@ -17001,10 +17040,10 @@
     </row>
     <row r="86" spans="1:30">
       <c r="A86" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B86" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C86" s="2">
         <v>45094.40732755787</v>
@@ -17022,13 +17061,13 @@
         <v>3090</v>
       </c>
       <c r="H86" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I86" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="J86" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="K86">
         <v>316</v>
@@ -17052,7 +17091,7 @@
         <v>-9.03333333</v>
       </c>
       <c r="V86" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W86">
         <v>0.004444</v>
@@ -17081,10 +17120,10 @@
     </row>
     <row r="87" spans="1:30">
       <c r="A87" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B87" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C87" s="2">
         <v>45094.40800915509</v>
@@ -17102,13 +17141,13 @@
         <v>3150</v>
       </c>
       <c r="H87" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I87" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="J87" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="K87">
         <v>114</v>
@@ -17132,7 +17171,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="V87" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W87">
         <v>0.005556</v>
@@ -17161,10 +17200,10 @@
     </row>
     <row r="88" spans="1:30">
       <c r="A88" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B88" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C88" s="2">
         <v>45094.40835655093</v>
@@ -17182,13 +17221,13 @@
         <v>3180</v>
       </c>
       <c r="H88" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I88" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="J88" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="K88">
         <v>123</v>
@@ -17212,7 +17251,7 @@
         <v>-8.733333330000001</v>
       </c>
       <c r="V88" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W88">
         <v>-0.001111</v>
@@ -17241,10 +17280,10 @@
     </row>
     <row r="89" spans="1:30">
       <c r="A89" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B89" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C89" s="2">
         <v>45094.40908092593</v>
@@ -17262,13 +17301,13 @@
         <v>3240</v>
       </c>
       <c r="H89" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="I89" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="J89" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="K89">
         <v>164</v>
@@ -17292,7 +17331,7 @@
         <v>-8.766666669999999</v>
       </c>
       <c r="V89" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="W89">
         <v>-0.000556</v>

--- a/www/flightdata/xlsx/eoss-343.xlsx
+++ b/www/flightdata/xlsx/eoss-343.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1257" uniqueCount="464">
   <si>
     <t>flight</t>
   </si>
@@ -228,6 +228,9 @@
     <t>velocity_curvefit</t>
   </si>
   <si>
+    <t>reynolds_transition</t>
+  </si>
+  <si>
     <t>AE0SS-9</t>
   </si>
   <si>
@@ -865,6 +868,12 @@
   </si>
   <si>
     <t>high Re</t>
+  </si>
+  <si>
+    <t>low_to_high</t>
+  </si>
+  <si>
+    <t>high_to_low</t>
   </si>
   <si>
     <t>descending</t>
@@ -1924,10 +1933,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE105"/>
+  <dimension ref="A1:AF105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -2021,13 +2030,16 @@
       <c r="AE1" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="2" spans="1:31">
+      <c r="AF1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" s="2">
         <v>45094.33592848379</v>
@@ -2045,13 +2057,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K2">
         <v>349</v>
@@ -2078,7 +2090,7 @@
         <v>1.38461538</v>
       </c>
       <c r="W2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Y2">
         <v>1.384615</v>
@@ -2087,12 +2099,12 @@
         <v>11.241245</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C3" s="2">
         <v>45094.33596957176</v>
@@ -2110,13 +2122,13 @@
         <v>4</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="K3">
         <v>311</v>
@@ -2143,7 +2155,7 @@
         <v>19.75</v>
       </c>
       <c r="W3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X3">
         <v>4.591346</v>
@@ -2164,12 +2176,12 @@
         <v>12.296767</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" s="2">
         <v>45094.33613355324</v>
@@ -2187,13 +2199,13 @@
         <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K4">
         <v>187</v>
@@ -2220,7 +2232,7 @@
         <v>17.46666667</v>
       </c>
       <c r="W4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X4">
         <v>-0.076111</v>
@@ -2247,12 +2259,12 @@
         <v>16.625394</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" s="2">
         <v>45094.33632274305</v>
@@ -2270,13 +2282,13 @@
         <v>34</v>
       </c>
       <c r="H5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K5">
         <v>90</v>
@@ -2303,7 +2315,7 @@
         <v>22.3</v>
       </c>
       <c r="W5" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X5">
         <v>0.161111</v>
@@ -2330,12 +2342,12 @@
         <v>18.789308</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" s="2">
         <v>45094.3364802662</v>
@@ -2353,13 +2365,13 @@
         <v>49</v>
       </c>
       <c r="H6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="K6">
         <v>93</v>
@@ -2386,7 +2398,7 @@
         <v>22.6</v>
       </c>
       <c r="W6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X6">
         <v>0.01</v>
@@ -2413,12 +2425,12 @@
         <v>21.066657</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="2">
         <v>45094.33666510417</v>
@@ -2436,13 +2448,13 @@
         <v>64</v>
       </c>
       <c r="H7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J7" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="K7">
         <v>98</v>
@@ -2469,7 +2481,7 @@
         <v>22.63333333</v>
       </c>
       <c r="W7" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X7">
         <v>0.001111</v>
@@ -2496,12 +2508,12 @@
         <v>22.087113</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:32">
       <c r="A8" t="s">
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" s="2">
         <v>45094.33682725694</v>
@@ -2519,13 +2531,13 @@
         <v>79</v>
       </c>
       <c r="H8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J8" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K8">
         <v>148</v>
@@ -2552,7 +2564,7 @@
         <v>22.73333333</v>
       </c>
       <c r="W8" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X8">
         <v>0.003333</v>
@@ -2579,12 +2591,12 @@
         <v>23.035136</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:32">
       <c r="A9" t="s">
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9" s="2">
         <v>45094.33701878472</v>
@@ -2602,13 +2614,13 @@
         <v>94</v>
       </c>
       <c r="H9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J9" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="K9">
         <v>165</v>
@@ -2635,7 +2647,7 @@
         <v>22.2</v>
       </c>
       <c r="W9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X9">
         <v>-0.017778</v>
@@ -2662,12 +2674,12 @@
         <v>23.357031</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:32">
       <c r="A10" t="s">
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" s="2">
         <v>45094.33717542824</v>
@@ -2685,13 +2697,13 @@
         <v>109</v>
       </c>
       <c r="H10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K10">
         <v>275</v>
@@ -2718,7 +2730,7 @@
         <v>21.6</v>
       </c>
       <c r="W10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X10">
         <v>-0.02</v>
@@ -2745,12 +2757,12 @@
         <v>23.554902</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:32">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" s="2">
         <v>45094.33736206019</v>
@@ -2768,13 +2780,13 @@
         <v>124</v>
       </c>
       <c r="H11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="K11">
         <v>271</v>
@@ -2801,7 +2813,7 @@
         <v>22.53333333</v>
       </c>
       <c r="W11" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X11">
         <v>0.031111</v>
@@ -2828,12 +2840,12 @@
         <v>23.539136</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:32">
       <c r="A12" t="s">
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" s="2">
         <v>45094.33752214121</v>
@@ -2851,13 +2863,13 @@
         <v>139</v>
       </c>
       <c r="H12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K12">
         <v>66</v>
@@ -2884,7 +2896,7 @@
         <v>22.2</v>
       </c>
       <c r="W12" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X12">
         <v>-0.011111</v>
@@ -2911,12 +2923,12 @@
         <v>23.38196</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:32">
       <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C13" s="2">
         <v>45094.33770380787</v>
@@ -2934,13 +2946,13 @@
         <v>154</v>
       </c>
       <c r="H13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="K13">
         <v>198</v>
@@ -2967,7 +2979,7 @@
         <v>21.86666667</v>
       </c>
       <c r="W13" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X13">
         <v>-0.011111</v>
@@ -2994,12 +3006,12 @@
         <v>23.209149</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:32">
       <c r="A14" t="s">
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" s="2">
         <v>45094.33786939815</v>
@@ -3017,13 +3029,13 @@
         <v>169</v>
       </c>
       <c r="H14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="K14">
         <v>144</v>
@@ -3050,7 +3062,7 @@
         <v>22.63333333</v>
       </c>
       <c r="W14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X14">
         <v>0.025556</v>
@@ -3077,12 +3089,12 @@
         <v>22.914681</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:32">
       <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" s="2">
         <v>45094.33805721065</v>
@@ -3100,13 +3112,13 @@
         <v>184</v>
       </c>
       <c r="H15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J15" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="K15">
         <v>120</v>
@@ -3133,7 +3145,7 @@
         <v>23.5</v>
       </c>
       <c r="W15" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X15">
         <v>0.028889</v>
@@ -3160,12 +3172,12 @@
         <v>22.690618</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:32">
       <c r="A16" t="s">
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" s="2">
         <v>45094.33821681713</v>
@@ -3183,13 +3195,13 @@
         <v>199</v>
       </c>
       <c r="H16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J16" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K16">
         <v>261</v>
@@ -3216,7 +3228,7 @@
         <v>23.26666667</v>
       </c>
       <c r="W16" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X16">
         <v>-0.007778</v>
@@ -3248,7 +3260,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" s="2">
         <v>45094.33856372685</v>
@@ -3266,13 +3278,13 @@
         <v>229</v>
       </c>
       <c r="H17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K17">
         <v>100</v>
@@ -3299,7 +3311,7 @@
         <v>22.56666667</v>
       </c>
       <c r="W17" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X17">
         <v>-0.023333</v>
@@ -3331,7 +3343,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18" s="2">
         <v>45094.33891157407</v>
@@ -3349,13 +3361,13 @@
         <v>259</v>
       </c>
       <c r="H18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J18" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="K18">
         <v>178</v>
@@ -3382,7 +3394,7 @@
         <v>22.03333333</v>
       </c>
       <c r="W18" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X18">
         <v>-0.017778</v>
@@ -3414,7 +3426,7 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C19" s="2">
         <v>45094.33909788194</v>
@@ -3432,13 +3444,13 @@
         <v>274</v>
       </c>
       <c r="H19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J19" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="K19">
         <v>164</v>
@@ -3465,7 +3477,7 @@
         <v>22.27777778</v>
       </c>
       <c r="W19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X19">
         <v>0.002716</v>
@@ -3497,7 +3509,7 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C20" s="2">
         <v>45094.33960560185</v>
@@ -3515,13 +3527,13 @@
         <v>319</v>
       </c>
       <c r="H20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J20" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K20">
         <v>146</v>
@@ -3548,7 +3560,7 @@
         <v>22.61666667</v>
       </c>
       <c r="W20" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X20">
         <v>0.005648</v>
@@ -3580,7 +3592,7 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" s="2">
         <v>45094.33979266204</v>
@@ -3598,13 +3610,13 @@
         <v>334</v>
       </c>
       <c r="H21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J21" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="K21">
         <v>147</v>
@@ -3631,7 +3643,7 @@
         <v>23.45</v>
       </c>
       <c r="W21" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X21">
         <v>0.013889</v>
@@ -3663,7 +3675,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C22" s="2">
         <v>45094.33995288194</v>
@@ -3681,13 +3693,13 @@
         <v>349</v>
       </c>
       <c r="H22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J22" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K22">
         <v>105</v>
@@ -3714,7 +3726,7 @@
         <v>22.96666667</v>
       </c>
       <c r="W22" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X22">
         <v>-0.016111</v>
@@ -3746,7 +3758,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C23" s="2">
         <v>45094.34029994213</v>
@@ -3764,13 +3776,13 @@
         <v>379</v>
       </c>
       <c r="H23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J23" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="K23">
         <v>160</v>
@@ -3797,7 +3809,7 @@
         <v>22.23333333</v>
       </c>
       <c r="W23" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X23">
         <v>-0.024444</v>
@@ -3829,7 +3841,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C24" s="2">
         <v>45094.34049260417</v>
@@ -3847,13 +3859,13 @@
         <v>395</v>
       </c>
       <c r="H24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J24" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K24">
         <v>114</v>
@@ -3880,7 +3892,7 @@
         <v>22.37704918</v>
       </c>
       <c r="W24" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X24">
         <v>0.002356</v>
@@ -3912,7 +3924,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C25" s="2">
         <v>45094.34064704861</v>
@@ -3930,13 +3942,13 @@
         <v>409</v>
       </c>
       <c r="H25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J25" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K25">
         <v>103</v>
@@ -3963,7 +3975,7 @@
         <v>23.7</v>
       </c>
       <c r="W25" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X25">
         <v>0.044098</v>
@@ -3995,7 +4007,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C26" s="2">
         <v>45094.34099342593</v>
@@ -4013,13 +4025,13 @@
         <v>439</v>
       </c>
       <c r="H26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J26" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="K26">
         <v>121</v>
@@ -4046,7 +4058,7 @@
         <v>23.23333333</v>
       </c>
       <c r="W26" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X26">
         <v>-0.015556</v>
@@ -4078,7 +4090,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C27" s="2">
         <v>45094.34117866898</v>
@@ -4096,13 +4108,13 @@
         <v>454</v>
       </c>
       <c r="H27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J27" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K27">
         <v>118</v>
@@ -4129,7 +4141,7 @@
         <v>23.23728814</v>
       </c>
       <c r="W27" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X27">
         <v>6.7E-05</v>
@@ -4161,7 +4173,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" s="2">
         <v>45094.34168921296</v>
@@ -4179,13 +4191,13 @@
         <v>499</v>
       </c>
       <c r="H28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J28" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K28">
         <v>137</v>
@@ -4212,7 +4224,7 @@
         <v>23.18333333</v>
       </c>
       <c r="W28" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X28">
         <v>-0.000899</v>
@@ -4244,7 +4256,7 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C29" s="2">
         <v>45094.34203625</v>
@@ -4262,13 +4274,13 @@
         <v>529</v>
       </c>
       <c r="H29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J29" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="K29">
         <v>162</v>
@@ -4295,7 +4307,7 @@
         <v>24.1</v>
       </c>
       <c r="W29" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X29">
         <v>0.030556</v>
@@ -4327,7 +4339,7 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C30" s="2">
         <v>45094.34222148148</v>
@@ -4345,13 +4357,13 @@
         <v>544</v>
       </c>
       <c r="H30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J30" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="K30">
         <v>119</v>
@@ -4378,7 +4390,7 @@
         <v>24.05555556</v>
       </c>
       <c r="W30" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X30">
         <v>-0.000494</v>
@@ -4410,7 +4422,7 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="2">
         <v>45094.34273024306</v>
@@ -4428,13 +4440,13 @@
         <v>589</v>
       </c>
       <c r="H31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J31" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="K31">
         <v>155</v>
@@ -4461,7 +4473,7 @@
         <v>23.96666667</v>
       </c>
       <c r="W31" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X31">
         <v>-0.001481</v>
@@ -4493,7 +4505,7 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C32" s="2">
         <v>45094.34291811343</v>
@@ -4511,13 +4523,13 @@
         <v>604</v>
       </c>
       <c r="H32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J32" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K32">
         <v>119</v>
@@ -4544,7 +4556,7 @@
         <v>23.78333333</v>
       </c>
       <c r="W32" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X32">
         <v>-0.003056</v>
@@ -4571,12 +4583,12 @@
         <v>24.086584</v>
       </c>
     </row>
-    <row r="33" spans="1:31">
+    <row r="33" spans="1:32">
       <c r="A33" t="s">
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C33" s="2">
         <v>45094.34411873842</v>
@@ -4594,13 +4606,13 @@
         <v>709</v>
       </c>
       <c r="H33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J33" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="K33">
         <v>257</v>
@@ -4627,7 +4639,7 @@
         <v>23.725</v>
       </c>
       <c r="W33" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X33">
         <v>-0.000486</v>
@@ -4654,12 +4666,12 @@
         <v>23.676536</v>
       </c>
     </row>
-    <row r="34" spans="1:31">
+    <row r="34" spans="1:32">
       <c r="A34" t="s">
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C34" s="2">
         <v>45094.34446693287</v>
@@ -4677,13 +4689,13 @@
         <v>739</v>
       </c>
       <c r="H34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J34" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="K34">
         <v>51</v>
@@ -4710,7 +4722,7 @@
         <v>23.6</v>
       </c>
       <c r="W34" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X34">
         <v>-0.004167</v>
@@ -4737,12 +4749,12 @@
         <v>23.572002</v>
       </c>
     </row>
-    <row r="35" spans="1:31">
+    <row r="35" spans="1:32">
       <c r="A35" t="s">
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C35" s="2">
         <v>45094.34481342592</v>
@@ -4760,13 +4772,13 @@
         <v>769</v>
       </c>
       <c r="H35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J35" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="K35">
         <v>221</v>
@@ -4793,7 +4805,7 @@
         <v>23.2</v>
       </c>
       <c r="W35" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X35">
         <v>-0.013333</v>
@@ -4820,12 +4832,12 @@
         <v>23.501375</v>
       </c>
     </row>
-    <row r="36" spans="1:31">
+    <row r="36" spans="1:32">
       <c r="A36" t="s">
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C36" s="2">
         <v>45094.34550837963</v>
@@ -4843,13 +4855,13 @@
         <v>829</v>
       </c>
       <c r="H36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J36" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K36">
         <v>69</v>
@@ -4876,7 +4888,7 @@
         <v>23.8</v>
       </c>
       <c r="W36" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X36">
         <v>0.01</v>
@@ -4903,12 +4915,12 @@
         <v>23.492725</v>
       </c>
     </row>
-    <row r="37" spans="1:31">
+    <row r="37" spans="1:32">
       <c r="A37" t="s">
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C37" s="2">
         <v>45094.34585572917</v>
@@ -4926,13 +4938,13 @@
         <v>859</v>
       </c>
       <c r="H37" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J37" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K37">
         <v>133</v>
@@ -4959,7 +4971,7 @@
         <v>23.56666667</v>
       </c>
       <c r="W37" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X37">
         <v>-0.007778</v>
@@ -4986,12 +4998,12 @@
         <v>23.565082</v>
       </c>
     </row>
-    <row r="38" spans="1:31">
+    <row r="38" spans="1:32">
       <c r="A38" t="s">
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C38" s="2">
         <v>45094.34620280092</v>
@@ -5009,13 +5021,13 @@
         <v>889</v>
       </c>
       <c r="H38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J38" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K38">
         <v>161</v>
@@ -5042,7 +5054,7 @@
         <v>24.16666667</v>
       </c>
       <c r="W38" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X38">
         <v>0.02</v>
@@ -5069,12 +5081,12 @@
         <v>23.691996</v>
       </c>
     </row>
-    <row r="39" spans="1:31">
+    <row r="39" spans="1:32">
       <c r="A39" t="s">
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C39" s="2">
         <v>45094.34654929398</v>
@@ -5092,13 +5104,13 @@
         <v>919</v>
       </c>
       <c r="H39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K39">
         <v>132</v>
@@ -5125,7 +5137,7 @@
         <v>24.16666667</v>
       </c>
       <c r="W39" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X39">
         <v>0</v>
@@ -5152,12 +5164,12 @@
         <v>23.868238</v>
       </c>
     </row>
-    <row r="40" spans="1:31">
+    <row r="40" spans="1:32">
       <c r="A40" t="s">
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C40" s="2">
         <v>45094.34689672454</v>
@@ -5175,13 +5187,13 @@
         <v>949</v>
       </c>
       <c r="H40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J40" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K40">
         <v>149</v>
@@ -5208,7 +5220,7 @@
         <v>24.26666667</v>
       </c>
       <c r="W40" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X40">
         <v>0.003333</v>
@@ -5235,12 +5247,12 @@
         <v>24.088167</v>
       </c>
     </row>
-    <row r="41" spans="1:31">
+    <row r="41" spans="1:32">
       <c r="A41" t="s">
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C41" s="2">
         <v>45094.34724454861</v>
@@ -5258,13 +5270,13 @@
         <v>979</v>
       </c>
       <c r="H41" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J41" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K41">
         <v>188</v>
@@ -5291,7 +5303,7 @@
         <v>23.23333333</v>
       </c>
       <c r="W41" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X41">
         <v>-0.034444</v>
@@ -5318,12 +5330,12 @@
         <v>24.33117</v>
       </c>
     </row>
-    <row r="42" spans="1:31">
+    <row r="42" spans="1:32">
       <c r="A42" t="s">
         <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C42" s="2">
         <v>45094.3475916088</v>
@@ -5341,13 +5353,13 @@
         <v>1009</v>
       </c>
       <c r="H42" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I42" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J42" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K42">
         <v>173</v>
@@ -5374,7 +5386,7 @@
         <v>25.06666667</v>
       </c>
       <c r="W42" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X42">
         <v>0.061111</v>
@@ -5401,12 +5413,12 @@
         <v>24.619012</v>
       </c>
     </row>
-    <row r="43" spans="1:31">
+    <row r="43" spans="1:32">
       <c r="A43" t="s">
         <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C43" s="2">
         <v>45094.34793854166</v>
@@ -5424,13 +5436,13 @@
         <v>1039</v>
       </c>
       <c r="H43" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J43" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K43">
         <v>115</v>
@@ -5457,7 +5469,7 @@
         <v>25.1</v>
       </c>
       <c r="W43" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X43">
         <v>0.001111</v>
@@ -5484,12 +5496,12 @@
         <v>24.92305</v>
       </c>
     </row>
-    <row r="44" spans="1:31">
+    <row r="44" spans="1:32">
       <c r="A44" t="s">
         <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C44" s="2">
         <v>45094.34863305555</v>
@@ -5507,13 +5519,13 @@
         <v>1099</v>
       </c>
       <c r="H44" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I44" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J44" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K44">
         <v>206</v>
@@ -5540,7 +5552,7 @@
         <v>25.01666667</v>
       </c>
       <c r="W44" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X44">
         <v>-0.001389</v>
@@ -5567,12 +5579,12 @@
         <v>25.534038</v>
       </c>
     </row>
-    <row r="45" spans="1:31">
+    <row r="45" spans="1:32">
       <c r="A45" t="s">
         <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C45" s="2">
         <v>45094.34882231482</v>
@@ -5590,13 +5602,13 @@
         <v>1114</v>
       </c>
       <c r="H45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I45" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J45" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K45">
         <v>143</v>
@@ -5623,7 +5635,7 @@
         <v>24.10392157</v>
       </c>
       <c r="W45" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X45">
         <v>-0.00179</v>
@@ -5649,13 +5661,16 @@
       <c r="AE45">
         <v>25.674335</v>
       </c>
-    </row>
-    <row r="46" spans="1:31">
+      <c r="AF45" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="46" spans="1:32">
       <c r="A46" t="s">
         <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C46" s="2">
         <v>45094.34897998843</v>
@@ -5673,13 +5688,13 @@
         <v>1129</v>
       </c>
       <c r="H46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J46" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K46">
         <v>187</v>
@@ -5706,7 +5721,7 @@
         <v>27.83333333</v>
       </c>
       <c r="W46" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X46">
         <v>0.124314</v>
@@ -5733,12 +5748,12 @@
         <v>25.855183</v>
       </c>
     </row>
-    <row r="47" spans="1:31">
+    <row r="47" spans="1:32">
       <c r="A47" t="s">
         <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C47" s="2">
         <v>45094.34932815973</v>
@@ -5756,13 +5771,13 @@
         <v>1159</v>
       </c>
       <c r="H47" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J47" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K47">
         <v>193</v>
@@ -5789,7 +5804,7 @@
         <v>26.53333333</v>
       </c>
       <c r="W47" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X47">
         <v>-0.043333</v>
@@ -5816,12 +5831,12 @@
         <v>26.137738</v>
       </c>
     </row>
-    <row r="48" spans="1:31">
+    <row r="48" spans="1:32">
       <c r="A48" t="s">
         <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C48" s="2">
         <v>45094.34967472222</v>
@@ -5839,13 +5854,13 @@
         <v>1189</v>
       </c>
       <c r="H48" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J48" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K48">
         <v>81</v>
@@ -5872,7 +5887,7 @@
         <v>27.5</v>
       </c>
       <c r="W48" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X48">
         <v>0.032222</v>
@@ -5904,7 +5919,7 @@
         <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C49" s="2">
         <v>45094.35036913194</v>
@@ -5922,13 +5937,13 @@
         <v>1249</v>
       </c>
       <c r="H49" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I49" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J49" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K49">
         <v>147</v>
@@ -5955,7 +5970,7 @@
         <v>27.01666667</v>
       </c>
       <c r="W49" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X49">
         <v>-0.008056000000000001</v>
@@ -5987,7 +6002,7 @@
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C50" s="2">
         <v>45094.35055534722</v>
@@ -6005,13 +6020,13 @@
         <v>1264</v>
       </c>
       <c r="H50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J50" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K50">
         <v>122</v>
@@ -6038,7 +6053,7 @@
         <v>27.36</v>
       </c>
       <c r="W50" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X50">
         <v>0.002289</v>
@@ -6070,7 +6085,7 @@
         <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C51" s="2">
         <v>45094.35071625</v>
@@ -6088,13 +6103,13 @@
         <v>1279</v>
       </c>
       <c r="H51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I51" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J51" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K51">
         <v>118</v>
@@ -6121,7 +6136,7 @@
         <v>26.93333333</v>
       </c>
       <c r="W51" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X51">
         <v>-0.014222</v>
@@ -6153,7 +6168,7 @@
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C52" s="2">
         <v>45094.35106363426</v>
@@ -6171,13 +6186,13 @@
         <v>1309</v>
       </c>
       <c r="H52" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I52" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J52" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K52">
         <v>104</v>
@@ -6204,7 +6219,7 @@
         <v>27.56666667</v>
       </c>
       <c r="W52" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X52">
         <v>0.021111</v>
@@ -6236,7 +6251,7 @@
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C53" s="2">
         <v>45094.35141146991</v>
@@ -6254,13 +6269,13 @@
         <v>1339</v>
       </c>
       <c r="H53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I53" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J53" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K53">
         <v>121</v>
@@ -6287,7 +6302,7 @@
         <v>25.36666667</v>
       </c>
       <c r="W53" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X53">
         <v>-0.073333</v>
@@ -6319,7 +6334,7 @@
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C54" s="2">
         <v>45094.35175868055</v>
@@ -6337,13 +6352,13 @@
         <v>1369</v>
       </c>
       <c r="H54" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I54" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J54" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K54">
         <v>139</v>
@@ -6370,7 +6385,7 @@
         <v>26.66666667</v>
       </c>
       <c r="W54" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X54">
         <v>0.043333</v>
@@ -6402,7 +6417,7 @@
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C55" s="2">
         <v>45094.35210487268</v>
@@ -6420,13 +6435,13 @@
         <v>1399</v>
       </c>
       <c r="H55" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I55" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J55" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K55">
         <v>136</v>
@@ -6453,7 +6468,7 @@
         <v>26.06666667</v>
       </c>
       <c r="W55" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X55">
         <v>-0.02</v>
@@ -6485,7 +6500,7 @@
         <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C56" s="2">
         <v>45094.35228836806</v>
@@ -6503,13 +6518,13 @@
         <v>1414</v>
       </c>
       <c r="H56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J56" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K56">
         <v>122</v>
@@ -6536,7 +6551,7 @@
         <v>26.55333333</v>
       </c>
       <c r="W56" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X56">
         <v>0.003244</v>
@@ -6568,7 +6583,7 @@
         <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C57" s="2">
         <v>45094.35245263889</v>
@@ -6586,13 +6601,13 @@
         <v>1429</v>
       </c>
       <c r="H57" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I57" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J57" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K57">
         <v>118</v>
@@ -6619,7 +6634,7 @@
         <v>27.16666667</v>
       </c>
       <c r="W57" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X57">
         <v>0.020444</v>
@@ -6651,7 +6666,7 @@
         <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C58" s="2">
         <v>45094.3527999537</v>
@@ -6669,13 +6684,13 @@
         <v>1459</v>
       </c>
       <c r="H58" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I58" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J58" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K58">
         <v>114</v>
@@ -6702,7 +6717,7 @@
         <v>27.73333333</v>
       </c>
       <c r="W58" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X58">
         <v>0.018889</v>
@@ -6734,7 +6749,7 @@
         <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C59" s="2">
         <v>45094.35349449074</v>
@@ -6752,13 +6767,13 @@
         <v>1519</v>
       </c>
       <c r="H59" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I59" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J59" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K59">
         <v>119</v>
@@ -6785,7 +6800,7 @@
         <v>29.13333333</v>
       </c>
       <c r="W59" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X59">
         <v>0.023333</v>
@@ -6817,7 +6832,7 @@
         <v>25</v>
       </c>
       <c r="B60" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C60" s="2">
         <v>45094.35384116898</v>
@@ -6835,13 +6850,13 @@
         <v>1549</v>
       </c>
       <c r="H60" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I60" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J60" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K60">
         <v>114</v>
@@ -6868,7 +6883,7 @@
         <v>27.63333333</v>
       </c>
       <c r="W60" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X60">
         <v>-0.05</v>
@@ -6900,7 +6915,7 @@
         <v>25</v>
       </c>
       <c r="B61" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C61" s="2">
         <v>45094.35418881944</v>
@@ -6918,13 +6933,13 @@
         <v>1579</v>
       </c>
       <c r="H61" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I61" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J61" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K61">
         <v>124</v>
@@ -6951,7 +6966,7 @@
         <v>28.23333333</v>
       </c>
       <c r="W61" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X61">
         <v>0.02</v>
@@ -6983,7 +6998,7 @@
         <v>25</v>
       </c>
       <c r="B62" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C62" s="2">
         <v>45094.35453560185</v>
@@ -7001,13 +7016,13 @@
         <v>1609</v>
       </c>
       <c r="H62" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I62" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J62" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K62">
         <v>117</v>
@@ -7034,7 +7049,7 @@
         <v>30.7</v>
       </c>
       <c r="W62" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X62">
         <v>0.082222</v>
@@ -7066,7 +7081,7 @@
         <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C63" s="2">
         <v>45094.35472105324</v>
@@ -7084,13 +7099,13 @@
         <v>1624</v>
       </c>
       <c r="H63" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I63" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J63" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K63">
         <v>123</v>
@@ -7117,7 +7132,7 @@
         <v>28.52380952</v>
       </c>
       <c r="W63" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X63">
         <v>-0.010363</v>
@@ -7149,7 +7164,7 @@
         <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C64" s="2">
         <v>45094.35488359954</v>
@@ -7167,13 +7182,13 @@
         <v>1639</v>
       </c>
       <c r="H64" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I64" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J64" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K64">
         <v>119</v>
@@ -7200,7 +7215,7 @@
         <v>28.26666667</v>
       </c>
       <c r="W64" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X64">
         <v>-0.008571</v>
@@ -7232,7 +7247,7 @@
         <v>25</v>
       </c>
       <c r="B65" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C65" s="2">
         <v>45094.35523041667</v>
@@ -7250,13 +7265,13 @@
         <v>1669</v>
       </c>
       <c r="H65" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I65" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J65" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K65">
         <v>121</v>
@@ -7283,7 +7298,7 @@
         <v>28.43333333</v>
       </c>
       <c r="W65" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X65">
         <v>0.005556</v>
@@ -7315,7 +7330,7 @@
         <v>25</v>
       </c>
       <c r="B66" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C66" s="2">
         <v>45094.35557736111</v>
@@ -7333,13 +7348,13 @@
         <v>1699</v>
       </c>
       <c r="H66" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I66" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J66" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K66">
         <v>119</v>
@@ -7366,7 +7381,7 @@
         <v>29.56666667</v>
       </c>
       <c r="W66" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X66">
         <v>0.037778</v>
@@ -7398,7 +7413,7 @@
         <v>25</v>
       </c>
       <c r="B67" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C67" s="2">
         <v>45094.35592439815</v>
@@ -7416,13 +7431,13 @@
         <v>1729</v>
       </c>
       <c r="H67" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I67" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J67" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K67">
         <v>115</v>
@@ -7449,7 +7464,7 @@
         <v>27.96666667</v>
       </c>
       <c r="W67" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X67">
         <v>-0.053333</v>
@@ -7481,7 +7496,7 @@
         <v>25</v>
       </c>
       <c r="B68" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C68" s="2">
         <v>45094.35627298611</v>
@@ -7499,13 +7514,13 @@
         <v>1759</v>
       </c>
       <c r="H68" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I68" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J68" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K68">
         <v>120</v>
@@ -7532,7 +7547,7 @@
         <v>31.6</v>
       </c>
       <c r="W68" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X68">
         <v>0.121111</v>
@@ -7564,7 +7579,7 @@
         <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C69" s="2">
         <v>45094.35661945602</v>
@@ -7582,13 +7597,13 @@
         <v>1789</v>
       </c>
       <c r="H69" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I69" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J69" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K69">
         <v>116</v>
@@ -7615,7 +7630,7 @@
         <v>34.36666667</v>
       </c>
       <c r="W69" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X69">
         <v>0.092222</v>
@@ -7647,7 +7662,7 @@
         <v>25</v>
       </c>
       <c r="B70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C70" s="2">
         <v>45094.3569668287</v>
@@ -7665,13 +7680,13 @@
         <v>1819</v>
       </c>
       <c r="H70" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I70" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J70" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K70">
         <v>116</v>
@@ -7698,7 +7713,7 @@
         <v>30.46666667</v>
       </c>
       <c r="W70" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X70">
         <v>-0.13</v>
@@ -7730,7 +7745,7 @@
         <v>25</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C71" s="2">
         <v>45094.35731451389</v>
@@ -7748,13 +7763,13 @@
         <v>1849</v>
       </c>
       <c r="H71" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I71" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J71" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K71">
         <v>125</v>
@@ -7781,7 +7796,7 @@
         <v>20.53333333</v>
       </c>
       <c r="W71" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X71">
         <v>-0.331111</v>
@@ -7813,7 +7828,7 @@
         <v>25</v>
       </c>
       <c r="B72" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C72" s="2">
         <v>45094.3580084375</v>
@@ -7831,13 +7846,13 @@
         <v>1909</v>
       </c>
       <c r="H72" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I72" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J72" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K72">
         <v>112</v>
@@ -7864,7 +7879,7 @@
         <v>31.93333333</v>
       </c>
       <c r="W72" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X72">
         <v>0.19</v>
@@ -7896,7 +7911,7 @@
         <v>25</v>
       </c>
       <c r="B73" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C73" s="2">
         <v>45094.35835541667</v>
@@ -7914,13 +7929,13 @@
         <v>1939</v>
       </c>
       <c r="H73" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I73" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J73" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K73">
         <v>97</v>
@@ -7947,7 +7962,7 @@
         <v>32.63333333</v>
       </c>
       <c r="W73" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X73">
         <v>0.023333</v>
@@ -7979,7 +7994,7 @@
         <v>25</v>
       </c>
       <c r="B74" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C74" s="2">
         <v>45094.35870262732</v>
@@ -7997,13 +8012,13 @@
         <v>1969</v>
       </c>
       <c r="H74" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I74" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J74" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K74">
         <v>102</v>
@@ -8030,7 +8045,7 @@
         <v>25.8</v>
       </c>
       <c r="W74" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X74">
         <v>-0.227778</v>
@@ -8062,7 +8077,7 @@
         <v>25</v>
       </c>
       <c r="B75" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C75" s="2">
         <v>45094.35904986111</v>
@@ -8080,13 +8095,13 @@
         <v>1999</v>
       </c>
       <c r="H75" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I75" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J75" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K75">
         <v>111</v>
@@ -8113,7 +8128,7 @@
         <v>23.46666667</v>
       </c>
       <c r="W75" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X75">
         <v>-0.077778</v>
@@ -8145,7 +8160,7 @@
         <v>25</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C76" s="2">
         <v>45094.35939660879</v>
@@ -8163,13 +8178,13 @@
         <v>2029</v>
       </c>
       <c r="H76" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I76" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J76" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K76">
         <v>114</v>
@@ -8196,7 +8211,7 @@
         <v>26.86666667</v>
       </c>
       <c r="W76" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X76">
         <v>0.113333</v>
@@ -8228,7 +8243,7 @@
         <v>25</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C77" s="2">
         <v>45094.35974424768</v>
@@ -8246,13 +8261,13 @@
         <v>2059</v>
       </c>
       <c r="H77" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I77" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J77" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K77">
         <v>156</v>
@@ -8279,7 +8294,7 @@
         <v>28.2</v>
       </c>
       <c r="W77" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X77">
         <v>0.044444</v>
@@ -8311,7 +8326,7 @@
         <v>25</v>
       </c>
       <c r="B78" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C78" s="2">
         <v>45094.36043918981</v>
@@ -8329,13 +8344,13 @@
         <v>2119</v>
       </c>
       <c r="H78" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I78" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J78" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K78">
         <v>154</v>
@@ -8362,7 +8377,7 @@
         <v>31.26666667</v>
       </c>
       <c r="W78" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X78">
         <v>0.051111</v>
@@ -8394,7 +8409,7 @@
         <v>25</v>
       </c>
       <c r="B79" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C79" s="2">
         <v>45094.36078555555</v>
@@ -8412,13 +8427,13 @@
         <v>2149</v>
       </c>
       <c r="H79" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I79" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J79" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K79">
         <v>49</v>
@@ -8445,7 +8460,7 @@
         <v>38.76666667</v>
       </c>
       <c r="W79" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X79">
         <v>0.25</v>
@@ -8477,7 +8492,7 @@
         <v>25</v>
       </c>
       <c r="B80" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C80" s="2">
         <v>45094.36113313658</v>
@@ -8495,13 +8510,13 @@
         <v>2179</v>
       </c>
       <c r="H80" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I80" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J80" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K80">
         <v>82</v>
@@ -8528,7 +8543,7 @@
         <v>22.5</v>
       </c>
       <c r="W80" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X80">
         <v>-0.542222</v>
@@ -8555,12 +8570,12 @@
         <v>27.591262</v>
       </c>
     </row>
-    <row r="81" spans="1:31">
+    <row r="81" spans="1:32">
       <c r="A81" t="s">
         <v>25</v>
       </c>
       <c r="B81" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C81" s="2">
         <v>45094.36148015047</v>
@@ -8578,13 +8593,13 @@
         <v>2209</v>
       </c>
       <c r="H81" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I81" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J81" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K81">
         <v>38</v>
@@ -8611,7 +8626,7 @@
         <v>29.73333333</v>
       </c>
       <c r="W81" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X81">
         <v>0.241111</v>
@@ -8638,12 +8653,12 @@
         <v>27.239332</v>
       </c>
     </row>
-    <row r="82" spans="1:31">
+    <row r="82" spans="1:32">
       <c r="A82" t="s">
         <v>25</v>
       </c>
       <c r="B82" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C82" s="2">
         <v>45094.36182846065</v>
@@ -8661,13 +8676,13 @@
         <v>2239</v>
       </c>
       <c r="H82" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I82" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J82" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K82">
         <v>115</v>
@@ -8694,7 +8709,7 @@
         <v>24.7</v>
       </c>
       <c r="W82" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X82">
         <v>-0.167778</v>
@@ -8721,12 +8736,12 @@
         <v>26.928806</v>
       </c>
     </row>
-    <row r="83" spans="1:31">
+    <row r="83" spans="1:32">
       <c r="A83" t="s">
         <v>25</v>
       </c>
       <c r="B83" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C83" s="2">
         <v>45094.36217550926</v>
@@ -8744,13 +8759,13 @@
         <v>2269</v>
       </c>
       <c r="H83" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I83" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J83" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K83">
         <v>153</v>
@@ -8777,7 +8792,7 @@
         <v>28.5</v>
       </c>
       <c r="W83" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="X83">
         <v>0.126667</v>
@@ -8804,12 +8819,12 @@
         <v>26.551521</v>
       </c>
     </row>
-    <row r="84" spans="1:31">
+    <row r="84" spans="1:32">
       <c r="A84" t="s">
         <v>25</v>
       </c>
       <c r="B84" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C84" s="2">
         <v>45094.36252275463</v>
@@ -8827,13 +8842,13 @@
         <v>2299</v>
       </c>
       <c r="H84" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I84" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J84" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K84">
         <v>81</v>
@@ -8860,7 +8875,7 @@
         <v>28.83333333</v>
       </c>
       <c r="W84" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X84">
         <v>0.011111</v>
@@ -8886,13 +8901,16 @@
       <c r="AE84">
         <v>26.152101</v>
       </c>
-    </row>
-    <row r="85" spans="1:31">
+      <c r="AF84" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="85" spans="1:32">
       <c r="A85" t="s">
         <v>25</v>
       </c>
       <c r="B85" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C85" s="2">
         <v>45094.3628693287</v>
@@ -8910,13 +8928,13 @@
         <v>2329</v>
       </c>
       <c r="H85" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I85" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J85" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K85">
         <v>149</v>
@@ -8943,7 +8961,7 @@
         <v>23.53333333</v>
       </c>
       <c r="W85" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X85">
         <v>-0.176667</v>
@@ -8970,12 +8988,12 @@
         <v>25.816432</v>
       </c>
     </row>
-    <row r="86" spans="1:31">
+    <row r="86" spans="1:32">
       <c r="A86" t="s">
         <v>25</v>
       </c>
       <c r="B86" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C86" s="2">
         <v>45094.36321664352</v>
@@ -8993,13 +9011,13 @@
         <v>2359</v>
       </c>
       <c r="H86" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I86" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J86" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K86">
         <v>119</v>
@@ -9026,7 +9044,7 @@
         <v>24.53333333</v>
       </c>
       <c r="W86" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X86">
         <v>0.033333</v>
@@ -9053,12 +9071,12 @@
         <v>25.462031</v>
       </c>
     </row>
-    <row r="87" spans="1:31">
+    <row r="87" spans="1:32">
       <c r="A87" t="s">
         <v>25</v>
       </c>
       <c r="B87" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C87" s="2">
         <v>45094.36356399306</v>
@@ -9076,13 +9094,13 @@
         <v>2389</v>
       </c>
       <c r="H87" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I87" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J87" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K87">
         <v>175</v>
@@ -9109,7 +9127,7 @@
         <v>23.6</v>
       </c>
       <c r="W87" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X87">
         <v>-0.031111</v>
@@ -9136,12 +9154,12 @@
         <v>25.122634</v>
       </c>
     </row>
-    <row r="88" spans="1:31">
+    <row r="88" spans="1:32">
       <c r="A88" t="s">
         <v>25</v>
       </c>
       <c r="B88" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C88" s="2">
         <v>45094.36391078704</v>
@@ -9159,13 +9177,13 @@
         <v>2419</v>
       </c>
       <c r="H88" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I88" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J88" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K88">
         <v>345</v>
@@ -9192,7 +9210,7 @@
         <v>22.86666667</v>
       </c>
       <c r="W88" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X88">
         <v>-0.024444</v>
@@ -9219,12 +9237,12 @@
         <v>24.802015</v>
       </c>
     </row>
-    <row r="89" spans="1:31">
+    <row r="89" spans="1:32">
       <c r="A89" t="s">
         <v>25</v>
       </c>
       <c r="B89" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C89" s="2">
         <v>45094.36425849537</v>
@@ -9242,13 +9260,13 @@
         <v>2449</v>
       </c>
       <c r="H89" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I89" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J89" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K89">
         <v>109</v>
@@ -9275,7 +9293,7 @@
         <v>21.7</v>
       </c>
       <c r="W89" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X89">
         <v>-0.038889</v>
@@ -9302,12 +9320,12 @@
         <v>24.512351</v>
       </c>
     </row>
-    <row r="90" spans="1:31">
+    <row r="90" spans="1:32">
       <c r="A90" t="s">
         <v>25</v>
       </c>
       <c r="B90" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C90" s="2">
         <v>45094.36460600694</v>
@@ -9325,13 +9343,13 @@
         <v>2479</v>
       </c>
       <c r="H90" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I90" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J90" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K90">
         <v>70</v>
@@ -9358,7 +9376,7 @@
         <v>21.5</v>
       </c>
       <c r="W90" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X90">
         <v>-0.006667</v>
@@ -9385,12 +9403,12 @@
         <v>24.246865</v>
       </c>
     </row>
-    <row r="91" spans="1:31">
+    <row r="91" spans="1:32">
       <c r="A91" t="s">
         <v>25</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C91" s="2">
         <v>45094.365646875</v>
@@ -9408,13 +9426,13 @@
         <v>2569</v>
       </c>
       <c r="H91" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I91" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J91" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K91">
         <v>190</v>
@@ -9441,7 +9459,7 @@
         <v>27.68888889</v>
       </c>
       <c r="W91" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X91">
         <v>0.06876500000000001</v>
@@ -9468,12 +9486,12 @@
         <v>23.565805</v>
       </c>
     </row>
-    <row r="92" spans="1:31">
+    <row r="92" spans="1:32">
       <c r="A92" t="s">
         <v>25</v>
       </c>
       <c r="B92" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C92" s="2">
         <v>45094.36599543982</v>
@@ -9491,13 +9509,13 @@
         <v>2599</v>
       </c>
       <c r="H92" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I92" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J92" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K92">
         <v>280</v>
@@ -9524,7 +9542,7 @@
         <v>24.63333333</v>
       </c>
       <c r="W92" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X92">
         <v>-0.101852</v>
@@ -9551,12 +9569,12 @@
         <v>23.508605</v>
       </c>
     </row>
-    <row r="93" spans="1:31">
+    <row r="93" spans="1:32">
       <c r="A93" t="s">
         <v>25</v>
       </c>
       <c r="B93" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C93" s="2">
         <v>45094.36634144676</v>
@@ -9574,13 +9592,13 @@
         <v>2629</v>
       </c>
       <c r="H93" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I93" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J93" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K93">
         <v>278</v>
@@ -9607,7 +9625,7 @@
         <v>25</v>
       </c>
       <c r="W93" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X93">
         <v>0.012222</v>
@@ -9634,12 +9652,12 @@
         <v>23.528926</v>
       </c>
     </row>
-    <row r="94" spans="1:31">
+    <row r="94" spans="1:32">
       <c r="A94" t="s">
         <v>25</v>
       </c>
       <c r="B94" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C94" s="2">
         <v>45094.36668912037</v>
@@ -9657,13 +9675,13 @@
         <v>2659</v>
       </c>
       <c r="H94" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I94" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J94" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K94">
         <v>291</v>
@@ -9690,7 +9708,7 @@
         <v>24.86666667</v>
       </c>
       <c r="W94" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X94">
         <v>-0.004444</v>
@@ -9717,12 +9735,12 @@
         <v>23.62475</v>
       </c>
     </row>
-    <row r="95" spans="1:31">
+    <row r="95" spans="1:32">
       <c r="A95" t="s">
         <v>25</v>
       </c>
       <c r="B95" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C95" s="2">
         <v>45094.36703568287</v>
@@ -9740,13 +9758,13 @@
         <v>2689</v>
       </c>
       <c r="H95" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I95" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J95" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K95">
         <v>210</v>
@@ -9773,7 +9791,7 @@
         <v>24.23333333</v>
       </c>
       <c r="W95" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X95">
         <v>-0.021111</v>
@@ -9800,12 +9818,12 @@
         <v>23.780487</v>
       </c>
     </row>
-    <row r="96" spans="1:31">
+    <row r="96" spans="1:32">
       <c r="A96" t="s">
         <v>25</v>
       </c>
       <c r="B96" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C96" s="2">
         <v>45094.36738269676</v>
@@ -9823,13 +9841,13 @@
         <v>2719</v>
       </c>
       <c r="H96" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I96" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J96" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K96">
         <v>311</v>
@@ -9856,7 +9874,7 @@
         <v>24.6</v>
       </c>
       <c r="W96" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X96">
         <v>0.012222</v>
@@ -9888,7 +9906,7 @@
         <v>25</v>
       </c>
       <c r="B97" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C97" s="2">
         <v>45094.36773050926</v>
@@ -9906,13 +9924,13 @@
         <v>2749</v>
       </c>
       <c r="H97" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I97" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J97" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K97">
         <v>250</v>
@@ -9939,7 +9957,7 @@
         <v>22.43333333</v>
       </c>
       <c r="W97" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X97">
         <v>-0.07222199999999999</v>
@@ -9971,7 +9989,7 @@
         <v>25</v>
       </c>
       <c r="B98" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C98" s="2">
         <v>45094.36807675926</v>
@@ -9989,13 +10007,13 @@
         <v>2779</v>
       </c>
       <c r="H98" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I98" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J98" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K98">
         <v>260</v>
@@ -10022,7 +10040,7 @@
         <v>22.63333333</v>
       </c>
       <c r="W98" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X98">
         <v>0.006667</v>
@@ -10054,7 +10072,7 @@
         <v>25</v>
       </c>
       <c r="B99" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C99" s="2">
         <v>45094.36877180556</v>
@@ -10072,13 +10090,13 @@
         <v>2839</v>
       </c>
       <c r="H99" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I99" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J99" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K99">
         <v>248</v>
@@ -10105,7 +10123,7 @@
         <v>24.65</v>
       </c>
       <c r="W99" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X99">
         <v>0.033611</v>
@@ -10137,7 +10155,7 @@
         <v>25</v>
       </c>
       <c r="B100" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C100" s="2">
         <v>45094.36946652778</v>
@@ -10155,13 +10173,13 @@
         <v>2899</v>
       </c>
       <c r="H100" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I100" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J100" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K100">
         <v>290</v>
@@ -10188,7 +10206,7 @@
         <v>22.41666667</v>
       </c>
       <c r="W100" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X100">
         <v>-0.037222</v>
@@ -10220,7 +10238,7 @@
         <v>25</v>
       </c>
       <c r="B101" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C101" s="2">
         <v>45094.36981353009</v>
@@ -10238,13 +10256,13 @@
         <v>2929</v>
       </c>
       <c r="H101" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I101" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J101" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K101">
         <v>289</v>
@@ -10271,7 +10289,7 @@
         <v>24.73333333</v>
       </c>
       <c r="W101" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X101">
         <v>0.077222</v>
@@ -10303,7 +10321,7 @@
         <v>25</v>
       </c>
       <c r="B102" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C102" s="2">
         <v>45094.37016189815</v>
@@ -10321,13 +10339,13 @@
         <v>2959</v>
       </c>
       <c r="H102" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I102" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J102" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K102">
         <v>295</v>
@@ -10354,7 +10372,7 @@
         <v>23.76666667</v>
       </c>
       <c r="W102" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X102">
         <v>-0.032222</v>
@@ -10386,7 +10404,7 @@
         <v>25</v>
       </c>
       <c r="B103" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C103" s="2">
         <v>45094.37050813658</v>
@@ -10404,13 +10422,13 @@
         <v>2989</v>
       </c>
       <c r="H103" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I103" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J103" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K103">
         <v>276</v>
@@ -10437,7 +10455,7 @@
         <v>24.23333333</v>
       </c>
       <c r="W103" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X103">
         <v>0.015556</v>
@@ -10469,7 +10487,7 @@
         <v>25</v>
       </c>
       <c r="B104" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C104" s="2">
         <v>45094.37085590278</v>
@@ -10487,13 +10505,13 @@
         <v>3019</v>
       </c>
       <c r="H104" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I104" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J104" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K104">
         <v>328</v>
@@ -10520,7 +10538,7 @@
         <v>24.46666667</v>
       </c>
       <c r="W104" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X104">
         <v>0.007778</v>
@@ -10552,7 +10570,7 @@
         <v>25</v>
       </c>
       <c r="B105" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C105" s="2">
         <v>45094.37120224537</v>
@@ -10570,13 +10588,13 @@
         <v>3049</v>
       </c>
       <c r="H105" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I105" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J105" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K105">
         <v>311</v>
@@ -10603,7 +10621,7 @@
         <v>23.73333333</v>
       </c>
       <c r="W105" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="X105">
         <v>-0.024444</v>
@@ -10637,10 +10655,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE89"/>
+  <dimension ref="A1:AF89"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -10734,13 +10752,16 @@
       <c r="AE1" s="1" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="2" spans="1:31">
+      <c r="AF1" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C2" s="2">
         <v>45094.37155011574</v>
@@ -10758,13 +10779,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="J2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K2">
         <v>318</v>
@@ -10791,7 +10812,7 @@
         <v>-33.13333333</v>
       </c>
       <c r="W2" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="Y2">
         <v>-33.133333</v>
@@ -10800,12 +10821,12 @@
         <v>-33.108959</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2">
         <v>45094.37189753472</v>
@@ -10823,13 +10844,13 @@
         <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I3" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="J3" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="K3">
         <v>297</v>
@@ -10856,7 +10877,7 @@
         <v>-51.76666667</v>
       </c>
       <c r="W3" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X3">
         <v>-0.621111</v>
@@ -10877,12 +10898,12 @@
         <v>-51.848209</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C4" s="2">
         <v>45094.37259148148</v>
@@ -10900,13 +10921,13 @@
         <v>90</v>
       </c>
       <c r="H4" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I4" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="J4" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="K4">
         <v>272</v>
@@ -10933,7 +10954,7 @@
         <v>-45.38333333</v>
       </c>
       <c r="W4" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X4">
         <v>0.106389</v>
@@ -10960,12 +10981,12 @@
         <v>-45.252176</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" s="2">
         <v>45094.37328638889</v>
@@ -10983,13 +11004,13 @@
         <v>150</v>
       </c>
       <c r="H5" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I5" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="J5" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="K5">
         <v>280</v>
@@ -11016,7 +11037,7 @@
         <v>-41.38333333</v>
       </c>
       <c r="W5" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X5">
         <v>0.066667</v>
@@ -11043,12 +11064,12 @@
         <v>-41.772975</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C6" s="2">
         <v>45094.37363313657</v>
@@ -11066,13 +11087,13 @@
         <v>180</v>
       </c>
       <c r="H6" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I6" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="J6" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="K6">
         <v>235</v>
@@ -11099,7 +11120,7 @@
         <v>-43.8</v>
       </c>
       <c r="W6" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X6">
         <v>-0.080556</v>
@@ -11126,12 +11147,12 @@
         <v>-41.330664</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2">
         <v>45094.37398188657</v>
@@ -11149,13 +11170,13 @@
         <v>210</v>
       </c>
       <c r="H7" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I7" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="J7" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="K7">
         <v>238</v>
@@ -11182,7 +11203,7 @@
         <v>-36.96666667</v>
       </c>
       <c r="W7" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X7">
         <v>0.227778</v>
@@ -11209,12 +11230,12 @@
         <v>-40.80953</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:32">
       <c r="A8" t="s">
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" s="2">
         <v>45094.37467542824</v>
@@ -11232,13 +11253,13 @@
         <v>270</v>
       </c>
       <c r="H8" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I8" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J8" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="K8">
         <v>194</v>
@@ -11265,7 +11286,7 @@
         <v>-40.2</v>
       </c>
       <c r="W8" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X8">
         <v>-0.053889</v>
@@ -11292,12 +11313,12 @@
         <v>-38.227058</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:32">
       <c r="A9" t="s">
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" s="2">
         <v>45094.37502232639</v>
@@ -11315,13 +11336,13 @@
         <v>300</v>
       </c>
       <c r="H9" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I9" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="J9" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="K9">
         <v>140</v>
@@ -11348,7 +11369,7 @@
         <v>-38.36666667</v>
       </c>
       <c r="W9" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X9">
         <v>0.061111</v>
@@ -11375,12 +11396,12 @@
         <v>-36.507823</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:32">
       <c r="A10" t="s">
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" s="2">
         <v>45094.37536953704</v>
@@ -11398,13 +11419,13 @@
         <v>330</v>
       </c>
       <c r="H10" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I10" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="J10" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="K10">
         <v>30</v>
@@ -11431,7 +11452,7 @@
         <v>-32.26666667</v>
       </c>
       <c r="W10" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X10">
         <v>0.203333</v>
@@ -11458,12 +11479,12 @@
         <v>-35.069966</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:32">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" s="2">
         <v>45094.37571655092</v>
@@ -11481,13 +11502,13 @@
         <v>360</v>
       </c>
       <c r="H11" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I11" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="J11" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="K11">
         <v>174</v>
@@ -11514,7 +11535,7 @@
         <v>-35.63333333</v>
       </c>
       <c r="W11" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X11">
         <v>-0.112222</v>
@@ -11541,12 +11562,12 @@
         <v>-33.678321</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:32">
       <c r="A12" t="s">
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" s="2">
         <v>45094.37606354167</v>
@@ -11564,13 +11585,13 @@
         <v>390</v>
       </c>
       <c r="H12" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I12" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="J12" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="K12">
         <v>25</v>
@@ -11597,7 +11618,7 @@
         <v>-33.16666667</v>
       </c>
       <c r="W12" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X12">
         <v>0.082222</v>
@@ -11624,12 +11645,12 @@
         <v>-32.686875</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:32">
       <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" s="2">
         <v>45094.37641184028</v>
@@ -11647,13 +11668,13 @@
         <v>420</v>
       </c>
       <c r="H13" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I13" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="J13" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="K13">
         <v>39</v>
@@ -11680,7 +11701,7 @@
         <v>-30.96666667</v>
       </c>
       <c r="W13" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X13">
         <v>0.073333</v>
@@ -11707,12 +11728,12 @@
         <v>-32.07369</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:32">
       <c r="A14" t="s">
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" s="2">
         <v>45094.37675826389</v>
@@ -11730,13 +11751,13 @@
         <v>450</v>
       </c>
       <c r="H14" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I14" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="J14" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="K14">
         <v>66</v>
@@ -11763,7 +11784,7 @@
         <v>-28.46666667</v>
       </c>
       <c r="W14" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X14">
         <v>0.083333</v>
@@ -11790,12 +11811,12 @@
         <v>-31.771777</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:32">
       <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C15" s="2">
         <v>45094.3771059838</v>
@@ -11813,13 +11834,13 @@
         <v>480</v>
       </c>
       <c r="H15" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I15" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="J15" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="K15">
         <v>94</v>
@@ -11846,7 +11867,7 @@
         <v>-31.83333333</v>
       </c>
       <c r="W15" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X15">
         <v>-0.112222</v>
@@ -11873,12 +11894,12 @@
         <v>-31.686312</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:32">
       <c r="A16" t="s">
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" s="2">
         <v>45094.37745237268</v>
@@ -11896,13 +11917,13 @@
         <v>510</v>
       </c>
       <c r="H16" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I16" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="J16" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="K16">
         <v>82</v>
@@ -11929,7 +11950,7 @@
         <v>-34.53333333</v>
       </c>
       <c r="W16" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X16">
         <v>-0.09</v>
@@ -11961,7 +11982,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C17" s="2">
         <v>45094.37918865741</v>
@@ -11979,13 +12000,13 @@
         <v>660</v>
       </c>
       <c r="H17" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I17" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="J17" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="K17">
         <v>131</v>
@@ -12012,7 +12033,7 @@
         <v>-33.04</v>
       </c>
       <c r="W17" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X17">
         <v>0.009956</v>
@@ -12044,7 +12065,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18" s="2">
         <v>45094.37953603009</v>
@@ -12062,13 +12083,13 @@
         <v>690</v>
       </c>
       <c r="H18" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I18" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="J18" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="K18">
         <v>121</v>
@@ -12095,7 +12116,7 @@
         <v>-29.96666667</v>
       </c>
       <c r="W18" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X18">
         <v>0.102444</v>
@@ -12127,7 +12148,7 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C19" s="2">
         <v>45094.3798837963</v>
@@ -12145,13 +12166,13 @@
         <v>720</v>
       </c>
       <c r="H19" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I19" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="J19" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="K19">
         <v>97</v>
@@ -12178,7 +12199,7 @@
         <v>-29.46666667</v>
       </c>
       <c r="W19" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X19">
         <v>0.016667</v>
@@ -12210,7 +12231,7 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C20" s="2">
         <v>45094.38057789352</v>
@@ -12228,13 +12249,13 @@
         <v>780</v>
       </c>
       <c r="H20" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I20" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="J20" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="K20">
         <v>114</v>
@@ -12261,7 +12282,7 @@
         <v>-28.15</v>
       </c>
       <c r="W20" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X20">
         <v>0.021944</v>
@@ -12293,7 +12314,7 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21" s="2">
         <v>45094.38092582176</v>
@@ -12311,13 +12332,13 @@
         <v>810</v>
       </c>
       <c r="H21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I21" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="J21" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="K21">
         <v>122</v>
@@ -12344,7 +12365,7 @@
         <v>-27.5</v>
       </c>
       <c r="W21" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X21">
         <v>0.021667</v>
@@ -12376,7 +12397,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C22" s="2">
         <v>45094.38148519676</v>
@@ -12394,13 +12415,13 @@
         <v>840</v>
       </c>
       <c r="H22" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I22" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="J22" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="K22">
         <v>124</v>
@@ -12427,7 +12448,7 @@
         <v>-26.06666667</v>
       </c>
       <c r="W22" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X22">
         <v>0.047778</v>
@@ -12459,7 +12480,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C23" s="2">
         <v>45094.3816187037</v>
@@ -12477,13 +12498,13 @@
         <v>870</v>
       </c>
       <c r="H23" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I23" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="J23" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="K23">
         <v>123</v>
@@ -12510,7 +12531,7 @@
         <v>-25.4</v>
       </c>
       <c r="W23" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X23">
         <v>0.022222</v>
@@ -12542,7 +12563,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C24" s="2">
         <v>45094.38196700231</v>
@@ -12560,13 +12581,13 @@
         <v>900</v>
       </c>
       <c r="H24" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I24" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="J24" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="K24">
         <v>114</v>
@@ -12593,7 +12614,7 @@
         <v>-21.96666667</v>
       </c>
       <c r="W24" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X24">
         <v>0.114444</v>
@@ -12625,7 +12646,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C25" s="2">
         <v>45094.38231439815</v>
@@ -12643,13 +12664,13 @@
         <v>930</v>
       </c>
       <c r="H25" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I25" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="J25" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="K25">
         <v>115</v>
@@ -12676,7 +12697,7 @@
         <v>-23.2</v>
       </c>
       <c r="W25" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X25">
         <v>-0.041111</v>
@@ -12708,7 +12729,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C26" s="2">
         <v>45094.38300857639</v>
@@ -12726,13 +12747,13 @@
         <v>990</v>
       </c>
       <c r="H26" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I26" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="J26" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="K26">
         <v>121</v>
@@ -12759,7 +12780,7 @@
         <v>-22.96666667</v>
       </c>
       <c r="W26" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X26">
         <v>0.003889</v>
@@ -12791,7 +12812,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C27" s="2">
         <v>45094.38335523148</v>
@@ -12809,13 +12830,13 @@
         <v>1020</v>
       </c>
       <c r="H27" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I27" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="J27" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="K27">
         <v>115</v>
@@ -12842,7 +12863,7 @@
         <v>-22.63333333</v>
       </c>
       <c r="W27" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X27">
         <v>0.011111</v>
@@ -12874,7 +12895,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" s="2">
         <v>45094.38370341435</v>
@@ -12892,13 +12913,13 @@
         <v>1050</v>
       </c>
       <c r="H28" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I28" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="J28" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K28">
         <v>120</v>
@@ -12925,7 +12946,7 @@
         <v>-21.66666667</v>
       </c>
       <c r="W28" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X28">
         <v>0.032222</v>
@@ -12957,7 +12978,7 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C29" s="2">
         <v>45094.38405054398</v>
@@ -12975,13 +12996,13 @@
         <v>1080</v>
       </c>
       <c r="H29" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I29" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="J29" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="K29">
         <v>120</v>
@@ -13008,7 +13029,7 @@
         <v>-21.6</v>
       </c>
       <c r="W29" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X29">
         <v>0.002222</v>
@@ -13040,7 +13061,7 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C30" s="2">
         <v>45094.38439748843</v>
@@ -13058,13 +13079,13 @@
         <v>1110</v>
       </c>
       <c r="H30" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I30" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="J30" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="K30">
         <v>116</v>
@@ -13091,7 +13112,7 @@
         <v>-21.26666667</v>
       </c>
       <c r="W30" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X30">
         <v>0.011111</v>
@@ -13123,7 +13144,7 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="2">
         <v>45094.38474394676</v>
@@ -13141,13 +13162,13 @@
         <v>1140</v>
       </c>
       <c r="H31" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I31" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="J31" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="K31">
         <v>118</v>
@@ -13174,7 +13195,7 @@
         <v>-21</v>
       </c>
       <c r="W31" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X31">
         <v>0.008888999999999999</v>
@@ -13206,7 +13227,7 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C32" s="2">
         <v>45094.38543905093</v>
@@ -13224,13 +13245,13 @@
         <v>1200</v>
       </c>
       <c r="H32" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I32" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="J32" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="K32">
         <v>125</v>
@@ -13257,7 +13278,7 @@
         <v>-20.21666667</v>
       </c>
       <c r="W32" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X32">
         <v>0.013056</v>
@@ -13289,7 +13310,7 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C33" s="2">
         <v>45094.38578665509</v>
@@ -13307,13 +13328,13 @@
         <v>1230</v>
       </c>
       <c r="H33" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I33" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="J33" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="K33">
         <v>125</v>
@@ -13340,7 +13361,7 @@
         <v>-19.16666667</v>
       </c>
       <c r="W33" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X33">
         <v>0.035</v>
@@ -13372,7 +13393,7 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C34" s="2">
         <v>45094.3861330787</v>
@@ -13390,13 +13411,13 @@
         <v>1260</v>
       </c>
       <c r="H34" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I34" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="J34" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="K34">
         <v>122</v>
@@ -13423,7 +13444,7 @@
         <v>-19.26666667</v>
       </c>
       <c r="W34" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X34">
         <v>-0.003333</v>
@@ -13455,7 +13476,7 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C35" s="2">
         <v>45094.38648175926</v>
@@ -13473,13 +13494,13 @@
         <v>1290</v>
       </c>
       <c r="H35" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I35" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J35" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="K35">
         <v>115</v>
@@ -13506,7 +13527,7 @@
         <v>-19</v>
       </c>
       <c r="W35" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X35">
         <v>0.008888999999999999</v>
@@ -13538,7 +13559,7 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C36" s="2">
         <v>45094.38682829861</v>
@@ -13556,13 +13577,13 @@
         <v>1320</v>
       </c>
       <c r="H36" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I36" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="J36" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="K36">
         <v>114</v>
@@ -13589,7 +13610,7 @@
         <v>-18.73333333</v>
       </c>
       <c r="W36" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X36">
         <v>0.008888999999999999</v>
@@ -13621,7 +13642,7 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C37" s="2">
         <v>45094.38717591435</v>
@@ -13639,13 +13660,13 @@
         <v>1350</v>
       </c>
       <c r="H37" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I37" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="J37" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="K37">
         <v>121</v>
@@ -13672,7 +13693,7 @@
         <v>-18.63333333</v>
       </c>
       <c r="W37" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X37">
         <v>0.003333</v>
@@ -13704,7 +13725,7 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C38" s="2">
         <v>45094.38752283565</v>
@@ -13722,13 +13743,13 @@
         <v>1380</v>
       </c>
       <c r="H38" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I38" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="J38" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="K38">
         <v>130</v>
@@ -13755,7 +13776,7 @@
         <v>-18.9</v>
       </c>
       <c r="W38" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X38">
         <v>-0.008888999999999999</v>
@@ -13787,7 +13808,7 @@
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C39" s="2">
         <v>45094.38787030092</v>
@@ -13805,13 +13826,13 @@
         <v>1410</v>
       </c>
       <c r="H39" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I39" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="J39" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="K39">
         <v>130</v>
@@ -13838,7 +13859,7 @@
         <v>-18.2</v>
       </c>
       <c r="W39" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X39">
         <v>0.023333</v>
@@ -13870,7 +13891,7 @@
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C40" s="2">
         <v>45094.38821748843</v>
@@ -13888,13 +13909,13 @@
         <v>1440</v>
       </c>
       <c r="H40" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I40" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="J40" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="K40">
         <v>129</v>
@@ -13921,7 +13942,7 @@
         <v>-18</v>
       </c>
       <c r="W40" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X40">
         <v>0.006667</v>
@@ -13953,7 +13974,7 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C41" s="2">
         <v>45094.38856420139</v>
@@ -13971,13 +13992,13 @@
         <v>1470</v>
       </c>
       <c r="H41" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I41" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="J41" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="K41">
         <v>129</v>
@@ -14004,7 +14025,7 @@
         <v>-18.5</v>
       </c>
       <c r="W41" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X41">
         <v>-0.016667</v>
@@ -14036,7 +14057,7 @@
         <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C42" s="2">
         <v>45094.38891199074</v>
@@ -14054,13 +14075,13 @@
         <v>1500</v>
       </c>
       <c r="H42" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I42" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="J42" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="K42">
         <v>118</v>
@@ -14087,7 +14108,7 @@
         <v>-18.56666667</v>
       </c>
       <c r="W42" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X42">
         <v>-0.002222</v>
@@ -14119,7 +14140,7 @@
         <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C43" s="2">
         <v>45094.38925871528</v>
@@ -14137,13 +14158,13 @@
         <v>1530</v>
       </c>
       <c r="H43" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I43" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="J43" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="K43">
         <v>106</v>
@@ -14170,7 +14191,7 @@
         <v>-17.96666667</v>
       </c>
       <c r="W43" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X43">
         <v>0.02</v>
@@ -14202,7 +14223,7 @@
         <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C44" s="2">
         <v>45094.38960546297</v>
@@ -14220,13 +14241,13 @@
         <v>1560</v>
       </c>
       <c r="H44" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I44" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="J44" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="K44">
         <v>108</v>
@@ -14253,7 +14274,7 @@
         <v>-17.26666667</v>
       </c>
       <c r="W44" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X44">
         <v>0.023333</v>
@@ -14285,7 +14306,7 @@
         <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C45" s="2">
         <v>45094.38995331019</v>
@@ -14303,13 +14324,13 @@
         <v>1590</v>
       </c>
       <c r="H45" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I45" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="J45" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K45">
         <v>102</v>
@@ -14336,7 +14357,7 @@
         <v>-17.26666667</v>
       </c>
       <c r="W45" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X45">
         <v>0</v>
@@ -14368,7 +14389,7 @@
         <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C46" s="2">
         <v>45094.39030013889</v>
@@ -14386,13 +14407,13 @@
         <v>1620</v>
       </c>
       <c r="H46" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I46" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="J46" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="K46">
         <v>107</v>
@@ -14419,7 +14440,7 @@
         <v>-16.73333333</v>
       </c>
       <c r="W46" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X46">
         <v>0.017778</v>
@@ -14451,7 +14472,7 @@
         <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C47" s="2">
         <v>45094.39064818287</v>
@@ -14469,13 +14490,13 @@
         <v>1650</v>
       </c>
       <c r="H47" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I47" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="J47" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="K47">
         <v>110</v>
@@ -14502,7 +14523,7 @@
         <v>-16.83333333</v>
       </c>
       <c r="W47" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X47">
         <v>-0.003333</v>
@@ -14534,7 +14555,7 @@
         <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C48" s="2">
         <v>45094.39099511574</v>
@@ -14552,13 +14573,13 @@
         <v>1680</v>
       </c>
       <c r="H48" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I48" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="J48" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="K48">
         <v>111</v>
@@ -14585,7 +14606,7 @@
         <v>-16.9</v>
       </c>
       <c r="W48" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X48">
         <v>-0.002222</v>
@@ -14617,7 +14638,7 @@
         <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C49" s="2">
         <v>45094.39203666666</v>
@@ -14635,13 +14656,13 @@
         <v>1770</v>
       </c>
       <c r="H49" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I49" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="J49" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="K49">
         <v>106</v>
@@ -14668,7 +14689,7 @@
         <v>-14.71111111</v>
       </c>
       <c r="W49" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X49">
         <v>0.024321</v>
@@ -14700,7 +14721,7 @@
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C50" s="2">
         <v>45094.39239282408</v>
@@ -14718,13 +14739,13 @@
         <v>1800</v>
       </c>
       <c r="H50" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I50" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="J50" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="K50">
         <v>137</v>
@@ -14751,7 +14772,7 @@
         <v>-12.53333333</v>
       </c>
       <c r="W50" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X50">
         <v>0.072593</v>
@@ -14783,7 +14804,7 @@
         <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C51" s="2">
         <v>45094.39273111111</v>
@@ -14801,13 +14822,13 @@
         <v>1830</v>
       </c>
       <c r="H51" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I51" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="J51" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="K51">
         <v>98</v>
@@ -14834,7 +14855,7 @@
         <v>-12.7</v>
       </c>
       <c r="W51" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X51">
         <v>-0.005556</v>
@@ -14866,7 +14887,7 @@
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C52" s="2">
         <v>45094.39307847223</v>
@@ -14884,13 +14905,13 @@
         <v>1860</v>
       </c>
       <c r="H52" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I52" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="J52" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="K52">
         <v>129</v>
@@ -14917,7 +14938,7 @@
         <v>-13.1</v>
       </c>
       <c r="W52" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X52">
         <v>-0.013333</v>
@@ -14949,7 +14970,7 @@
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C53" s="2">
         <v>45094.39342516204</v>
@@ -14967,13 +14988,13 @@
         <v>1890</v>
       </c>
       <c r="H53" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I53" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="J53" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="K53">
         <v>99</v>
@@ -15000,7 +15021,7 @@
         <v>-11.9</v>
       </c>
       <c r="W53" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X53">
         <v>0.04</v>
@@ -15032,7 +15053,7 @@
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C54" s="2">
         <v>45094.39377326389</v>
@@ -15050,13 +15071,13 @@
         <v>1920</v>
       </c>
       <c r="H54" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I54" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="J54" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="K54">
         <v>112</v>
@@ -15083,7 +15104,7 @@
         <v>-12.1</v>
       </c>
       <c r="W54" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X54">
         <v>-0.006667</v>
@@ -15115,7 +15136,7 @@
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C55" s="2">
         <v>45094.39446917824</v>
@@ -15133,13 +15154,13 @@
         <v>1980</v>
       </c>
       <c r="H55" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I55" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="J55" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="K55">
         <v>99</v>
@@ -15166,7 +15187,7 @@
         <v>-12.01666667</v>
       </c>
       <c r="W55" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X55">
         <v>0.001389</v>
@@ -15198,7 +15219,7 @@
         <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C56" s="2">
         <v>45094.39487491898</v>
@@ -15216,13 +15237,13 @@
         <v>2010</v>
       </c>
       <c r="H56" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I56" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="J56" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="K56">
         <v>162</v>
@@ -15249,7 +15270,7 @@
         <v>-11.76666667</v>
       </c>
       <c r="W56" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X56">
         <v>0.008333</v>
@@ -15281,7 +15302,7 @@
         <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C57" s="2">
         <v>45094.39516130787</v>
@@ -15299,13 +15320,13 @@
         <v>2040</v>
       </c>
       <c r="H57" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I57" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="J57" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="K57">
         <v>100</v>
@@ -15332,7 +15353,7 @@
         <v>-11.9</v>
       </c>
       <c r="W57" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X57">
         <v>-0.004444</v>
@@ -15364,7 +15385,7 @@
         <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C58" s="2">
         <v>45094.39551729167</v>
@@ -15382,13 +15403,13 @@
         <v>2070</v>
       </c>
       <c r="H58" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I58" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="J58" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="K58">
         <v>169</v>
@@ -15415,7 +15436,7 @@
         <v>-11.8</v>
       </c>
       <c r="W58" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X58">
         <v>0.003333</v>
@@ -15447,7 +15468,7 @@
         <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C59" s="2">
         <v>45094.3958559838</v>
@@ -15465,13 +15486,13 @@
         <v>2100</v>
       </c>
       <c r="H59" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I59" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="J59" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="K59">
         <v>113</v>
@@ -15498,7 +15519,7 @@
         <v>-11.9</v>
       </c>
       <c r="W59" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X59">
         <v>-0.003333</v>
@@ -15530,7 +15551,7 @@
         <v>25</v>
       </c>
       <c r="B60" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C60" s="2">
         <v>45094.39620366898</v>
@@ -15548,13 +15569,13 @@
         <v>2130</v>
       </c>
       <c r="H60" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I60" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="J60" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="K60">
         <v>162</v>
@@ -15581,7 +15602,7 @@
         <v>-12.56666667</v>
       </c>
       <c r="W60" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X60">
         <v>-0.022222</v>
@@ -15613,7 +15634,7 @@
         <v>25</v>
       </c>
       <c r="B61" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C61" s="2">
         <v>45094.39654993056</v>
@@ -15631,13 +15652,13 @@
         <v>2160</v>
       </c>
       <c r="H61" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I61" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="J61" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="K61">
         <v>101</v>
@@ -15664,7 +15685,7 @@
         <v>-11.73333333</v>
       </c>
       <c r="W61" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X61">
         <v>0.027778</v>
@@ -15696,7 +15717,7 @@
         <v>25</v>
       </c>
       <c r="B62" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C62" s="2">
         <v>45094.3975924537</v>
@@ -15714,13 +15735,13 @@
         <v>2250</v>
       </c>
       <c r="H62" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I62" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="J62" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K62">
         <v>171</v>
@@ -15747,7 +15768,7 @@
         <v>-11.46666667</v>
       </c>
       <c r="W62" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X62">
         <v>0.002963</v>
@@ -15779,7 +15800,7 @@
         <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C63" s="2">
         <v>45094.39793901621</v>
@@ -15797,13 +15818,13 @@
         <v>2280</v>
       </c>
       <c r="H63" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I63" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="J63" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="K63">
         <v>139</v>
@@ -15830,7 +15851,7 @@
         <v>-11.13333333</v>
       </c>
       <c r="W63" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X63">
         <v>0.011111</v>
@@ -15862,7 +15883,7 @@
         <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C64" s="2">
         <v>45094.3982862037</v>
@@ -15880,13 +15901,13 @@
         <v>2310</v>
       </c>
       <c r="H64" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I64" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="J64" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="K64">
         <v>114</v>
@@ -15913,7 +15934,7 @@
         <v>-11.26666667</v>
       </c>
       <c r="W64" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X64">
         <v>-0.004444</v>
@@ -15945,7 +15966,7 @@
         <v>25</v>
       </c>
       <c r="B65" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C65" s="2">
         <v>45094.39863377315</v>
@@ -15963,13 +15984,13 @@
         <v>2340</v>
       </c>
       <c r="H65" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I65" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="J65" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="K65">
         <v>171</v>
@@ -15996,7 +16017,7 @@
         <v>-11.06666667</v>
       </c>
       <c r="W65" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X65">
         <v>0.006667</v>
@@ -16028,7 +16049,7 @@
         <v>25</v>
       </c>
       <c r="B66" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C66" s="2">
         <v>45094.39898017361</v>
@@ -16046,13 +16067,13 @@
         <v>2370</v>
       </c>
       <c r="H66" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I66" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="J66" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="K66">
         <v>140</v>
@@ -16079,7 +16100,7 @@
         <v>-11</v>
       </c>
       <c r="W66" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X66">
         <v>0.002222</v>
@@ -16111,7 +16132,7 @@
         <v>25</v>
       </c>
       <c r="B67" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C67" s="2">
         <v>45094.39932827546</v>
@@ -16129,13 +16150,13 @@
         <v>2400</v>
       </c>
       <c r="H67" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I67" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="J67" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="K67">
         <v>93</v>
@@ -16162,7 +16183,7 @@
         <v>-10.46666667</v>
       </c>
       <c r="W67" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X67">
         <v>0.017778</v>
@@ -16194,7 +16215,7 @@
         <v>25</v>
       </c>
       <c r="B68" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C68" s="2">
         <v>45094.40002246528</v>
@@ -16212,13 +16233,13 @@
         <v>2460</v>
       </c>
       <c r="H68" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I68" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="J68" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="K68">
         <v>156</v>
@@ -16245,7 +16266,7 @@
         <v>-10.23333333</v>
       </c>
       <c r="W68" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X68">
         <v>0.003889</v>
@@ -16277,7 +16298,7 @@
         <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C69" s="2">
         <v>45094.40036984954</v>
@@ -16295,13 +16316,13 @@
         <v>2490</v>
       </c>
       <c r="H69" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I69" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="J69" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="K69">
         <v>149</v>
@@ -16328,7 +16349,7 @@
         <v>-9.866666670000001</v>
       </c>
       <c r="W69" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X69">
         <v>0.012222</v>
@@ -16360,7 +16381,7 @@
         <v>25</v>
       </c>
       <c r="B70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C70" s="2">
         <v>45094.40071681713</v>
@@ -16378,13 +16399,13 @@
         <v>2520</v>
       </c>
       <c r="H70" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I70" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="J70" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="K70">
         <v>131</v>
@@ -16411,7 +16432,7 @@
         <v>-10.1</v>
       </c>
       <c r="W70" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X70">
         <v>-0.007778</v>
@@ -16443,7 +16464,7 @@
         <v>25</v>
       </c>
       <c r="B71" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C71" s="2">
         <v>45094.4010644213</v>
@@ -16461,13 +16482,13 @@
         <v>2550</v>
       </c>
       <c r="H71" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I71" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="J71" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="K71">
         <v>134</v>
@@ -16494,7 +16515,7 @@
         <v>-9.83333333</v>
       </c>
       <c r="W71" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X71">
         <v>0.008888999999999999</v>
@@ -16526,7 +16547,7 @@
         <v>25</v>
       </c>
       <c r="B72" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C72" s="2">
         <v>45094.40141065972</v>
@@ -16544,13 +16565,13 @@
         <v>2580</v>
       </c>
       <c r="H72" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I72" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="J72" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="K72">
         <v>147</v>
@@ -16577,7 +16598,7 @@
         <v>-9.66666667</v>
       </c>
       <c r="W72" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X72">
         <v>0.005556</v>
@@ -16609,7 +16630,7 @@
         <v>25</v>
       </c>
       <c r="B73" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C73" s="2">
         <v>45094.40175862268</v>
@@ -16627,13 +16648,13 @@
         <v>2610</v>
       </c>
       <c r="H73" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I73" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="J73" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K73">
         <v>129</v>
@@ -16660,7 +16681,7 @@
         <v>-9.66666667</v>
       </c>
       <c r="W73" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X73">
         <v>0</v>
@@ -16692,7 +16713,7 @@
         <v>25</v>
       </c>
       <c r="B74" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C74" s="2">
         <v>45094.40245278935</v>
@@ -16710,13 +16731,13 @@
         <v>2670</v>
       </c>
       <c r="H74" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I74" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="J74" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="K74">
         <v>131</v>
@@ -16743,7 +16764,7 @@
         <v>-9.68333333</v>
       </c>
       <c r="W74" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X74">
         <v>-0.000278</v>
@@ -16775,7 +16796,7 @@
         <v>25</v>
       </c>
       <c r="B75" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C75" s="2">
         <v>45094.40279944445</v>
@@ -16793,13 +16814,13 @@
         <v>2700</v>
       </c>
       <c r="H75" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I75" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="J75" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="K75">
         <v>121</v>
@@ -16826,7 +16847,7 @@
         <v>-9.733333330000001</v>
       </c>
       <c r="W75" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X75">
         <v>-0.001667</v>
@@ -16858,7 +16879,7 @@
         <v>25</v>
       </c>
       <c r="B76" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C76" s="2">
         <v>45094.40314679398</v>
@@ -16876,13 +16897,13 @@
         <v>2730</v>
       </c>
       <c r="H76" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I76" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="J76" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="K76">
         <v>99</v>
@@ -16909,7 +16930,7 @@
         <v>-9.633333329999999</v>
       </c>
       <c r="W76" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X76">
         <v>0.003333</v>
@@ -16941,7 +16962,7 @@
         <v>25</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C77" s="2">
         <v>45094.40349465278</v>
@@ -16959,13 +16980,13 @@
         <v>2760</v>
       </c>
       <c r="H77" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I77" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="J77" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="K77">
         <v>83</v>
@@ -16992,7 +17013,7 @@
         <v>-9.866666670000001</v>
       </c>
       <c r="W77" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X77">
         <v>-0.007778</v>
@@ -17024,7 +17045,7 @@
         <v>25</v>
       </c>
       <c r="B78" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C78" s="2">
         <v>45094.40384165509</v>
@@ -17042,13 +17063,13 @@
         <v>2790</v>
       </c>
       <c r="H78" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I78" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="J78" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="K78">
         <v>61</v>
@@ -17075,7 +17096,7 @@
         <v>-9.43333333</v>
       </c>
       <c r="W78" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X78">
         <v>0.014444</v>
@@ -17107,7 +17128,7 @@
         <v>25</v>
       </c>
       <c r="B79" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C79" s="2">
         <v>45094.40418819444</v>
@@ -17125,13 +17146,13 @@
         <v>2820</v>
       </c>
       <c r="H79" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I79" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="J79" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="K79">
         <v>52</v>
@@ -17158,7 +17179,7 @@
         <v>-9.53333333</v>
       </c>
       <c r="W79" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X79">
         <v>-0.003333</v>
@@ -17190,7 +17211,7 @@
         <v>25</v>
       </c>
       <c r="B80" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C80" s="2">
         <v>45094.40453605324</v>
@@ -17208,13 +17229,13 @@
         <v>2850</v>
       </c>
       <c r="H80" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I80" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="J80" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="K80">
         <v>24</v>
@@ -17241,7 +17262,7 @@
         <v>-9.46666667</v>
       </c>
       <c r="W80" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X80">
         <v>0.002222</v>
@@ -17273,7 +17294,7 @@
         <v>25</v>
       </c>
       <c r="B81" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C81" s="2">
         <v>45094.40488373843</v>
@@ -17291,13 +17312,13 @@
         <v>2880</v>
       </c>
       <c r="H81" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I81" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="J81" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="K81">
         <v>81</v>
@@ -17324,7 +17345,7 @@
         <v>-9.56666667</v>
       </c>
       <c r="W81" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X81">
         <v>-0.003333</v>
@@ -17356,7 +17377,7 @@
         <v>25</v>
       </c>
       <c r="B82" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C82" s="2">
         <v>45094.40523104167</v>
@@ -17374,13 +17395,13 @@
         <v>2910</v>
       </c>
       <c r="H82" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I82" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="J82" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="K82">
         <v>175</v>
@@ -17407,7 +17428,7 @@
         <v>-9.43333333</v>
       </c>
       <c r="W82" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X82">
         <v>0.004444</v>
@@ -17439,7 +17460,7 @@
         <v>25</v>
       </c>
       <c r="B83" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C83" s="2">
         <v>45094.40557918981</v>
@@ -17457,13 +17478,13 @@
         <v>2940</v>
       </c>
       <c r="H83" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I83" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="J83" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="K83">
         <v>173</v>
@@ -17490,7 +17511,7 @@
         <v>-9.733333330000001</v>
       </c>
       <c r="W83" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X83">
         <v>-0.01</v>
@@ -17522,7 +17543,7 @@
         <v>25</v>
       </c>
       <c r="B84" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C84" s="2">
         <v>45094.40662034722</v>
@@ -17540,13 +17561,13 @@
         <v>3030</v>
       </c>
       <c r="H84" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I84" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="J84" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="K84">
         <v>214</v>
@@ -17573,7 +17594,7 @@
         <v>-9.57777778</v>
       </c>
       <c r="W84" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X84">
         <v>0.001728</v>
@@ -17605,7 +17626,7 @@
         <v>25</v>
       </c>
       <c r="B85" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C85" s="2">
         <v>45094.40696665509</v>
@@ -17623,13 +17644,13 @@
         <v>3060</v>
       </c>
       <c r="H85" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I85" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="J85" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="K85">
         <v>250</v>
@@ -17656,7 +17677,7 @@
         <v>-9.16666667</v>
       </c>
       <c r="W85" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X85">
         <v>0.013704</v>
@@ -17688,7 +17709,7 @@
         <v>25</v>
       </c>
       <c r="B86" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C86" s="2">
         <v>45094.40732755787</v>
@@ -17706,13 +17727,13 @@
         <v>3090</v>
       </c>
       <c r="H86" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I86" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="J86" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="K86">
         <v>316</v>
@@ -17739,7 +17760,7 @@
         <v>-9.03333333</v>
       </c>
       <c r="W86" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X86">
         <v>0.004444</v>
@@ -17771,7 +17792,7 @@
         <v>25</v>
       </c>
       <c r="B87" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C87" s="2">
         <v>45094.40800915509</v>
@@ -17789,13 +17810,13 @@
         <v>3150</v>
       </c>
       <c r="H87" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I87" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="J87" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="K87">
         <v>114</v>
@@ -17822,7 +17843,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="W87" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X87">
         <v>0.005556</v>
@@ -17854,7 +17875,7 @@
         <v>25</v>
       </c>
       <c r="B88" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C88" s="2">
         <v>45094.40835655093</v>
@@ -17872,13 +17893,13 @@
         <v>3180</v>
       </c>
       <c r="H88" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I88" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="J88" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="K88">
         <v>123</v>
@@ -17905,7 +17926,7 @@
         <v>-8.733333330000001</v>
       </c>
       <c r="W88" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X88">
         <v>-0.001111</v>
@@ -17937,7 +17958,7 @@
         <v>25</v>
       </c>
       <c r="B89" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C89" s="2">
         <v>45094.40908092593</v>
@@ -17955,13 +17976,13 @@
         <v>3240</v>
       </c>
       <c r="H89" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="I89" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J89" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="K89">
         <v>164</v>
@@ -17988,7 +18009,7 @@
         <v>-8.766666669999999</v>
       </c>
       <c r="W89" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="X89">
         <v>-0.000556</v>

--- a/www/flightdata/xlsx/eoss-343.xlsx
+++ b/www/flightdata/xlsx/eoss-343.xlsx
@@ -1992,7 +1992,7 @@
         <v>24002.7</v>
       </c>
       <c r="I2">
-        <v>322</v>
+        <v>195</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>

--- a/www/flightdata/xlsx/eoss-343.xlsx
+++ b/www/flightdata/xlsx/eoss-343.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1312" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="501">
   <si>
     <t>flight</t>
   </si>
@@ -57,6 +57,21 @@
     <t>range_distance_traveled_km</t>
   </si>
   <si>
+    <t>parachute.description</t>
+  </si>
+  <si>
+    <t>parachute.size_ft</t>
+  </si>
+  <si>
+    <t>parachute.size_m</t>
+  </si>
+  <si>
+    <t>parachute.weight_lb</t>
+  </si>
+  <si>
+    <t>parachute.weight_kg</t>
+  </si>
+  <si>
     <t>weights.client_lb</t>
   </si>
   <si>
@@ -99,6 +114,15 @@
     <t>weights.necklift_kg</t>
   </si>
   <si>
+    <t>detected_burst.detected</t>
+  </si>
+  <si>
+    <t>detected_burst.burst_ft</t>
+  </si>
+  <si>
+    <t>detected_burst.burst_m</t>
+  </si>
+  <si>
     <t>launch_location.latitude</t>
   </si>
   <si>
@@ -148,6 +172,12 @@
   </si>
   <si>
     <t>1hrs 55mins 15secs</t>
+  </si>
+  <si>
+    <t>Spherachute</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
   <si>
     <t>flightid</t>
@@ -1850,10 +1880,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AS2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1965,25 +1995,49 @@
       <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:45">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>78749</v>
@@ -1995,7 +2049,7 @@
         <v>195</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="K2">
         <v>6915</v>
@@ -2006,76 +2060,100 @@
       <c r="M2">
         <v>64.27</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2">
+        <v>3.05</v>
+      </c>
+      <c r="Q2">
+        <v>2.4</v>
+      </c>
+      <c r="R2">
+        <v>1.09</v>
+      </c>
+      <c r="S2">
         <v>3.13</v>
       </c>
-      <c r="O2">
+      <c r="T2">
         <v>1.42</v>
       </c>
-      <c r="P2">
+      <c r="U2">
         <v>2.87</v>
       </c>
-      <c r="Q2">
+      <c r="V2">
         <v>1.3</v>
       </c>
-      <c r="R2">
+      <c r="W2">
         <v>2.4</v>
       </c>
-      <c r="S2">
+      <c r="X2">
         <v>1.09</v>
       </c>
-      <c r="T2">
+      <c r="Y2">
         <v>8.4</v>
       </c>
-      <c r="U2">
+      <c r="Z2">
         <v>3.81</v>
       </c>
-      <c r="V2">
+      <c r="AA2">
         <v>6.61</v>
       </c>
-      <c r="W2">
+      <c r="AB2">
         <v>3</v>
       </c>
-      <c r="X2">
+      <c r="AC2">
         <v>15.01</v>
       </c>
-      <c r="Y2">
+      <c r="AD2">
         <v>6.81</v>
       </c>
-      <c r="Z2">
+      <c r="AE2">
         <v>11.4</v>
       </c>
-      <c r="AA2">
+      <c r="AF2">
         <v>5.17</v>
       </c>
-      <c r="AB2">
+      <c r="AG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0</v>
+      </c>
+      <c r="AJ2">
         <v>34.7251666667</v>
       </c>
-      <c r="AC2">
+      <c r="AK2">
         <v>-86.64700000000001</v>
       </c>
-      <c r="AD2">
+      <c r="AL2">
         <v>705</v>
       </c>
-      <c r="AE2">
+      <c r="AM2">
         <v>214.88</v>
       </c>
-      <c r="AF2">
+      <c r="AN2">
         <v>34.3866833333</v>
       </c>
-      <c r="AG2">
+      <c r="AO2">
         <v>-86.07745</v>
       </c>
-      <c r="AH2">
+      <c r="AP2">
         <v>39.94</v>
       </c>
-      <c r="AI2">
+      <c r="AQ2">
         <v>64.27</v>
       </c>
-      <c r="AJ2">
+      <c r="AR2">
         <v>9711</v>
       </c>
-      <c r="AK2">
+      <c r="AS2">
         <v>2959.91</v>
       </c>
     </row>
@@ -2091,156 +2169,156 @@
   <sheetData>
     <row r="1" spans="1:48">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:48">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C2" s="2">
         <v>45094.33562050926</v>
@@ -2261,16 +2339,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L2" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="M2">
         <v>45</v>
@@ -2306,7 +2384,7 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="AE2" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AG2">
         <v>0.233333</v>
@@ -2323,10 +2401,10 @@
     </row>
     <row r="3" spans="1:48">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C3" s="2">
         <v>45094.33578667824</v>
@@ -2347,16 +2425,16 @@
         <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="L3" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="M3">
         <v>200</v>
@@ -2392,7 +2470,7 @@
         <v>0.03066667</v>
       </c>
       <c r="AE3" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF3">
         <v>-0.004444</v>
@@ -2433,10 +2511,10 @@
     </row>
     <row r="4" spans="1:48">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C4" s="2">
         <v>45094.33592848379</v>
@@ -2457,16 +2535,16 @@
         <v>26</v>
       </c>
       <c r="I4" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="L4" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="M4">
         <v>349</v>
@@ -2502,7 +2580,7 @@
         <v>0.42230769</v>
       </c>
       <c r="AE4" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF4">
         <v>0.049408</v>
@@ -2555,10 +2633,10 @@
     </row>
     <row r="5" spans="1:48">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2">
         <v>45094.33596957176</v>
@@ -2579,16 +2657,16 @@
         <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="L5" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="M5">
         <v>311</v>
@@ -2624,7 +2702,7 @@
         <v>6.02</v>
       </c>
       <c r="AE5" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF5">
         <v>4.591346</v>
@@ -2677,10 +2755,10 @@
     </row>
     <row r="6" spans="1:48">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2">
         <v>45094.33613355324</v>
@@ -2701,16 +2779,16 @@
         <v>45</v>
       </c>
       <c r="I6" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="L6" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="M6">
         <v>187</v>
@@ -2746,7 +2824,7 @@
         <v>5.32366667</v>
       </c>
       <c r="AE6" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF6">
         <v>-0.076111</v>
@@ -2799,10 +2877,10 @@
     </row>
     <row r="7" spans="1:48">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C7" s="2">
         <v>45094.33632274305</v>
@@ -2823,16 +2901,16 @@
         <v>60</v>
       </c>
       <c r="I7" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="L7" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="M7">
         <v>90</v>
@@ -2868,7 +2946,7 @@
         <v>6.797</v>
       </c>
       <c r="AE7" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF7">
         <v>0.161111</v>
@@ -2921,10 +2999,10 @@
     </row>
     <row r="8" spans="1:48">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2">
         <v>45094.3364802662</v>
@@ -2945,16 +3023,16 @@
         <v>75</v>
       </c>
       <c r="I8" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="L8" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="M8">
         <v>93</v>
@@ -2990,7 +3068,7 @@
         <v>6.88866667</v>
       </c>
       <c r="AE8" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF8">
         <v>0.01</v>
@@ -3043,10 +3121,10 @@
     </row>
     <row r="9" spans="1:48">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2">
         <v>45094.33666510417</v>
@@ -3067,16 +3145,16 @@
         <v>90</v>
       </c>
       <c r="I9" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L9" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="M9">
         <v>98</v>
@@ -3112,7 +3190,7 @@
         <v>6.89866667</v>
       </c>
       <c r="AE9" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF9">
         <v>0.001111</v>
@@ -3165,10 +3243,10 @@
     </row>
     <row r="10" spans="1:48">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2">
         <v>45094.33682725694</v>
@@ -3189,16 +3267,16 @@
         <v>105</v>
       </c>
       <c r="I10" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L10" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="M10">
         <v>148</v>
@@ -3234,7 +3312,7 @@
         <v>6.929</v>
       </c>
       <c r="AE10" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF10">
         <v>0.003333</v>
@@ -3287,10 +3365,10 @@
     </row>
     <row r="11" spans="1:48">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C11" s="2">
         <v>45094.33701878472</v>
@@ -3311,16 +3389,16 @@
         <v>120</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="L11" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="M11">
         <v>165</v>
@@ -3356,7 +3434,7 @@
         <v>6.76633333</v>
       </c>
       <c r="AE11" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF11">
         <v>-0.017778</v>
@@ -3409,10 +3487,10 @@
     </row>
     <row r="12" spans="1:48">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C12" s="2">
         <v>45094.33717542824</v>
@@ -3433,16 +3511,16 @@
         <v>135</v>
       </c>
       <c r="I12" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="L12" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="M12">
         <v>275</v>
@@ -3478,7 +3556,7 @@
         <v>6.58366667</v>
       </c>
       <c r="AE12" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF12">
         <v>-0.02</v>
@@ -3531,10 +3609,10 @@
     </row>
     <row r="13" spans="1:48">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C13" s="2">
         <v>45094.33736206019</v>
@@ -3555,16 +3633,16 @@
         <v>150</v>
       </c>
       <c r="I13" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="L13" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="M13">
         <v>271</v>
@@ -3600,7 +3678,7 @@
         <v>6.86833333</v>
       </c>
       <c r="AE13" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF13">
         <v>0.031111</v>
@@ -3653,10 +3731,10 @@
     </row>
     <row r="14" spans="1:48">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C14" s="2">
         <v>45094.33752214121</v>
@@ -3677,16 +3755,16 @@
         <v>165</v>
       </c>
       <c r="I14" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="L14" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="M14">
         <v>66</v>
@@ -3722,7 +3800,7 @@
         <v>6.76666667</v>
       </c>
       <c r="AE14" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF14">
         <v>-0.011111</v>
@@ -3775,10 +3853,10 @@
     </row>
     <row r="15" spans="1:48">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C15" s="2">
         <v>45094.33770380787</v>
@@ -3799,16 +3877,16 @@
         <v>180</v>
       </c>
       <c r="I15" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="L15" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="M15">
         <v>198</v>
@@ -3844,7 +3922,7 @@
         <v>6.665</v>
       </c>
       <c r="AE15" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF15">
         <v>-0.011111</v>
@@ -3897,10 +3975,10 @@
     </row>
     <row r="16" spans="1:48">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C16" s="2">
         <v>45094.33786939815</v>
@@ -3921,16 +3999,16 @@
         <v>195</v>
       </c>
       <c r="I16" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="L16" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="M16">
         <v>144</v>
@@ -3966,7 +4044,7 @@
         <v>6.89866667</v>
       </c>
       <c r="AE16" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF16">
         <v>0.025556</v>
@@ -4019,10 +4097,10 @@
     </row>
     <row r="17" spans="1:47">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C17" s="2">
         <v>45094.33805721065</v>
@@ -4043,16 +4121,16 @@
         <v>210</v>
       </c>
       <c r="I17" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="L17" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="M17">
         <v>120</v>
@@ -4088,7 +4166,7 @@
         <v>7.16266667</v>
       </c>
       <c r="AE17" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF17">
         <v>0.028889</v>
@@ -4141,10 +4219,10 @@
     </row>
     <row r="18" spans="1:47">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C18" s="2">
         <v>45094.33821681713</v>
@@ -4165,16 +4243,16 @@
         <v>225</v>
       </c>
       <c r="I18" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="L18" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="M18">
         <v>261</v>
@@ -4210,7 +4288,7 @@
         <v>7.09166667</v>
       </c>
       <c r="AE18" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF18">
         <v>-0.007778</v>
@@ -4263,10 +4341,10 @@
     </row>
     <row r="19" spans="1:47">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C19" s="2">
         <v>45094.33856372685</v>
@@ -4287,16 +4365,16 @@
         <v>255</v>
       </c>
       <c r="I19" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="L19" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="M19">
         <v>100</v>
@@ -4332,7 +4410,7 @@
         <v>6.87833333</v>
       </c>
       <c r="AE19" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF19">
         <v>-0.023333</v>
@@ -4385,10 +4463,10 @@
     </row>
     <row r="20" spans="1:47">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C20" s="2">
         <v>45094.33891157407</v>
@@ -4409,16 +4487,16 @@
         <v>285</v>
       </c>
       <c r="I20" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="L20" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="M20">
         <v>178</v>
@@ -4454,7 +4532,7 @@
         <v>6.71566667</v>
       </c>
       <c r="AE20" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF20">
         <v>-0.017778</v>
@@ -4507,10 +4585,10 @@
     </row>
     <row r="21" spans="1:47">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C21" s="2">
         <v>45094.33909788194</v>
@@ -4531,16 +4609,16 @@
         <v>300</v>
       </c>
       <c r="I21" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="L21" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="M21">
         <v>164</v>
@@ -4576,7 +4654,7 @@
         <v>6.79022222</v>
       </c>
       <c r="AE21" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF21">
         <v>0.002716</v>
@@ -4629,10 +4707,10 @@
     </row>
     <row r="22" spans="1:47">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C22" s="2">
         <v>45094.33960560185</v>
@@ -4653,16 +4731,16 @@
         <v>345</v>
       </c>
       <c r="I22" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="L22" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="M22">
         <v>146</v>
@@ -4698,7 +4776,7 @@
         <v>6.8935</v>
       </c>
       <c r="AE22" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF22">
         <v>0.005648</v>
@@ -4751,10 +4829,10 @@
     </row>
     <row r="23" spans="1:47">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C23" s="2">
         <v>45094.33979266204</v>
@@ -4775,16 +4853,16 @@
         <v>360</v>
       </c>
       <c r="I23" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="L23" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="M23">
         <v>147</v>
@@ -4820,7 +4898,7 @@
         <v>7.14766667</v>
       </c>
       <c r="AE23" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF23">
         <v>0.013889</v>
@@ -4873,10 +4951,10 @@
     </row>
     <row r="24" spans="1:47">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C24" s="2">
         <v>45094.33995288194</v>
@@ -4897,16 +4975,16 @@
         <v>375</v>
       </c>
       <c r="I24" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="L24" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="M24">
         <v>105</v>
@@ -4942,7 +5020,7 @@
         <v>7.00033333</v>
       </c>
       <c r="AE24" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF24">
         <v>-0.016111</v>
@@ -4995,10 +5073,10 @@
     </row>
     <row r="25" spans="1:47">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C25" s="2">
         <v>45094.34029994213</v>
@@ -5019,16 +5097,16 @@
         <v>405</v>
       </c>
       <c r="I25" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="L25" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="M25">
         <v>160</v>
@@ -5064,7 +5142,7 @@
         <v>6.77666667</v>
       </c>
       <c r="AE25" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF25">
         <v>-0.024444</v>
@@ -5117,10 +5195,10 @@
     </row>
     <row r="26" spans="1:47">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C26" s="2">
         <v>45094.34049260417</v>
@@ -5141,16 +5219,16 @@
         <v>421</v>
       </c>
       <c r="I26" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="L26" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="M26">
         <v>114</v>
@@ -5186,7 +5264,7 @@
         <v>6.8204918</v>
       </c>
       <c r="AE26" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF26">
         <v>0.002356</v>
@@ -5239,10 +5317,10 @@
     </row>
     <row r="27" spans="1:47">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C27" s="2">
         <v>45094.34064704861</v>
@@ -5263,16 +5341,16 @@
         <v>435</v>
       </c>
       <c r="I27" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="L27" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="M27">
         <v>103</v>
@@ -5308,7 +5386,7 @@
         <v>7.22366667</v>
       </c>
       <c r="AE27" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF27">
         <v>0.044098</v>
@@ -5361,10 +5439,10 @@
     </row>
     <row r="28" spans="1:47">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C28" s="2">
         <v>45094.34099342593</v>
@@ -5385,16 +5463,16 @@
         <v>465</v>
       </c>
       <c r="I28" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="L28" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="M28">
         <v>121</v>
@@ -5430,7 +5508,7 @@
         <v>7.08166667</v>
       </c>
       <c r="AE28" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF28">
         <v>-0.015556</v>
@@ -5483,10 +5561,10 @@
     </row>
     <row r="29" spans="1:47">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C29" s="2">
         <v>45094.34117866898</v>
@@ -5507,16 +5585,16 @@
         <v>480</v>
       </c>
       <c r="I29" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="L29" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="M29">
         <v>118</v>
@@ -5552,7 +5630,7 @@
         <v>7.08271186</v>
       </c>
       <c r="AE29" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF29">
         <v>6.7E-05</v>
@@ -5605,10 +5683,10 @@
     </row>
     <row r="30" spans="1:47">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C30" s="2">
         <v>45094.34168921296</v>
@@ -5629,16 +5707,16 @@
         <v>525</v>
       </c>
       <c r="I30" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="L30" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="M30">
         <v>137</v>
@@ -5674,7 +5752,7 @@
         <v>7.06633333</v>
       </c>
       <c r="AE30" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF30">
         <v>-0.000899</v>
@@ -5727,10 +5805,10 @@
     </row>
     <row r="31" spans="1:47">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C31" s="2">
         <v>45094.34203625</v>
@@ -5751,16 +5829,16 @@
         <v>555</v>
       </c>
       <c r="I31" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="L31" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="M31">
         <v>162</v>
@@ -5796,7 +5874,7 @@
         <v>7.34566667</v>
       </c>
       <c r="AE31" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF31">
         <v>0.030556</v>
@@ -5849,10 +5927,10 @@
     </row>
     <row r="32" spans="1:47">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C32" s="2">
         <v>45094.34222148148</v>
@@ -5873,16 +5951,16 @@
         <v>570</v>
       </c>
       <c r="I32" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="L32" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="M32">
         <v>119</v>
@@ -5918,7 +5996,7 @@
         <v>7.33211111</v>
       </c>
       <c r="AE32" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF32">
         <v>-0.000494</v>
@@ -5971,10 +6049,10 @@
     </row>
     <row r="33" spans="1:48">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C33" s="2">
         <v>45094.34273024306</v>
@@ -5995,16 +6073,16 @@
         <v>615</v>
       </c>
       <c r="I33" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="L33" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="M33">
         <v>155</v>
@@ -6040,7 +6118,7 @@
         <v>7.305</v>
       </c>
       <c r="AE33" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF33">
         <v>-0.001481</v>
@@ -6093,10 +6171,10 @@
     </row>
     <row r="34" spans="1:48">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C34" s="2">
         <v>45094.34291811343</v>
@@ -6117,16 +6195,16 @@
         <v>630</v>
       </c>
       <c r="I34" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="L34" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="M34">
         <v>119</v>
@@ -6162,7 +6240,7 @@
         <v>7.24916667</v>
       </c>
       <c r="AE34" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF34">
         <v>-0.003056</v>
@@ -6215,10 +6293,10 @@
     </row>
     <row r="35" spans="1:48">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C35" s="2">
         <v>45094.34411873842</v>
@@ -6239,16 +6317,16 @@
         <v>735</v>
       </c>
       <c r="I35" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="L35" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="M35">
         <v>257</v>
@@ -6284,7 +6362,7 @@
         <v>7.23133333</v>
       </c>
       <c r="AE35" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF35">
         <v>-0.000486</v>
@@ -6337,10 +6415,10 @@
     </row>
     <row r="36" spans="1:48">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C36" s="2">
         <v>45094.34446693287</v>
@@ -6361,16 +6439,16 @@
         <v>765</v>
       </c>
       <c r="I36" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="L36" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="M36">
         <v>51</v>
@@ -6406,7 +6484,7 @@
         <v>7.19333333</v>
       </c>
       <c r="AE36" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF36">
         <v>-0.004167</v>
@@ -6459,10 +6537,10 @@
     </row>
     <row r="37" spans="1:48">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C37" s="2">
         <v>45094.34481342592</v>
@@ -6483,16 +6561,16 @@
         <v>795</v>
       </c>
       <c r="I37" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="L37" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="M37">
         <v>221</v>
@@ -6528,7 +6606,7 @@
         <v>7.07133333</v>
       </c>
       <c r="AE37" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF37">
         <v>-0.013333</v>
@@ -6581,10 +6659,10 @@
     </row>
     <row r="38" spans="1:48">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C38" s="2">
         <v>45094.34550837963</v>
@@ -6605,16 +6683,16 @@
         <v>855</v>
       </c>
       <c r="I38" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="L38" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="M38">
         <v>69</v>
@@ -6650,7 +6728,7 @@
         <v>7.25433333</v>
       </c>
       <c r="AE38" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF38">
         <v>0.01</v>
@@ -6703,10 +6781,10 @@
     </row>
     <row r="39" spans="1:48">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C39" s="2">
         <v>45094.34585572917</v>
@@ -6727,16 +6805,16 @@
         <v>885</v>
       </c>
       <c r="I39" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="L39" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="M39">
         <v>133</v>
@@ -6772,7 +6850,7 @@
         <v>7.183</v>
       </c>
       <c r="AE39" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF39">
         <v>-0.007778</v>
@@ -6825,10 +6903,10 @@
     </row>
     <row r="40" spans="1:48">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C40" s="2">
         <v>45094.34620280092</v>
@@ -6849,16 +6927,16 @@
         <v>915</v>
       </c>
       <c r="I40" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="L40" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="M40">
         <v>161</v>
@@ -6894,7 +6972,7 @@
         <v>7.366</v>
       </c>
       <c r="AE40" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF40">
         <v>0.02</v>
@@ -6947,10 +7025,10 @@
     </row>
     <row r="41" spans="1:48">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C41" s="2">
         <v>45094.34654929398</v>
@@ -6971,16 +7049,16 @@
         <v>945</v>
       </c>
       <c r="I41" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="L41" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="M41">
         <v>132</v>
@@ -7016,7 +7094,7 @@
         <v>7.366</v>
       </c>
       <c r="AE41" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF41">
         <v>0</v>
@@ -7069,10 +7147,10 @@
     </row>
     <row r="42" spans="1:48">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C42" s="2">
         <v>45094.34689672454</v>
@@ -7093,16 +7171,16 @@
         <v>975</v>
       </c>
       <c r="I42" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="L42" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="M42">
         <v>149</v>
@@ -7138,7 +7216,7 @@
         <v>7.39666667</v>
       </c>
       <c r="AE42" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF42">
         <v>0.003333</v>
@@ -7191,10 +7269,10 @@
     </row>
     <row r="43" spans="1:48">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C43" s="2">
         <v>45094.34724454861</v>
@@ -7215,16 +7293,16 @@
         <v>1005</v>
       </c>
       <c r="I43" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="L43" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="M43">
         <v>188</v>
@@ -7260,7 +7338,7 @@
         <v>7.08133333</v>
       </c>
       <c r="AE43" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF43">
         <v>-0.034444</v>
@@ -7313,10 +7391,10 @@
     </row>
     <row r="44" spans="1:48">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C44" s="2">
         <v>45094.3475916088</v>
@@ -7337,16 +7415,16 @@
         <v>1035</v>
       </c>
       <c r="I44" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="L44" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="M44">
         <v>173</v>
@@ -7382,7 +7460,7 @@
         <v>7.64033333</v>
       </c>
       <c r="AE44" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF44">
         <v>0.061111</v>
@@ -7435,10 +7513,10 @@
     </row>
     <row r="45" spans="1:48">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C45" s="2">
         <v>45094.34793854166</v>
@@ -7459,16 +7537,16 @@
         <v>1065</v>
       </c>
       <c r="I45" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="L45" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="M45">
         <v>115</v>
@@ -7504,7 +7582,7 @@
         <v>7.65066667</v>
       </c>
       <c r="AE45" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF45">
         <v>0.001111</v>
@@ -7557,10 +7635,10 @@
     </row>
     <row r="46" spans="1:48">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C46" s="2">
         <v>45094.34863305555</v>
@@ -7581,16 +7659,16 @@
         <v>1125</v>
       </c>
       <c r="I46" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="L46" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="M46">
         <v>206</v>
@@ -7626,7 +7704,7 @@
         <v>7.625</v>
       </c>
       <c r="AE46" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF46">
         <v>-0.001389</v>
@@ -7679,10 +7757,10 @@
     </row>
     <row r="47" spans="1:48">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C47" s="2">
         <v>45094.34882231482</v>
@@ -7703,16 +7781,16 @@
         <v>1140</v>
       </c>
       <c r="I47" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="L47" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="M47">
         <v>143</v>
@@ -7748,7 +7826,7 @@
         <v>7.34688235</v>
       </c>
       <c r="AE47" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF47">
         <v>-0.00179</v>
@@ -7799,15 +7877,15 @@
         <v>7.882701</v>
       </c>
       <c r="AV47" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
     </row>
     <row r="48" spans="1:48">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C48" s="2">
         <v>45094.34897998843</v>
@@ -7828,16 +7906,16 @@
         <v>1155</v>
       </c>
       <c r="I48" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="L48" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="M48">
         <v>187</v>
@@ -7873,7 +7951,7 @@
         <v>8.48366667</v>
       </c>
       <c r="AE48" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF48">
         <v>0.124314</v>
@@ -7926,10 +8004,10 @@
     </row>
     <row r="49" spans="1:47">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C49" s="2">
         <v>45094.34932815973</v>
@@ -7950,16 +8028,16 @@
         <v>1185</v>
       </c>
       <c r="I49" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="L49" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="M49">
         <v>193</v>
@@ -7995,7 +8073,7 @@
         <v>8.08733333</v>
       </c>
       <c r="AE49" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF49">
         <v>-0.043333</v>
@@ -8048,10 +8126,10 @@
     </row>
     <row r="50" spans="1:47">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C50" s="2">
         <v>45094.34967472222</v>
@@ -8072,16 +8150,16 @@
         <v>1215</v>
       </c>
       <c r="I50" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="L50" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="M50">
         <v>81</v>
@@ -8117,7 +8195,7 @@
         <v>8.382</v>
       </c>
       <c r="AE50" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF50">
         <v>0.032222</v>
@@ -8170,10 +8248,10 @@
     </row>
     <row r="51" spans="1:47">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C51" s="2">
         <v>45094.35036913194</v>
@@ -8194,16 +8272,16 @@
         <v>1275</v>
       </c>
       <c r="I51" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="L51" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="M51">
         <v>147</v>
@@ -8239,7 +8317,7 @@
         <v>8.234666669999999</v>
       </c>
       <c r="AE51" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF51">
         <v>-0.008056000000000001</v>
@@ -8292,10 +8370,10 @@
     </row>
     <row r="52" spans="1:47">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C52" s="2">
         <v>45094.35055534722</v>
@@ -8316,16 +8394,16 @@
         <v>1290</v>
       </c>
       <c r="I52" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="L52" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="M52">
         <v>122</v>
@@ -8361,7 +8439,7 @@
         <v>8.339333330000001</v>
       </c>
       <c r="AE52" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF52">
         <v>0.002289</v>
@@ -8414,10 +8492,10 @@
     </row>
     <row r="53" spans="1:47">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C53" s="2">
         <v>45094.35071625</v>
@@ -8438,16 +8516,16 @@
         <v>1305</v>
       </c>
       <c r="I53" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J53" t="b">
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="L53" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="M53">
         <v>118</v>
@@ -8483,7 +8561,7 @@
         <v>8.20933333</v>
       </c>
       <c r="AE53" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF53">
         <v>-0.014222</v>
@@ -8536,10 +8614,10 @@
     </row>
     <row r="54" spans="1:47">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B54" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C54" s="2">
         <v>45094.35106363426</v>
@@ -8560,16 +8638,16 @@
         <v>1335</v>
       </c>
       <c r="I54" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J54" t="b">
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="L54" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="M54">
         <v>104</v>
@@ -8605,7 +8683,7 @@
         <v>8.402333329999999</v>
       </c>
       <c r="AE54" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF54">
         <v>0.021111</v>
@@ -8658,10 +8736,10 @@
     </row>
     <row r="55" spans="1:47">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C55" s="2">
         <v>45094.35141146991</v>
@@ -8682,16 +8760,16 @@
         <v>1365</v>
       </c>
       <c r="I55" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J55" t="b">
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="L55" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="M55">
         <v>121</v>
@@ -8727,7 +8805,7 @@
         <v>7.73166667</v>
       </c>
       <c r="AE55" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF55">
         <v>-0.073333</v>
@@ -8780,10 +8858,10 @@
     </row>
     <row r="56" spans="1:47">
       <c r="A56" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C56" s="2">
         <v>45094.35175868055</v>
@@ -8804,16 +8882,16 @@
         <v>1395</v>
       </c>
       <c r="I56" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J56" t="b">
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="L56" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="M56">
         <v>139</v>
@@ -8849,7 +8927,7 @@
         <v>8.128</v>
       </c>
       <c r="AE56" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF56">
         <v>0.043333</v>
@@ -8902,10 +8980,10 @@
     </row>
     <row r="57" spans="1:47">
       <c r="A57" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C57" s="2">
         <v>45094.35210487268</v>
@@ -8926,16 +9004,16 @@
         <v>1425</v>
       </c>
       <c r="I57" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L57" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="M57">
         <v>136</v>
@@ -8971,7 +9049,7 @@
         <v>7.945</v>
       </c>
       <c r="AE57" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF57">
         <v>-0.02</v>
@@ -9024,10 +9102,10 @@
     </row>
     <row r="58" spans="1:47">
       <c r="A58" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B58" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C58" s="2">
         <v>45094.35228836806</v>
@@ -9048,16 +9126,16 @@
         <v>1440</v>
       </c>
       <c r="I58" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="L58" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="M58">
         <v>122</v>
@@ -9093,7 +9171,7 @@
         <v>8.09346667</v>
       </c>
       <c r="AE58" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF58">
         <v>0.003244</v>
@@ -9146,10 +9224,10 @@
     </row>
     <row r="59" spans="1:47">
       <c r="A59" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B59" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C59" s="2">
         <v>45094.35245263889</v>
@@ -9170,16 +9248,16 @@
         <v>1455</v>
       </c>
       <c r="I59" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="L59" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="M59">
         <v>118</v>
@@ -9215,7 +9293,7 @@
         <v>8.28066667</v>
       </c>
       <c r="AE59" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF59">
         <v>0.020444</v>
@@ -9268,10 +9346,10 @@
     </row>
     <row r="60" spans="1:47">
       <c r="A60" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B60" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C60" s="2">
         <v>45094.3527999537</v>
@@ -9292,16 +9370,16 @@
         <v>1485</v>
       </c>
       <c r="I60" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="L60" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="M60">
         <v>114</v>
@@ -9337,7 +9415,7 @@
         <v>8.452999999999999</v>
       </c>
       <c r="AE60" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF60">
         <v>0.018889</v>
@@ -9390,10 +9468,10 @@
     </row>
     <row r="61" spans="1:47">
       <c r="A61" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C61" s="2">
         <v>45094.35349449074</v>
@@ -9414,16 +9492,16 @@
         <v>1545</v>
       </c>
       <c r="I61" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="L61" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="M61">
         <v>119</v>
@@ -9459,7 +9537,7 @@
         <v>8.87983333</v>
       </c>
       <c r="AE61" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF61">
         <v>0.023333</v>
@@ -9512,10 +9590,10 @@
     </row>
     <row r="62" spans="1:47">
       <c r="A62" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C62" s="2">
         <v>45094.35384116898</v>
@@ -9536,16 +9614,16 @@
         <v>1575</v>
       </c>
       <c r="I62" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="L62" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="M62">
         <v>114</v>
@@ -9581,7 +9659,7 @@
         <v>8.42266667</v>
       </c>
       <c r="AE62" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF62">
         <v>-0.05</v>
@@ -9634,10 +9712,10 @@
     </row>
     <row r="63" spans="1:47">
       <c r="A63" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B63" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C63" s="2">
         <v>45094.35418881944</v>
@@ -9658,16 +9736,16 @@
         <v>1605</v>
       </c>
       <c r="I63" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="L63" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="M63">
         <v>124</v>
@@ -9703,7 +9781,7 @@
         <v>8.60566667</v>
       </c>
       <c r="AE63" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF63">
         <v>0.02</v>
@@ -9756,10 +9834,10 @@
     </row>
     <row r="64" spans="1:47">
       <c r="A64" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C64" s="2">
         <v>45094.35453560185</v>
@@ -9780,16 +9858,16 @@
         <v>1635</v>
       </c>
       <c r="I64" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J64" t="b">
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="L64" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="M64">
         <v>117</v>
@@ -9825,7 +9903,7 @@
         <v>9.357333329999999</v>
       </c>
       <c r="AE64" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF64">
         <v>0.082222</v>
@@ -9878,10 +9956,10 @@
     </row>
     <row r="65" spans="1:47">
       <c r="A65" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B65" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C65" s="2">
         <v>45094.35472105324</v>
@@ -9902,16 +9980,16 @@
         <v>1650</v>
       </c>
       <c r="I65" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J65" t="b">
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="L65" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="M65">
         <v>123</v>
@@ -9947,7 +10025,7 @@
         <v>8.694047619999999</v>
       </c>
       <c r="AE65" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF65">
         <v>-0.010363</v>
@@ -10000,10 +10078,10 @@
     </row>
     <row r="66" spans="1:47">
       <c r="A66" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B66" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C66" s="2">
         <v>45094.35488359954</v>
@@ -10024,16 +10102,16 @@
         <v>1665</v>
       </c>
       <c r="I66" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J66" t="b">
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="L66" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="M66">
         <v>119</v>
@@ -10069,7 +10147,7 @@
         <v>8.61566667</v>
       </c>
       <c r="AE66" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF66">
         <v>-0.008571</v>
@@ -10122,10 +10200,10 @@
     </row>
     <row r="67" spans="1:47">
       <c r="A67" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B67" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C67" s="2">
         <v>45094.35523041667</v>
@@ -10146,16 +10224,16 @@
         <v>1695</v>
       </c>
       <c r="I67" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J67" t="b">
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L67" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="M67">
         <v>121</v>
@@ -10191,7 +10269,7 @@
         <v>8.666333330000001</v>
       </c>
       <c r="AE67" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF67">
         <v>0.005556</v>
@@ -10244,10 +10322,10 @@
     </row>
     <row r="68" spans="1:47">
       <c r="A68" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B68" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C68" s="2">
         <v>45094.35557736111</v>
@@ -10268,16 +10346,16 @@
         <v>1725</v>
       </c>
       <c r="I68" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J68" t="b">
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="L68" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="M68">
         <v>119</v>
@@ -10313,7 +10391,7 @@
         <v>9.012</v>
       </c>
       <c r="AE68" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF68">
         <v>0.037778</v>
@@ -10366,10 +10444,10 @@
     </row>
     <row r="69" spans="1:47">
       <c r="A69" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B69" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C69" s="2">
         <v>45094.35592439815</v>
@@ -10390,16 +10468,16 @@
         <v>1755</v>
       </c>
       <c r="I69" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J69" t="b">
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="L69" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="M69">
         <v>115</v>
@@ -10435,7 +10513,7 @@
         <v>8.524333329999999</v>
       </c>
       <c r="AE69" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF69">
         <v>-0.053333</v>
@@ -10488,10 +10566,10 @@
     </row>
     <row r="70" spans="1:47">
       <c r="A70" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B70" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C70" s="2">
         <v>45094.35627298611</v>
@@ -10512,16 +10590,16 @@
         <v>1785</v>
       </c>
       <c r="I70" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J70" t="b">
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="L70" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="M70">
         <v>120</v>
@@ -10557,7 +10635,7 @@
         <v>9.63166667</v>
       </c>
       <c r="AE70" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF70">
         <v>0.121111</v>
@@ -10610,10 +10688,10 @@
     </row>
     <row r="71" spans="1:47">
       <c r="A71" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B71" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C71" s="2">
         <v>45094.35661945602</v>
@@ -10634,16 +10712,16 @@
         <v>1815</v>
       </c>
       <c r="I71" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J71" t="b">
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="L71" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="M71">
         <v>116</v>
@@ -10679,7 +10757,7 @@
         <v>10.475</v>
       </c>
       <c r="AE71" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF71">
         <v>0.092222</v>
@@ -10732,10 +10810,10 @@
     </row>
     <row r="72" spans="1:47">
       <c r="A72" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B72" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C72" s="2">
         <v>45094.3569668287</v>
@@ -10756,16 +10834,16 @@
         <v>1845</v>
       </c>
       <c r="I72" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="L72" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="M72">
         <v>116</v>
@@ -10801,7 +10879,7 @@
         <v>9.286</v>
       </c>
       <c r="AE72" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF72">
         <v>-0.13</v>
@@ -10854,10 +10932,10 @@
     </row>
     <row r="73" spans="1:47">
       <c r="A73" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B73" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C73" s="2">
         <v>45094.35731451389</v>
@@ -10878,16 +10956,16 @@
         <v>1875</v>
       </c>
       <c r="I73" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J73" t="b">
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="L73" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="M73">
         <v>125</v>
@@ -10923,7 +11001,7 @@
         <v>6.25866667</v>
       </c>
       <c r="AE73" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF73">
         <v>-0.331111</v>
@@ -10976,10 +11054,10 @@
     </row>
     <row r="74" spans="1:47">
       <c r="A74" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C74" s="2">
         <v>45094.3580084375</v>
@@ -11000,16 +11078,16 @@
         <v>1935</v>
       </c>
       <c r="I74" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J74" t="b">
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="L74" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="M74">
         <v>112</v>
@@ -11045,7 +11123,7 @@
         <v>9.733333330000001</v>
       </c>
       <c r="AE74" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF74">
         <v>0.19</v>
@@ -11098,10 +11176,10 @@
     </row>
     <row r="75" spans="1:47">
       <c r="A75" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B75" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C75" s="2">
         <v>45094.35835541667</v>
@@ -11122,16 +11200,16 @@
         <v>1965</v>
       </c>
       <c r="I75" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J75" t="b">
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="L75" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="M75">
         <v>97</v>
@@ -11167,7 +11245,7 @@
         <v>9.946666670000001</v>
       </c>
       <c r="AE75" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF75">
         <v>0.023333</v>
@@ -11220,10 +11298,10 @@
     </row>
     <row r="76" spans="1:47">
       <c r="A76" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B76" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C76" s="2">
         <v>45094.35870262732</v>
@@ -11244,16 +11322,16 @@
         <v>1995</v>
       </c>
       <c r="I76" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J76" t="b">
         <v>1</v>
       </c>
       <c r="K76" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="L76" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="M76">
         <v>102</v>
@@ -11289,7 +11367,7 @@
         <v>7.86366667</v>
       </c>
       <c r="AE76" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF76">
         <v>-0.227778</v>
@@ -11342,10 +11420,10 @@
     </row>
     <row r="77" spans="1:47">
       <c r="A77" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B77" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C77" s="2">
         <v>45094.35904986111</v>
@@ -11366,16 +11444,16 @@
         <v>2025</v>
       </c>
       <c r="I77" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J77" t="b">
         <v>1</v>
       </c>
       <c r="K77" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="L77" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="M77">
         <v>111</v>
@@ -11411,7 +11489,7 @@
         <v>7.15266667</v>
       </c>
       <c r="AE77" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF77">
         <v>-0.077778</v>
@@ -11464,10 +11542,10 @@
     </row>
     <row r="78" spans="1:47">
       <c r="A78" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B78" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C78" s="2">
         <v>45094.35939660879</v>
@@ -11488,16 +11566,16 @@
         <v>2055</v>
       </c>
       <c r="I78" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J78" t="b">
         <v>1</v>
       </c>
       <c r="K78" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="L78" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="M78">
         <v>114</v>
@@ -11533,7 +11611,7 @@
         <v>8.189</v>
       </c>
       <c r="AE78" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF78">
         <v>0.113333</v>
@@ -11586,10 +11664,10 @@
     </row>
     <row r="79" spans="1:47">
       <c r="A79" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B79" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C79" s="2">
         <v>45094.35974424768</v>
@@ -11610,16 +11688,16 @@
         <v>2085</v>
       </c>
       <c r="I79" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J79" t="b">
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="L79" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="M79">
         <v>156</v>
@@ -11655,7 +11733,7 @@
         <v>8.595333330000001</v>
       </c>
       <c r="AE79" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF79">
         <v>0.044444</v>
@@ -11708,10 +11786,10 @@
     </row>
     <row r="80" spans="1:47">
       <c r="A80" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B80" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C80" s="2">
         <v>45094.36043918981</v>
@@ -11732,16 +11810,16 @@
         <v>2145</v>
       </c>
       <c r="I80" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J80" t="b">
         <v>1</v>
       </c>
       <c r="K80" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="L80" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="M80">
         <v>154</v>
@@ -11777,7 +11855,7 @@
         <v>9.529999999999999</v>
       </c>
       <c r="AE80" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF80">
         <v>0.051111</v>
@@ -11830,10 +11908,10 @@
     </row>
     <row r="81" spans="1:48">
       <c r="A81" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B81" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C81" s="2">
         <v>45094.36078555555</v>
@@ -11854,16 +11932,16 @@
         <v>2175</v>
       </c>
       <c r="I81" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J81" t="b">
         <v>1</v>
       </c>
       <c r="K81" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="L81" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="M81">
         <v>49</v>
@@ -11899,7 +11977,7 @@
         <v>11.81633333</v>
       </c>
       <c r="AE81" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF81">
         <v>0.25</v>
@@ -11952,10 +12030,10 @@
     </row>
     <row r="82" spans="1:48">
       <c r="A82" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B82" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C82" s="2">
         <v>45094.36113313658</v>
@@ -11976,16 +12054,16 @@
         <v>2205</v>
       </c>
       <c r="I82" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J82" t="b">
         <v>1</v>
       </c>
       <c r="K82" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="L82" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="M82">
         <v>82</v>
@@ -12021,7 +12099,7 @@
         <v>6.858</v>
       </c>
       <c r="AE82" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF82">
         <v>-0.542222</v>
@@ -12074,10 +12152,10 @@
     </row>
     <row r="83" spans="1:48">
       <c r="A83" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B83" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C83" s="2">
         <v>45094.36148015047</v>
@@ -12098,16 +12176,16 @@
         <v>2235</v>
       </c>
       <c r="I83" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
       </c>
       <c r="K83" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L83" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="M83">
         <v>38</v>
@@ -12143,7 +12221,7 @@
         <v>9.06266667</v>
       </c>
       <c r="AE83" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF83">
         <v>0.241111</v>
@@ -12196,10 +12274,10 @@
     </row>
     <row r="84" spans="1:48">
       <c r="A84" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C84" s="2">
         <v>45094.36182846065</v>
@@ -12220,16 +12298,16 @@
         <v>2265</v>
       </c>
       <c r="I84" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J84" t="b">
         <v>1</v>
       </c>
       <c r="K84" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="L84" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="M84">
         <v>115</v>
@@ -12265,7 +12343,7 @@
         <v>7.52833333</v>
       </c>
       <c r="AE84" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF84">
         <v>-0.167778</v>
@@ -12318,10 +12396,10 @@
     </row>
     <row r="85" spans="1:48">
       <c r="A85" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C85" s="2">
         <v>45094.36217550926</v>
@@ -12342,16 +12420,16 @@
         <v>2295</v>
       </c>
       <c r="I85" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J85" t="b">
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="L85" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="M85">
         <v>153</v>
@@ -12387,7 +12465,7 @@
         <v>8.686999999999999</v>
       </c>
       <c r="AE85" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="AF85">
         <v>0.126667</v>
@@ -12440,10 +12518,10 @@
     </row>
     <row r="86" spans="1:48">
       <c r="A86" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B86" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C86" s="2">
         <v>45094.36252275463</v>
@@ -12464,16 +12542,16 @@
         <v>2325</v>
       </c>
       <c r="I86" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J86" t="b">
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="L86" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="M86">
         <v>81</v>
@@ -12509,7 +12587,7 @@
         <v>8.78833333</v>
       </c>
       <c r="AE86" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF86">
         <v>0.011111</v>
@@ -12560,15 +12638,15 @@
         <v>7.999313</v>
       </c>
       <c r="AV86" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
     </row>
     <row r="87" spans="1:48">
       <c r="A87" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B87" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C87" s="2">
         <v>45094.3628693287</v>
@@ -12589,16 +12667,16 @@
         <v>2355</v>
       </c>
       <c r="I87" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J87" t="b">
         <v>1</v>
       </c>
       <c r="K87" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="L87" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="M87">
         <v>149</v>
@@ -12634,7 +12712,7 @@
         <v>7.173</v>
       </c>
       <c r="AE87" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF87">
         <v>-0.176667</v>
@@ -12687,10 +12765,10 @@
     </row>
     <row r="88" spans="1:48">
       <c r="A88" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B88" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C88" s="2">
         <v>45094.36321664352</v>
@@ -12711,16 +12789,16 @@
         <v>2385</v>
       </c>
       <c r="I88" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J88" t="b">
         <v>1</v>
       </c>
       <c r="K88" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="L88" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="M88">
         <v>119</v>
@@ -12756,7 +12834,7 @@
         <v>7.47766667</v>
       </c>
       <c r="AE88" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF88">
         <v>0.033333</v>
@@ -12809,10 +12887,10 @@
     </row>
     <row r="89" spans="1:48">
       <c r="A89" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B89" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C89" s="2">
         <v>45094.36356399306</v>
@@ -12833,16 +12911,16 @@
         <v>2415</v>
       </c>
       <c r="I89" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J89" t="b">
         <v>1</v>
       </c>
       <c r="K89" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="L89" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="M89">
         <v>175</v>
@@ -12878,7 +12956,7 @@
         <v>7.19333333</v>
       </c>
       <c r="AE89" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF89">
         <v>-0.031111</v>
@@ -12931,10 +13009,10 @@
     </row>
     <row r="90" spans="1:48">
       <c r="A90" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C90" s="2">
         <v>45094.36391078704</v>
@@ -12955,16 +13033,16 @@
         <v>2445</v>
       </c>
       <c r="I90" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J90" t="b">
         <v>1</v>
       </c>
       <c r="K90" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="L90" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="M90">
         <v>345</v>
@@ -13000,7 +13078,7 @@
         <v>6.96966667</v>
       </c>
       <c r="AE90" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF90">
         <v>-0.024444</v>
@@ -13053,10 +13131,10 @@
     </row>
     <row r="91" spans="1:48">
       <c r="A91" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B91" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C91" s="2">
         <v>45094.36425849537</v>
@@ -13077,16 +13155,16 @@
         <v>2475</v>
       </c>
       <c r="I91" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J91" t="b">
         <v>1</v>
       </c>
       <c r="K91" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="L91" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="M91">
         <v>109</v>
@@ -13122,7 +13200,7 @@
         <v>6.61433333</v>
       </c>
       <c r="AE91" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF91">
         <v>-0.038889</v>
@@ -13175,10 +13253,10 @@
     </row>
     <row r="92" spans="1:48">
       <c r="A92" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B92" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C92" s="2">
         <v>45094.36460600694</v>
@@ -13199,16 +13277,16 @@
         <v>2505</v>
       </c>
       <c r="I92" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J92" t="b">
         <v>1</v>
       </c>
       <c r="K92" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="L92" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="M92">
         <v>70</v>
@@ -13244,7 +13322,7 @@
         <v>6.553</v>
       </c>
       <c r="AE92" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF92">
         <v>-0.006667</v>
@@ -13297,10 +13375,10 @@
     </row>
     <row r="93" spans="1:48">
       <c r="A93" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C93" s="2">
         <v>45094.365646875</v>
@@ -13321,16 +13399,16 @@
         <v>2595</v>
       </c>
       <c r="I93" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J93" t="b">
         <v>1</v>
       </c>
       <c r="K93" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L93" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="M93">
         <v>190</v>
@@ -13366,7 +13444,7 @@
         <v>8.439666669999999</v>
       </c>
       <c r="AE93" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF93">
         <v>0.06876500000000001</v>
@@ -13419,10 +13497,10 @@
     </row>
     <row r="94" spans="1:48">
       <c r="A94" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B94" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C94" s="2">
         <v>45094.36599543982</v>
@@ -13443,16 +13521,16 @@
         <v>2625</v>
       </c>
       <c r="I94" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J94" t="b">
         <v>1</v>
       </c>
       <c r="K94" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="L94" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="M94">
         <v>280</v>
@@ -13488,7 +13566,7 @@
         <v>7.508</v>
       </c>
       <c r="AE94" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF94">
         <v>-0.101852</v>
@@ -13541,10 +13619,10 @@
     </row>
     <row r="95" spans="1:48">
       <c r="A95" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B95" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C95" s="2">
         <v>45094.36634144676</v>
@@ -13565,16 +13643,16 @@
         <v>2655</v>
       </c>
       <c r="I95" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J95" t="b">
         <v>1</v>
       </c>
       <c r="K95" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="L95" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="M95">
         <v>278</v>
@@ -13610,7 +13688,7 @@
         <v>7.62</v>
       </c>
       <c r="AE95" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF95">
         <v>0.012222</v>
@@ -13663,10 +13741,10 @@
     </row>
     <row r="96" spans="1:48">
       <c r="A96" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B96" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C96" s="2">
         <v>45094.36668912037</v>
@@ -13687,16 +13765,16 @@
         <v>2685</v>
       </c>
       <c r="I96" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J96" t="b">
         <v>1</v>
       </c>
       <c r="K96" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="L96" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="M96">
         <v>291</v>
@@ -13732,7 +13810,7 @@
         <v>7.57933333</v>
       </c>
       <c r="AE96" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF96">
         <v>-0.004444</v>
@@ -13785,10 +13863,10 @@
     </row>
     <row r="97" spans="1:47">
       <c r="A97" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B97" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C97" s="2">
         <v>45094.36703568287</v>
@@ -13809,16 +13887,16 @@
         <v>2715</v>
       </c>
       <c r="I97" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J97" t="b">
         <v>1</v>
       </c>
       <c r="K97" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="L97" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="M97">
         <v>210</v>
@@ -13854,7 +13932,7 @@
         <v>7.38633333</v>
       </c>
       <c r="AE97" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF97">
         <v>-0.021111</v>
@@ -13907,10 +13985,10 @@
     </row>
     <row r="98" spans="1:47">
       <c r="A98" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B98" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C98" s="2">
         <v>45094.36738269676</v>
@@ -13931,16 +14009,16 @@
         <v>2745</v>
       </c>
       <c r="I98" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J98" t="b">
         <v>1</v>
       </c>
       <c r="K98" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="L98" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="M98">
         <v>311</v>
@@ -13976,7 +14054,7 @@
         <v>7.49833333</v>
       </c>
       <c r="AE98" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF98">
         <v>0.012222</v>
@@ -14029,10 +14107,10 @@
     </row>
     <row r="99" spans="1:47">
       <c r="A99" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B99" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C99" s="2">
         <v>45094.36773050926</v>
@@ -14053,16 +14131,16 @@
         <v>2775</v>
       </c>
       <c r="I99" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J99" t="b">
         <v>1</v>
       </c>
       <c r="K99" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="L99" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="M99">
         <v>250</v>
@@ -14098,7 +14176,7 @@
         <v>6.83766667</v>
       </c>
       <c r="AE99" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF99">
         <v>-0.07222199999999999</v>
@@ -14151,10 +14229,10 @@
     </row>
     <row r="100" spans="1:47">
       <c r="A100" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B100" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C100" s="2">
         <v>45094.36807675926</v>
@@ -14175,16 +14253,16 @@
         <v>2805</v>
       </c>
       <c r="I100" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J100" t="b">
         <v>1</v>
       </c>
       <c r="K100" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="L100" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="M100">
         <v>260</v>
@@ -14220,7 +14298,7 @@
         <v>6.89866667</v>
       </c>
       <c r="AE100" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF100">
         <v>0.006667</v>
@@ -14273,10 +14351,10 @@
     </row>
     <row r="101" spans="1:47">
       <c r="A101" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B101" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C101" s="2">
         <v>45094.36877180556</v>
@@ -14297,16 +14375,16 @@
         <v>2865</v>
       </c>
       <c r="I101" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J101" t="b">
         <v>1</v>
       </c>
       <c r="K101" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="L101" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="M101">
         <v>248</v>
@@ -14342,7 +14420,7 @@
         <v>7.51316667</v>
       </c>
       <c r="AE101" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF101">
         <v>0.033611</v>
@@ -14395,10 +14473,10 @@
     </row>
     <row r="102" spans="1:47">
       <c r="A102" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B102" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C102" s="2">
         <v>45094.36946652778</v>
@@ -14419,16 +14497,16 @@
         <v>2925</v>
       </c>
       <c r="I102" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J102" t="b">
         <v>1</v>
       </c>
       <c r="K102" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="L102" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="M102">
         <v>290</v>
@@ -14464,7 +14542,7 @@
         <v>6.83266667</v>
       </c>
       <c r="AE102" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF102">
         <v>-0.037222</v>
@@ -14517,10 +14595,10 @@
     </row>
     <row r="103" spans="1:47">
       <c r="A103" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B103" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C103" s="2">
         <v>45094.36981353009</v>
@@ -14541,16 +14619,16 @@
         <v>2955</v>
       </c>
       <c r="I103" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J103" t="b">
         <v>1</v>
       </c>
       <c r="K103" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="L103" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="M103">
         <v>289</v>
@@ -14586,7 +14664,7 @@
         <v>7.53866667</v>
       </c>
       <c r="AE103" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF103">
         <v>0.077222</v>
@@ -14639,10 +14717,10 @@
     </row>
     <row r="104" spans="1:47">
       <c r="A104" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B104" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C104" s="2">
         <v>45094.37016189815</v>
@@ -14663,16 +14741,16 @@
         <v>2985</v>
       </c>
       <c r="I104" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J104" t="b">
         <v>1</v>
       </c>
       <c r="K104" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="L104" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="M104">
         <v>295</v>
@@ -14708,7 +14786,7 @@
         <v>7.244</v>
       </c>
       <c r="AE104" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF104">
         <v>-0.032222</v>
@@ -14761,10 +14839,10 @@
     </row>
     <row r="105" spans="1:47">
       <c r="A105" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B105" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C105" s="2">
         <v>45094.37050813658</v>
@@ -14785,16 +14863,16 @@
         <v>3015</v>
       </c>
       <c r="I105" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J105" t="b">
         <v>1</v>
       </c>
       <c r="K105" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="L105" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="M105">
         <v>276</v>
@@ -14830,7 +14908,7 @@
         <v>7.38633333</v>
       </c>
       <c r="AE105" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF105">
         <v>0.015556</v>
@@ -14883,10 +14961,10 @@
     </row>
     <row r="106" spans="1:47">
       <c r="A106" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B106" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C106" s="2">
         <v>45094.37085590278</v>
@@ -14907,16 +14985,16 @@
         <v>3045</v>
       </c>
       <c r="I106" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J106" t="b">
         <v>1</v>
       </c>
       <c r="K106" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="L106" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="M106">
         <v>328</v>
@@ -14952,7 +15030,7 @@
         <v>7.45766667</v>
       </c>
       <c r="AE106" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF106">
         <v>0.007778</v>
@@ -15005,10 +15083,10 @@
     </row>
     <row r="107" spans="1:47">
       <c r="A107" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B107" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C107" s="2">
         <v>45094.37120224537</v>
@@ -15029,16 +15107,16 @@
         <v>3075</v>
       </c>
       <c r="I107" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J107" t="b">
         <v>1</v>
       </c>
       <c r="K107" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="L107" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="M107">
         <v>311</v>
@@ -15074,7 +15152,7 @@
         <v>7.234</v>
       </c>
       <c r="AE107" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="AF107">
         <v>-0.024444</v>
@@ -15137,156 +15215,156 @@
   <sheetData>
     <row r="1" spans="1:48">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:48">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C2" s="2">
         <v>45094.37155011574</v>
@@ -15307,16 +15385,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="L2" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="M2">
         <v>318</v>
@@ -15352,7 +15430,7 @@
         <v>-10.09933333</v>
       </c>
       <c r="AE2" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AG2">
         <v>-33.133333</v>
@@ -15369,10 +15447,10 @@
     </row>
     <row r="3" spans="1:48">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C3" s="2">
         <v>45094.37189753472</v>
@@ -15393,16 +15471,16 @@
         <v>30</v>
       </c>
       <c r="I3" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="L3" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="M3">
         <v>297</v>
@@ -15438,7 +15516,7 @@
         <v>-15.77833333</v>
       </c>
       <c r="AE3" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF3">
         <v>-0.621111</v>
@@ -15479,10 +15557,10 @@
     </row>
     <row r="4" spans="1:48">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C4" s="2">
         <v>45094.37259148148</v>
@@ -15503,16 +15581,16 @@
         <v>90</v>
       </c>
       <c r="I4" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="L4" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="M4">
         <v>272</v>
@@ -15548,7 +15626,7 @@
         <v>-13.83283333</v>
       </c>
       <c r="AE4" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF4">
         <v>0.106389</v>
@@ -15601,10 +15679,10 @@
     </row>
     <row r="5" spans="1:48">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2">
         <v>45094.37328638889</v>
@@ -15625,16 +15703,16 @@
         <v>150</v>
       </c>
       <c r="I5" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="L5" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="M5">
         <v>280</v>
@@ -15670,7 +15748,7 @@
         <v>-12.61366667</v>
       </c>
       <c r="AE5" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF5">
         <v>0.066667</v>
@@ -15723,10 +15801,10 @@
     </row>
     <row r="6" spans="1:48">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2">
         <v>45094.37363313657</v>
@@ -15747,16 +15825,16 @@
         <v>180</v>
       </c>
       <c r="I6" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="L6" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
       <c r="M6">
         <v>235</v>
@@ -15792,7 +15870,7 @@
         <v>-13.35033333</v>
       </c>
       <c r="AE6" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF6">
         <v>-0.080556</v>
@@ -15845,10 +15923,10 @@
     </row>
     <row r="7" spans="1:48">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C7" s="2">
         <v>45094.37398188657</v>
@@ -15869,16 +15947,16 @@
         <v>210</v>
       </c>
       <c r="I7" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="L7" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="M7">
         <v>238</v>
@@ -15914,7 +15992,7 @@
         <v>-11.26733333</v>
       </c>
       <c r="AE7" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF7">
         <v>0.227778</v>
@@ -15967,10 +16045,10 @@
     </row>
     <row r="8" spans="1:48">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2">
         <v>45094.37467542824</v>
@@ -15991,16 +16069,16 @@
         <v>270</v>
       </c>
       <c r="I8" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="L8" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="M8">
         <v>194</v>
@@ -16036,7 +16114,7 @@
         <v>-12.253</v>
       </c>
       <c r="AE8" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF8">
         <v>-0.053889</v>
@@ -16089,10 +16167,10 @@
     </row>
     <row r="9" spans="1:48">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2">
         <v>45094.37502232639</v>
@@ -16113,16 +16191,16 @@
         <v>300</v>
       </c>
       <c r="I9" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="L9" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="M9">
         <v>140</v>
@@ -16158,7 +16236,7 @@
         <v>-11.694</v>
       </c>
       <c r="AE9" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF9">
         <v>0.061111</v>
@@ -16211,10 +16289,10 @@
     </row>
     <row r="10" spans="1:48">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2">
         <v>45094.37536953704</v>
@@ -16235,16 +16313,16 @@
         <v>330</v>
       </c>
       <c r="I10" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="L10" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="M10">
         <v>30</v>
@@ -16280,7 +16358,7 @@
         <v>-9.835000000000001</v>
       </c>
       <c r="AE10" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF10">
         <v>0.203333</v>
@@ -16333,10 +16411,10 @@
     </row>
     <row r="11" spans="1:48">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2">
         <v>45094.37571655092</v>
@@ -16357,16 +16435,16 @@
         <v>360</v>
       </c>
       <c r="I11" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="L11" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="M11">
         <v>174</v>
@@ -16402,7 +16480,7 @@
         <v>-10.861</v>
       </c>
       <c r="AE11" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF11">
         <v>-0.112222</v>
@@ -16455,10 +16533,10 @@
     </row>
     <row r="12" spans="1:48">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C12" s="2">
         <v>45094.37606354167</v>
@@ -16479,16 +16557,16 @@
         <v>390</v>
       </c>
       <c r="I12" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="L12" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="M12">
         <v>25</v>
@@ -16524,7 +16602,7 @@
         <v>-10.10933333</v>
       </c>
       <c r="AE12" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF12">
         <v>0.082222</v>
@@ -16577,10 +16655,10 @@
     </row>
     <row r="13" spans="1:48">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C13" s="2">
         <v>45094.37641184028</v>
@@ -16601,16 +16679,16 @@
         <v>420</v>
       </c>
       <c r="I13" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="L13" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="M13">
         <v>39</v>
@@ -16646,7 +16724,7 @@
         <v>-9.438333330000001</v>
       </c>
       <c r="AE13" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF13">
         <v>0.073333</v>
@@ -16699,10 +16777,10 @@
     </row>
     <row r="14" spans="1:48">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C14" s="2">
         <v>45094.37675826389</v>
@@ -16723,16 +16801,16 @@
         <v>450</v>
       </c>
       <c r="I14" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="L14" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="M14">
         <v>66</v>
@@ -16768,7 +16846,7 @@
         <v>-8.676666669999999</v>
       </c>
       <c r="AE14" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF14">
         <v>0.083333</v>
@@ -16821,10 +16899,10 @@
     </row>
     <row r="15" spans="1:48">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C15" s="2">
         <v>45094.3771059838</v>
@@ -16845,16 +16923,16 @@
         <v>480</v>
       </c>
       <c r="I15" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="L15" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="M15">
         <v>94</v>
@@ -16890,7 +16968,7 @@
         <v>-9.702999999999999</v>
       </c>
       <c r="AE15" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF15">
         <v>-0.112222</v>
@@ -16943,10 +17021,10 @@
     </row>
     <row r="16" spans="1:48">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C16" s="2">
         <v>45094.37745237268</v>
@@ -16967,16 +17045,16 @@
         <v>510</v>
       </c>
       <c r="I16" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="L16" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="M16">
         <v>82</v>
@@ -17012,7 +17090,7 @@
         <v>-10.52566667</v>
       </c>
       <c r="AE16" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF16">
         <v>-0.09</v>
@@ -17065,10 +17143,10 @@
     </row>
     <row r="17" spans="1:47">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C17" s="2">
         <v>45094.37918865741</v>
@@ -17089,16 +17167,16 @@
         <v>660</v>
       </c>
       <c r="I17" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="L17" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="M17">
         <v>131</v>
@@ -17134,7 +17212,7 @@
         <v>-10.0706</v>
       </c>
       <c r="AE17" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF17">
         <v>0.009956</v>
@@ -17187,10 +17265,10 @@
     </row>
     <row r="18" spans="1:47">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C18" s="2">
         <v>45094.37953603009</v>
@@ -17211,16 +17289,16 @@
         <v>690</v>
       </c>
       <c r="I18" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="L18" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="M18">
         <v>121</v>
@@ -17256,7 +17334,7 @@
         <v>-9.13366667</v>
       </c>
       <c r="AE18" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF18">
         <v>0.102444</v>
@@ -17309,10 +17387,10 @@
     </row>
     <row r="19" spans="1:47">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C19" s="2">
         <v>45094.3798837963</v>
@@ -17333,16 +17411,16 @@
         <v>720</v>
       </c>
       <c r="I19" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="L19" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="M19">
         <v>97</v>
@@ -17378,7 +17456,7 @@
         <v>-8.981666669999999</v>
       </c>
       <c r="AE19" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF19">
         <v>0.016667</v>
@@ -17431,10 +17509,10 @@
     </row>
     <row r="20" spans="1:47">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C20" s="2">
         <v>45094.38057789352</v>
@@ -17455,16 +17533,16 @@
         <v>780</v>
       </c>
       <c r="I20" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="L20" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="M20">
         <v>114</v>
@@ -17500,7 +17578,7 @@
         <v>-8.580166670000001</v>
       </c>
       <c r="AE20" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF20">
         <v>0.021944</v>
@@ -17553,10 +17631,10 @@
     </row>
     <row r="21" spans="1:47">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C21" s="2">
         <v>45094.38092582176</v>
@@ -17577,16 +17655,16 @@
         <v>810</v>
       </c>
       <c r="I21" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="L21" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="M21">
         <v>122</v>
@@ -17622,7 +17700,7 @@
         <v>-8.382</v>
       </c>
       <c r="AE21" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF21">
         <v>0.021667</v>
@@ -17675,10 +17753,10 @@
     </row>
     <row r="22" spans="1:47">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C22" s="2">
         <v>45094.38148519676</v>
@@ -17699,16 +17777,16 @@
         <v>840</v>
       </c>
       <c r="I22" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="L22" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="M22">
         <v>124</v>
@@ -17744,7 +17822,7 @@
         <v>-7.945</v>
       </c>
       <c r="AE22" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF22">
         <v>0.047778</v>
@@ -17797,10 +17875,10 @@
     </row>
     <row r="23" spans="1:47">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C23" s="2">
         <v>45094.3816187037</v>
@@ -17821,16 +17899,16 @@
         <v>870</v>
       </c>
       <c r="I23" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="L23" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="M23">
         <v>123</v>
@@ -17866,7 +17944,7 @@
         <v>-7.742</v>
       </c>
       <c r="AE23" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF23">
         <v>0.022222</v>
@@ -17919,10 +17997,10 @@
     </row>
     <row r="24" spans="1:47">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C24" s="2">
         <v>45094.38196700231</v>
@@ -17943,16 +18021,16 @@
         <v>900</v>
       </c>
       <c r="I24" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="L24" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="M24">
         <v>114</v>
@@ -17988,7 +18066,7 @@
         <v>-6.69533333</v>
       </c>
       <c r="AE24" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF24">
         <v>0.114444</v>
@@ -18041,10 +18119,10 @@
     </row>
     <row r="25" spans="1:47">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C25" s="2">
         <v>45094.38231439815</v>
@@ -18065,16 +18143,16 @@
         <v>930</v>
       </c>
       <c r="I25" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="L25" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="M25">
         <v>115</v>
@@ -18110,7 +18188,7 @@
         <v>-7.07133333</v>
       </c>
       <c r="AE25" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF25">
         <v>-0.041111</v>
@@ -18163,10 +18241,10 @@
     </row>
     <row r="26" spans="1:47">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C26" s="2">
         <v>45094.38300857639</v>
@@ -18187,16 +18265,16 @@
         <v>990</v>
       </c>
       <c r="I26" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="L26" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="M26">
         <v>121</v>
@@ -18232,7 +18310,7 @@
         <v>-7.00016667</v>
       </c>
       <c r="AE26" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF26">
         <v>0.003889</v>
@@ -18285,10 +18363,10 @@
     </row>
     <row r="27" spans="1:47">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C27" s="2">
         <v>45094.38335523148</v>
@@ -18309,16 +18387,16 @@
         <v>1020</v>
       </c>
       <c r="I27" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="L27" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="M27">
         <v>115</v>
@@ -18354,7 +18432,7 @@
         <v>-6.89866667</v>
       </c>
       <c r="AE27" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF27">
         <v>0.011111</v>
@@ -18407,10 +18485,10 @@
     </row>
     <row r="28" spans="1:47">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C28" s="2">
         <v>45094.38370341435</v>
@@ -18431,16 +18509,16 @@
         <v>1050</v>
       </c>
       <c r="I28" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="L28" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="M28">
         <v>120</v>
@@ -18476,7 +18554,7 @@
         <v>-6.604</v>
       </c>
       <c r="AE28" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF28">
         <v>0.032222</v>
@@ -18529,10 +18607,10 @@
     </row>
     <row r="29" spans="1:47">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C29" s="2">
         <v>45094.38405054398</v>
@@ -18553,16 +18631,16 @@
         <v>1080</v>
       </c>
       <c r="I29" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="L29" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="M29">
         <v>120</v>
@@ -18598,7 +18676,7 @@
         <v>-6.58366667</v>
       </c>
       <c r="AE29" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF29">
         <v>0.002222</v>
@@ -18651,10 +18729,10 @@
     </row>
     <row r="30" spans="1:47">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C30" s="2">
         <v>45094.38439748843</v>
@@ -18675,16 +18753,16 @@
         <v>1110</v>
       </c>
       <c r="I30" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="L30" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="M30">
         <v>116</v>
@@ -18720,7 +18798,7 @@
         <v>-6.48233333</v>
       </c>
       <c r="AE30" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF30">
         <v>0.011111</v>
@@ -18773,10 +18851,10 @@
     </row>
     <row r="31" spans="1:47">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C31" s="2">
         <v>45094.38474394676</v>
@@ -18797,16 +18875,16 @@
         <v>1140</v>
       </c>
       <c r="I31" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="L31" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="M31">
         <v>118</v>
@@ -18842,7 +18920,7 @@
         <v>-6.40066667</v>
       </c>
       <c r="AE31" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF31">
         <v>0.008888999999999999</v>
@@ -18895,10 +18973,10 @@
     </row>
     <row r="32" spans="1:47">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C32" s="2">
         <v>45094.38543905093</v>
@@ -18919,16 +18997,16 @@
         <v>1200</v>
       </c>
       <c r="I32" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="L32" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
       <c r="M32">
         <v>125</v>
@@ -18964,7 +19042,7 @@
         <v>-6.162</v>
       </c>
       <c r="AE32" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF32">
         <v>0.013056</v>
@@ -19017,10 +19095,10 @@
     </row>
     <row r="33" spans="1:47">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C33" s="2">
         <v>45094.38578665509</v>
@@ -19041,16 +19119,16 @@
         <v>1230</v>
       </c>
       <c r="I33" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="L33" t="s">
-        <v>432</v>
+        <v>442</v>
       </c>
       <c r="M33">
         <v>125</v>
@@ -19086,7 +19164,7 @@
         <v>-5.842</v>
       </c>
       <c r="AE33" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF33">
         <v>0.035</v>
@@ -19139,10 +19217,10 @@
     </row>
     <row r="34" spans="1:47">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C34" s="2">
         <v>45094.3861330787</v>
@@ -19163,16 +19241,16 @@
         <v>1260</v>
       </c>
       <c r="I34" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="L34" t="s">
-        <v>433</v>
+        <v>443</v>
       </c>
       <c r="M34">
         <v>122</v>
@@ -19208,7 +19286,7 @@
         <v>-5.87266667</v>
       </c>
       <c r="AE34" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF34">
         <v>-0.003333</v>
@@ -19261,10 +19339,10 @@
     </row>
     <row r="35" spans="1:47">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C35" s="2">
         <v>45094.38648175926</v>
@@ -19285,16 +19363,16 @@
         <v>1290</v>
       </c>
       <c r="I35" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="L35" t="s">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="M35">
         <v>115</v>
@@ -19330,7 +19408,7 @@
         <v>-5.791</v>
       </c>
       <c r="AE35" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF35">
         <v>0.008888999999999999</v>
@@ -19383,10 +19461,10 @@
     </row>
     <row r="36" spans="1:47">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C36" s="2">
         <v>45094.38682829861</v>
@@ -19407,16 +19485,16 @@
         <v>1320</v>
       </c>
       <c r="I36" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="L36" t="s">
-        <v>435</v>
+        <v>445</v>
       </c>
       <c r="M36">
         <v>114</v>
@@ -19452,7 +19530,7 @@
         <v>-5.71</v>
       </c>
       <c r="AE36" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF36">
         <v>0.008888999999999999</v>
@@ -19505,10 +19583,10 @@
     </row>
     <row r="37" spans="1:47">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C37" s="2">
         <v>45094.38717591435</v>
@@ -19529,16 +19607,16 @@
         <v>1350</v>
       </c>
       <c r="I37" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="L37" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="M37">
         <v>121</v>
@@ -19574,7 +19652,7 @@
         <v>-5.67933333</v>
       </c>
       <c r="AE37" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF37">
         <v>0.003333</v>
@@ -19627,10 +19705,10 @@
     </row>
     <row r="38" spans="1:47">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C38" s="2">
         <v>45094.38752283565</v>
@@ -19651,16 +19729,16 @@
         <v>1380</v>
       </c>
       <c r="I38" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="L38" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="M38">
         <v>130</v>
@@ -19696,7 +19774,7 @@
         <v>-5.761</v>
       </c>
       <c r="AE38" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF38">
         <v>-0.008888999999999999</v>
@@ -19749,10 +19827,10 @@
     </row>
     <row r="39" spans="1:47">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C39" s="2">
         <v>45094.38787030092</v>
@@ -19773,16 +19851,16 @@
         <v>1410</v>
       </c>
       <c r="I39" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="L39" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="M39">
         <v>130</v>
@@ -19818,7 +19896,7 @@
         <v>-5.54733333</v>
       </c>
       <c r="AE39" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF39">
         <v>0.023333</v>
@@ -19871,10 +19949,10 @@
     </row>
     <row r="40" spans="1:47">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C40" s="2">
         <v>45094.38821748843</v>
@@ -19895,16 +19973,16 @@
         <v>1440</v>
       </c>
       <c r="I40" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="L40" t="s">
-        <v>439</v>
+        <v>449</v>
       </c>
       <c r="M40">
         <v>129</v>
@@ -19940,7 +20018,7 @@
         <v>-5.48633333</v>
       </c>
       <c r="AE40" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF40">
         <v>0.006667</v>
@@ -19993,10 +20071,10 @@
     </row>
     <row r="41" spans="1:47">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C41" s="2">
         <v>45094.38856420139</v>
@@ -20017,16 +20095,16 @@
         <v>1470</v>
       </c>
       <c r="I41" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="L41" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
       <c r="M41">
         <v>129</v>
@@ -20062,7 +20140,7 @@
         <v>-5.63866667</v>
       </c>
       <c r="AE41" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF41">
         <v>-0.016667</v>
@@ -20115,10 +20193,10 @@
     </row>
     <row r="42" spans="1:47">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C42" s="2">
         <v>45094.38891199074</v>
@@ -20139,16 +20217,16 @@
         <v>1500</v>
       </c>
       <c r="I42" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="L42" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="M42">
         <v>118</v>
@@ -20184,7 +20262,7 @@
         <v>-5.65933333</v>
       </c>
       <c r="AE42" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF42">
         <v>-0.002222</v>
@@ -20237,10 +20315,10 @@
     </row>
     <row r="43" spans="1:47">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C43" s="2">
         <v>45094.38925871528</v>
@@ -20261,16 +20339,16 @@
         <v>1530</v>
       </c>
       <c r="I43" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="L43" t="s">
-        <v>442</v>
+        <v>452</v>
       </c>
       <c r="M43">
         <v>106</v>
@@ -20306,7 +20384,7 @@
         <v>-5.476</v>
       </c>
       <c r="AE43" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF43">
         <v>0.02</v>
@@ -20359,10 +20437,10 @@
     </row>
     <row r="44" spans="1:47">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C44" s="2">
         <v>45094.38960546297</v>
@@ -20383,16 +20461,16 @@
         <v>1560</v>
       </c>
       <c r="I44" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="L44" t="s">
-        <v>443</v>
+        <v>453</v>
       </c>
       <c r="M44">
         <v>108</v>
@@ -20428,7 +20506,7 @@
         <v>-5.263</v>
       </c>
       <c r="AE44" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF44">
         <v>0.023333</v>
@@ -20481,10 +20559,10 @@
     </row>
     <row r="45" spans="1:47">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C45" s="2">
         <v>45094.38995331019</v>
@@ -20505,16 +20583,16 @@
         <v>1590</v>
       </c>
       <c r="I45" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="L45" t="s">
-        <v>444</v>
+        <v>454</v>
       </c>
       <c r="M45">
         <v>102</v>
@@ -20550,7 +20628,7 @@
         <v>-5.263</v>
       </c>
       <c r="AE45" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF45">
         <v>0</v>
@@ -20603,10 +20681,10 @@
     </row>
     <row r="46" spans="1:47">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C46" s="2">
         <v>45094.39030013889</v>
@@ -20627,16 +20705,16 @@
         <v>1620</v>
       </c>
       <c r="I46" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="L46" t="s">
-        <v>445</v>
+        <v>455</v>
       </c>
       <c r="M46">
         <v>107</v>
@@ -20672,7 +20750,7 @@
         <v>-5.10033333</v>
       </c>
       <c r="AE46" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF46">
         <v>0.017778</v>
@@ -20725,10 +20803,10 @@
     </row>
     <row r="47" spans="1:47">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C47" s="2">
         <v>45094.39064818287</v>
@@ -20749,16 +20827,16 @@
         <v>1650</v>
       </c>
       <c r="I47" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="L47" t="s">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="M47">
         <v>110</v>
@@ -20794,7 +20872,7 @@
         <v>-5.13066667</v>
       </c>
       <c r="AE47" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF47">
         <v>-0.003333</v>
@@ -20847,10 +20925,10 @@
     </row>
     <row r="48" spans="1:47">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C48" s="2">
         <v>45094.39099511574</v>
@@ -20871,16 +20949,16 @@
         <v>1680</v>
       </c>
       <c r="I48" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="L48" t="s">
-        <v>447</v>
+        <v>457</v>
       </c>
       <c r="M48">
         <v>111</v>
@@ -20916,7 +20994,7 @@
         <v>-5.151</v>
       </c>
       <c r="AE48" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF48">
         <v>-0.002222</v>
@@ -20969,10 +21047,10 @@
     </row>
     <row r="49" spans="1:47">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C49" s="2">
         <v>45094.39203666666</v>
@@ -20993,16 +21071,16 @@
         <v>1770</v>
       </c>
       <c r="I49" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="L49" t="s">
-        <v>448</v>
+        <v>458</v>
       </c>
       <c r="M49">
         <v>106</v>
@@ -21038,7 +21116,7 @@
         <v>-4.484</v>
       </c>
       <c r="AE49" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF49">
         <v>0.024321</v>
@@ -21091,10 +21169,10 @@
     </row>
     <row r="50" spans="1:47">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C50" s="2">
         <v>45094.39239282408</v>
@@ -21115,16 +21193,16 @@
         <v>1800</v>
       </c>
       <c r="I50" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="L50" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="M50">
         <v>137</v>
@@ -21160,7 +21238,7 @@
         <v>-3.82</v>
       </c>
       <c r="AE50" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF50">
         <v>0.072593</v>
@@ -21213,10 +21291,10 @@
     </row>
     <row r="51" spans="1:47">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C51" s="2">
         <v>45094.39273111111</v>
@@ -21237,16 +21315,16 @@
         <v>1830</v>
       </c>
       <c r="I51" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="L51" t="s">
-        <v>450</v>
+        <v>460</v>
       </c>
       <c r="M51">
         <v>98</v>
@@ -21282,7 +21360,7 @@
         <v>-3.871</v>
       </c>
       <c r="AE51" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF51">
         <v>-0.005556</v>
@@ -21335,10 +21413,10 @@
     </row>
     <row r="52" spans="1:47">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C52" s="2">
         <v>45094.39307847223</v>
@@ -21359,16 +21437,16 @@
         <v>1860</v>
       </c>
       <c r="I52" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="L52" t="s">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="M52">
         <v>129</v>
@@ -21404,7 +21482,7 @@
         <v>-3.993</v>
       </c>
       <c r="AE52" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF52">
         <v>-0.013333</v>
@@ -21457,10 +21535,10 @@
     </row>
     <row r="53" spans="1:47">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C53" s="2">
         <v>45094.39342516204</v>
@@ -21481,16 +21559,16 @@
         <v>1890</v>
       </c>
       <c r="I53" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J53" t="b">
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="L53" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="M53">
         <v>99</v>
@@ -21526,7 +21604,7 @@
         <v>-3.627</v>
       </c>
       <c r="AE53" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF53">
         <v>0.04</v>
@@ -21579,10 +21657,10 @@
     </row>
     <row r="54" spans="1:47">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B54" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C54" s="2">
         <v>45094.39377326389</v>
@@ -21603,16 +21681,16 @@
         <v>1920</v>
       </c>
       <c r="I54" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J54" t="b">
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="L54" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="M54">
         <v>112</v>
@@ -21648,7 +21726,7 @@
         <v>-3.688</v>
       </c>
       <c r="AE54" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF54">
         <v>-0.006667</v>
@@ -21701,10 +21779,10 @@
     </row>
     <row r="55" spans="1:47">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C55" s="2">
         <v>45094.39446917824</v>
@@ -21725,16 +21803,16 @@
         <v>1980</v>
       </c>
       <c r="I55" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J55" t="b">
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="L55" t="s">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="M55">
         <v>99</v>
@@ -21770,7 +21848,7 @@
         <v>-3.66283333</v>
       </c>
       <c r="AE55" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF55">
         <v>0.001389</v>
@@ -21823,10 +21901,10 @@
     </row>
     <row r="56" spans="1:47">
       <c r="A56" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C56" s="2">
         <v>45094.39487491898</v>
@@ -21847,16 +21925,16 @@
         <v>2010</v>
       </c>
       <c r="I56" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J56" t="b">
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="L56" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="M56">
         <v>162</v>
@@ -21892,7 +21970,7 @@
         <v>-3.58633333</v>
       </c>
       <c r="AE56" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF56">
         <v>0.008333</v>
@@ -21945,10 +22023,10 @@
     </row>
     <row r="57" spans="1:47">
       <c r="A57" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C57" s="2">
         <v>45094.39516130787</v>
@@ -21969,16 +22047,16 @@
         <v>2040</v>
       </c>
       <c r="I57" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="L57" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
       <c r="M57">
         <v>100</v>
@@ -22014,7 +22092,7 @@
         <v>-3.627</v>
       </c>
       <c r="AE57" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF57">
         <v>-0.004444</v>
@@ -22067,10 +22145,10 @@
     </row>
     <row r="58" spans="1:47">
       <c r="A58" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B58" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C58" s="2">
         <v>45094.39551729167</v>
@@ -22091,16 +22169,16 @@
         <v>2070</v>
       </c>
       <c r="I58" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="L58" t="s">
-        <v>457</v>
+        <v>467</v>
       </c>
       <c r="M58">
         <v>169</v>
@@ -22136,7 +22214,7 @@
         <v>-3.59666667</v>
       </c>
       <c r="AE58" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF58">
         <v>0.003333</v>
@@ -22189,10 +22267,10 @@
     </row>
     <row r="59" spans="1:47">
       <c r="A59" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B59" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C59" s="2">
         <v>45094.3958559838</v>
@@ -22213,16 +22291,16 @@
         <v>2100</v>
       </c>
       <c r="I59" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="L59" t="s">
-        <v>458</v>
+        <v>468</v>
       </c>
       <c r="M59">
         <v>113</v>
@@ -22258,7 +22336,7 @@
         <v>-3.62733333</v>
       </c>
       <c r="AE59" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF59">
         <v>-0.003333</v>
@@ -22311,10 +22389,10 @@
     </row>
     <row r="60" spans="1:47">
       <c r="A60" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B60" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C60" s="2">
         <v>45094.39620366898</v>
@@ -22335,16 +22413,16 @@
         <v>2130</v>
       </c>
       <c r="I60" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="L60" t="s">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="M60">
         <v>162</v>
@@ -22380,7 +22458,7 @@
         <v>-3.83033333</v>
       </c>
       <c r="AE60" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF60">
         <v>-0.022222</v>
@@ -22433,10 +22511,10 @@
     </row>
     <row r="61" spans="1:47">
       <c r="A61" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C61" s="2">
         <v>45094.39654993056</v>
@@ -22457,16 +22535,16 @@
         <v>2160</v>
       </c>
       <c r="I61" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="L61" t="s">
-        <v>460</v>
+        <v>470</v>
       </c>
       <c r="M61">
         <v>101</v>
@@ -22502,7 +22580,7 @@
         <v>-3.57633333</v>
       </c>
       <c r="AE61" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF61">
         <v>0.027778</v>
@@ -22555,10 +22633,10 @@
     </row>
     <row r="62" spans="1:47">
       <c r="A62" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C62" s="2">
         <v>45094.3975924537</v>
@@ -22579,16 +22657,16 @@
         <v>2250</v>
       </c>
       <c r="I62" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="L62" t="s">
-        <v>461</v>
+        <v>471</v>
       </c>
       <c r="M62">
         <v>171</v>
@@ -22624,7 +22702,7 @@
         <v>-3.495</v>
       </c>
       <c r="AE62" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF62">
         <v>0.002963</v>
@@ -22677,10 +22755,10 @@
     </row>
     <row r="63" spans="1:47">
       <c r="A63" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B63" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C63" s="2">
         <v>45094.39793901621</v>
@@ -22701,16 +22779,16 @@
         <v>2280</v>
       </c>
       <c r="I63" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="L63" t="s">
-        <v>462</v>
+        <v>472</v>
       </c>
       <c r="M63">
         <v>139</v>
@@ -22746,7 +22824,7 @@
         <v>-3.39333333</v>
       </c>
       <c r="AE63" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF63">
         <v>0.011111</v>
@@ -22799,10 +22877,10 @@
     </row>
     <row r="64" spans="1:47">
       <c r="A64" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C64" s="2">
         <v>45094.3982862037</v>
@@ -22823,16 +22901,16 @@
         <v>2310</v>
       </c>
       <c r="I64" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J64" t="b">
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="L64" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
       <c r="M64">
         <v>114</v>
@@ -22868,7 +22946,7 @@
         <v>-3.434</v>
       </c>
       <c r="AE64" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF64">
         <v>-0.004444</v>
@@ -22921,10 +22999,10 @@
     </row>
     <row r="65" spans="1:47">
       <c r="A65" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B65" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C65" s="2">
         <v>45094.39863377315</v>
@@ -22945,16 +23023,16 @@
         <v>2340</v>
       </c>
       <c r="I65" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J65" t="b">
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="L65" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="M65">
         <v>171</v>
@@ -22990,7 +23068,7 @@
         <v>-3.37333333</v>
       </c>
       <c r="AE65" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF65">
         <v>0.006667</v>
@@ -23043,10 +23121,10 @@
     </row>
     <row r="66" spans="1:47">
       <c r="A66" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B66" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C66" s="2">
         <v>45094.39898017361</v>
@@ -23067,16 +23145,16 @@
         <v>2370</v>
       </c>
       <c r="I66" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J66" t="b">
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="L66" t="s">
-        <v>465</v>
+        <v>475</v>
       </c>
       <c r="M66">
         <v>140</v>
@@ -23112,7 +23190,7 @@
         <v>-3.35266667</v>
       </c>
       <c r="AE66" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF66">
         <v>0.002222</v>
@@ -23165,10 +23243,10 @@
     </row>
     <row r="67" spans="1:47">
       <c r="A67" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B67" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C67" s="2">
         <v>45094.39932827546</v>
@@ -23189,16 +23267,16 @@
         <v>2400</v>
       </c>
       <c r="I67" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J67" t="b">
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="L67" t="s">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="M67">
         <v>93</v>
@@ -23234,7 +23312,7 @@
         <v>-3.19033333</v>
       </c>
       <c r="AE67" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF67">
         <v>0.017778</v>
@@ -23287,10 +23365,10 @@
     </row>
     <row r="68" spans="1:47">
       <c r="A68" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B68" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C68" s="2">
         <v>45094.40002246528</v>
@@ -23311,16 +23389,16 @@
         <v>2460</v>
       </c>
       <c r="I68" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J68" t="b">
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="L68" t="s">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="M68">
         <v>156</v>
@@ -23356,7 +23434,7 @@
         <v>-3.11916667</v>
       </c>
       <c r="AE68" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF68">
         <v>0.003889</v>
@@ -23409,10 +23487,10 @@
     </row>
     <row r="69" spans="1:47">
       <c r="A69" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B69" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C69" s="2">
         <v>45094.40036984954</v>
@@ -23433,16 +23511,16 @@
         <v>2490</v>
       </c>
       <c r="I69" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J69" t="b">
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="L69" t="s">
-        <v>468</v>
+        <v>478</v>
       </c>
       <c r="M69">
         <v>149</v>
@@ -23478,7 +23556,7 @@
         <v>-3.00733333</v>
       </c>
       <c r="AE69" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF69">
         <v>0.012222</v>
@@ -23531,10 +23609,10 @@
     </row>
     <row r="70" spans="1:47">
       <c r="A70" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B70" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C70" s="2">
         <v>45094.40071681713</v>
@@ -23555,16 +23633,16 @@
         <v>2520</v>
       </c>
       <c r="I70" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J70" t="b">
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
       <c r="L70" t="s">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="M70">
         <v>131</v>
@@ -23600,7 +23678,7 @@
         <v>-3.07833333</v>
       </c>
       <c r="AE70" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF70">
         <v>-0.007778</v>
@@ -23653,10 +23731,10 @@
     </row>
     <row r="71" spans="1:47">
       <c r="A71" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B71" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C71" s="2">
         <v>45094.4010644213</v>
@@ -23677,16 +23755,16 @@
         <v>2550</v>
       </c>
       <c r="I71" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J71" t="b">
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="L71" t="s">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="M71">
         <v>134</v>
@@ -23722,7 +23800,7 @@
         <v>-2.99733333</v>
       </c>
       <c r="AE71" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF71">
         <v>0.008888999999999999</v>
@@ -23775,10 +23853,10 @@
     </row>
     <row r="72" spans="1:47">
       <c r="A72" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B72" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C72" s="2">
         <v>45094.40141065972</v>
@@ -23799,16 +23877,16 @@
         <v>2580</v>
       </c>
       <c r="I72" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="L72" t="s">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="M72">
         <v>147</v>
@@ -23844,7 +23922,7 @@
         <v>-2.94633333</v>
       </c>
       <c r="AE72" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF72">
         <v>0.005556</v>
@@ -23897,10 +23975,10 @@
     </row>
     <row r="73" spans="1:47">
       <c r="A73" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B73" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C73" s="2">
         <v>45094.40175862268</v>
@@ -23921,16 +23999,16 @@
         <v>2610</v>
       </c>
       <c r="I73" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J73" t="b">
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="L73" t="s">
-        <v>472</v>
+        <v>482</v>
       </c>
       <c r="M73">
         <v>129</v>
@@ -23966,7 +24044,7 @@
         <v>-2.94633333</v>
       </c>
       <c r="AE73" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF73">
         <v>0</v>
@@ -24019,10 +24097,10 @@
     </row>
     <row r="74" spans="1:47">
       <c r="A74" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C74" s="2">
         <v>45094.40245278935</v>
@@ -24043,16 +24121,16 @@
         <v>2670</v>
       </c>
       <c r="I74" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J74" t="b">
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="L74" t="s">
-        <v>473</v>
+        <v>483</v>
       </c>
       <c r="M74">
         <v>131</v>
@@ -24088,7 +24166,7 @@
         <v>-2.9515</v>
       </c>
       <c r="AE74" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF74">
         <v>-0.000278</v>
@@ -24141,10 +24219,10 @@
     </row>
     <row r="75" spans="1:47">
       <c r="A75" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B75" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C75" s="2">
         <v>45094.40279944445</v>
@@ -24165,16 +24243,16 @@
         <v>2700</v>
       </c>
       <c r="I75" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J75" t="b">
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="L75" t="s">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="M75">
         <v>121</v>
@@ -24210,7 +24288,7 @@
         <v>-2.96666667</v>
       </c>
       <c r="AE75" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF75">
         <v>-0.001667</v>
@@ -24263,10 +24341,10 @@
     </row>
     <row r="76" spans="1:47">
       <c r="A76" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B76" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C76" s="2">
         <v>45094.40314679398</v>
@@ -24287,16 +24365,16 @@
         <v>2730</v>
       </c>
       <c r="I76" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J76" t="b">
         <v>1</v>
       </c>
       <c r="K76" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="L76" t="s">
-        <v>475</v>
+        <v>485</v>
       </c>
       <c r="M76">
         <v>99</v>
@@ -24332,7 +24410,7 @@
         <v>-2.93633333</v>
       </c>
       <c r="AE76" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF76">
         <v>0.003333</v>
@@ -24385,10 +24463,10 @@
     </row>
     <row r="77" spans="1:47">
       <c r="A77" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B77" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C77" s="2">
         <v>45094.40349465278</v>
@@ -24409,16 +24487,16 @@
         <v>2760</v>
       </c>
       <c r="I77" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J77" t="b">
         <v>1</v>
       </c>
       <c r="K77" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="L77" t="s">
-        <v>476</v>
+        <v>486</v>
       </c>
       <c r="M77">
         <v>83</v>
@@ -24454,7 +24532,7 @@
         <v>-3.00733333</v>
       </c>
       <c r="AE77" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF77">
         <v>-0.007778</v>
@@ -24507,10 +24585,10 @@
     </row>
     <row r="78" spans="1:47">
       <c r="A78" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B78" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C78" s="2">
         <v>45094.40384165509</v>
@@ -24531,16 +24609,16 @@
         <v>2790</v>
       </c>
       <c r="I78" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J78" t="b">
         <v>1</v>
       </c>
       <c r="K78" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="L78" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="M78">
         <v>61</v>
@@ -24576,7 +24654,7 @@
         <v>-2.87533333</v>
       </c>
       <c r="AE78" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF78">
         <v>0.014444</v>
@@ -24629,10 +24707,10 @@
     </row>
     <row r="79" spans="1:47">
       <c r="A79" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B79" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C79" s="2">
         <v>45094.40418819444</v>
@@ -24653,16 +24731,16 @@
         <v>2820</v>
       </c>
       <c r="I79" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J79" t="b">
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="L79" t="s">
-        <v>478</v>
+        <v>488</v>
       </c>
       <c r="M79">
         <v>52</v>
@@ -24698,7 +24776,7 @@
         <v>-2.90566667</v>
       </c>
       <c r="AE79" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF79">
         <v>-0.003333</v>
@@ -24751,10 +24829,10 @@
     </row>
     <row r="80" spans="1:47">
       <c r="A80" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B80" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C80" s="2">
         <v>45094.40453605324</v>
@@ -24775,16 +24853,16 @@
         <v>2850</v>
       </c>
       <c r="I80" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J80" t="b">
         <v>1</v>
       </c>
       <c r="K80" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="L80" t="s">
-        <v>479</v>
+        <v>489</v>
       </c>
       <c r="M80">
         <v>24</v>
@@ -24820,7 +24898,7 @@
         <v>-2.88533333</v>
       </c>
       <c r="AE80" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF80">
         <v>0.002222</v>
@@ -24873,10 +24951,10 @@
     </row>
     <row r="81" spans="1:47">
       <c r="A81" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B81" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C81" s="2">
         <v>45094.40488373843</v>
@@ -24897,16 +24975,16 @@
         <v>2880</v>
       </c>
       <c r="I81" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J81" t="b">
         <v>1</v>
       </c>
       <c r="K81" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="L81" t="s">
-        <v>480</v>
+        <v>490</v>
       </c>
       <c r="M81">
         <v>81</v>
@@ -24942,7 +25020,7 @@
         <v>-2.916</v>
       </c>
       <c r="AE81" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF81">
         <v>-0.003333</v>
@@ -24995,10 +25073,10 @@
     </row>
     <row r="82" spans="1:47">
       <c r="A82" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B82" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C82" s="2">
         <v>45094.40523104167</v>
@@ -25019,16 +25097,16 @@
         <v>2910</v>
       </c>
       <c r="I82" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J82" t="b">
         <v>1</v>
       </c>
       <c r="K82" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="L82" t="s">
-        <v>481</v>
+        <v>491</v>
       </c>
       <c r="M82">
         <v>175</v>
@@ -25064,7 +25142,7 @@
         <v>-2.87533333</v>
       </c>
       <c r="AE82" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF82">
         <v>0.004444</v>
@@ -25117,10 +25195,10 @@
     </row>
     <row r="83" spans="1:47">
       <c r="A83" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B83" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C83" s="2">
         <v>45094.40557918981</v>
@@ -25141,16 +25219,16 @@
         <v>2940</v>
       </c>
       <c r="I83" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
       </c>
       <c r="K83" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="L83" t="s">
-        <v>482</v>
+        <v>492</v>
       </c>
       <c r="M83">
         <v>173</v>
@@ -25186,7 +25264,7 @@
         <v>-2.96666667</v>
       </c>
       <c r="AE83" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF83">
         <v>-0.01</v>
@@ -25239,10 +25317,10 @@
     </row>
     <row r="84" spans="1:47">
       <c r="A84" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C84" s="2">
         <v>45094.40662034722</v>
@@ -25263,16 +25341,16 @@
         <v>3030</v>
       </c>
       <c r="I84" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J84" t="b">
         <v>1</v>
       </c>
       <c r="K84" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="L84" t="s">
-        <v>483</v>
+        <v>493</v>
       </c>
       <c r="M84">
         <v>214</v>
@@ -25308,7 +25386,7 @@
         <v>-2.91933333</v>
       </c>
       <c r="AE84" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF84">
         <v>0.001728</v>
@@ -25361,10 +25439,10 @@
     </row>
     <row r="85" spans="1:47">
       <c r="A85" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C85" s="2">
         <v>45094.40696665509</v>
@@ -25385,16 +25463,16 @@
         <v>3060</v>
       </c>
       <c r="I85" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J85" t="b">
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="L85" t="s">
-        <v>484</v>
+        <v>494</v>
       </c>
       <c r="M85">
         <v>250</v>
@@ -25430,7 +25508,7 @@
         <v>-2.794</v>
       </c>
       <c r="AE85" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF85">
         <v>0.013704</v>
@@ -25483,10 +25561,10 @@
     </row>
     <row r="86" spans="1:47">
       <c r="A86" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B86" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C86" s="2">
         <v>45094.40732755787</v>
@@ -25507,16 +25585,16 @@
         <v>3090</v>
       </c>
       <c r="I86" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J86" t="b">
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="L86" t="s">
-        <v>485</v>
+        <v>495</v>
       </c>
       <c r="M86">
         <v>316</v>
@@ -25552,7 +25630,7 @@
         <v>-2.75333333</v>
       </c>
       <c r="AE86" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF86">
         <v>0.004444</v>
@@ -25605,10 +25683,10 @@
     </row>
     <row r="87" spans="1:47">
       <c r="A87" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B87" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C87" s="2">
         <v>45094.40800915509</v>
@@ -25629,16 +25707,16 @@
         <v>3150</v>
       </c>
       <c r="I87" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J87" t="b">
         <v>1</v>
       </c>
       <c r="K87" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="L87" t="s">
-        <v>486</v>
+        <v>496</v>
       </c>
       <c r="M87">
         <v>114</v>
@@ -25674,7 +25752,7 @@
         <v>-2.65183333</v>
       </c>
       <c r="AE87" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF87">
         <v>0.005556</v>
@@ -25727,10 +25805,10 @@
     </row>
     <row r="88" spans="1:47">
       <c r="A88" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B88" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C88" s="2">
         <v>45094.40835655093</v>
@@ -25751,16 +25829,16 @@
         <v>3180</v>
       </c>
       <c r="I88" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J88" t="b">
         <v>1</v>
       </c>
       <c r="K88" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="L88" t="s">
-        <v>487</v>
+        <v>497</v>
       </c>
       <c r="M88">
         <v>123</v>
@@ -25796,7 +25874,7 @@
         <v>-2.66166667</v>
       </c>
       <c r="AE88" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF88">
         <v>-0.001111</v>
@@ -25849,10 +25927,10 @@
     </row>
     <row r="89" spans="1:47">
       <c r="A89" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B89" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C89" s="2">
         <v>45094.40908092593</v>
@@ -25873,16 +25951,16 @@
         <v>3240</v>
       </c>
       <c r="I89" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J89" t="b">
         <v>1</v>
       </c>
       <c r="K89" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="L89" t="s">
-        <v>488</v>
+        <v>498</v>
       </c>
       <c r="M89">
         <v>164</v>
@@ -25918,7 +25996,7 @@
         <v>-2.67216667</v>
       </c>
       <c r="AE89" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF89">
         <v>-0.000556</v>
@@ -25971,10 +26049,10 @@
     </row>
     <row r="90" spans="1:47">
       <c r="A90" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C90" s="2">
         <v>45094.41575502315</v>
@@ -25995,16 +26073,16 @@
         <v>3810</v>
       </c>
       <c r="I90" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="J90" t="b">
         <v>1</v>
       </c>
       <c r="K90" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="L90" t="s">
-        <v>489</v>
+        <v>499</v>
       </c>
       <c r="M90">
         <v>124</v>
@@ -26040,7 +26118,7 @@
         <v>-2.71807018</v>
       </c>
       <c r="AE90" t="s">
-        <v>490</v>
+        <v>500</v>
       </c>
       <c r="AF90">
         <v>-0.000265</v>
